--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E83506-3ABA-4BD7-862A-E38BB160F416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B49FC9E-10B7-4880-BC83-4BF885AE744E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -6124,12 +6124,10 @@
         <v>25</v>
       </c>
       <c r="T42" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="V42" s="14" t="str">
         <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
@@ -7878,12 +7876,10 @@
         <v>37</v>
       </c>
       <c r="T63" s="18">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U63" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.97297297297297303</v>
+        <v>1</v>
       </c>
       <c r="V63" s="14" t="str">
         <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B49FC9E-10B7-4880-BC83-4BF885AE744E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23669BD7-D23B-4EB9-BFD2-B42016D79CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -17,9 +17,6 @@
     <sheet name="Terceiros" sheetId="3" r:id="rId2"/>
     <sheet name="jan_26 (2)" sheetId="4" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="IYD7460_">'jan_26 (2)'!$D$2:$D$4</definedName>
     <definedName name="Placa">Planilha2!#REF!</definedName>
@@ -46,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="65">
   <si>
     <t>Data</t>
   </si>
@@ -242,9 +239,6 @@
   <si>
     <t>Rosinaldo</t>
   </si>
-  <si>
-    <t>Atendeu a Meta</t>
-  </si>
 </sst>
 </file>
 
@@ -256,7 +250,7 @@
     <numFmt numFmtId="165" formatCode="&quot; &quot;[$R$-416]&quot; &quot;* #,##0.00&quot; &quot;;&quot;-&quot;[$R$-416]&quot; &quot;* #,##0.00&quot; &quot;;&quot; &quot;[$R$-416]&quot; &quot;* &quot;-&quot;#&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
     <numFmt numFmtId="166" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,22 +284,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u val="singleAccounting"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -513,10 +491,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -528,7 +506,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="156">
     <dxf>
       <font>
         <b/>
@@ -607,83 +585,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -738,8 +639,401 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="&quot; R$ &quot;* #,##0.00&quot; &quot;;&quot;-R$ &quot;* #,##0.00&quot; &quot;;&quot; R$ &quot;* &quot;-&quot;00&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -756,404 +1050,7 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1191,6 +1088,622 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1653,124 +2166,95 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Planilha2"/>
-      <sheetName val="Terceiros"/>
-      <sheetName val="jan_26 (2)"/>
-      <sheetName val="Saida_BEL_2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>IUG8882</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V5" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V5" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="155" dataDxfId="153" headerRowBorderDxfId="154" tableBorderDxfId="152" totalsRowBorderDxfId="151" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V7" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="150"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="149"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="148"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="147"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="146" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="145" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="144"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="143" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="142"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="141"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="140">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="139" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="138" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="137"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="136"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="135"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="134">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="133" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="132" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="131"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="130"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="129"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y83" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:Y83" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y94" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36" headerRowCellStyle="Normal 2 2 2">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
-      <calculatedColumnFormula>YEAR([1]!Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
+      <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
-      <calculatedColumnFormula>MONTH([1]!Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
+      <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
-      <calculatedColumnFormula>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Porcentagem">
-      <calculatedColumnFormula>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Porcentagem">
+      <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
-      <calculatedColumnFormula>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
+      <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
-      <calculatedColumnFormula>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
+      <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
-      <calculatedColumnFormula>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
+      <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda 2 2">
-      <calculatedColumnFormula>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda 2 2">
+      <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25" dataCellStyle="Moeda 3">
-      <calculatedColumnFormula>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14" dataCellStyle="Moeda 3">
+      <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2199,7 +2683,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2551,40 +3035,150 @@
       <c r="U5" s="4"/>
       <c r="V5" s="5"/>
     </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>46247</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="10">
+        <v>5668.48</v>
+      </c>
+      <c r="F6" s="10">
+        <v>94110.1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>787</v>
+      </c>
+      <c r="H6" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>6.0232429887971631E-2</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="10">
+        <v>500</v>
+      </c>
+      <c r="M6" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>8.8207067855933172E-2</v>
+      </c>
+      <c r="N6" s="4">
+        <v>201</v>
+      </c>
+      <c r="O6" s="4">
+        <v>20</v>
+      </c>
+      <c r="P6" s="4">
+        <v>19</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="R6" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>0.95</v>
+      </c>
+      <c r="S6" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="U6" s="4">
+        <v>1</v>
+      </c>
+      <c r="V6" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="9" t="e">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="9" t="e">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S7" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H5">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="cellIs" dxfId="128" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="127" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R5">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R7">
+    <cfRule type="cellIs" dxfId="126" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="125" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="124" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="123" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="122" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="120" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S5">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S7">
+    <cfRule type="expression" dxfId="119" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -2593,7 +3187,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="118" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2607,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y83"/>
+  <dimension ref="A1:Y94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2630,7 +3224,7 @@
     <col min="21" max="21" width="11.85546875" customWidth="1"/>
     <col min="22" max="22" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.5703125" customWidth="1"/>
-    <col min="24" max="24" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" customWidth="1"/>
     <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2716,11 +3310,11 @@
         <v>46237</v>
       </c>
       <c r="B2" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C2" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -2728,7 +3322,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G2" s="10">
@@ -2741,7 +3335,7 @@
         <v>2224</v>
       </c>
       <c r="J2" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>3.8545699274519507E-2</v>
       </c>
       <c r="K2" s="11">
@@ -2751,7 +3345,7 @@
         <v>0.75694444444444442</v>
       </c>
       <c r="M2" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4861111111111111</v>
       </c>
       <c r="N2" s="4">
@@ -2761,7 +3355,7 @@
         <v>123227</v>
       </c>
       <c r="P2" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>62</v>
       </c>
       <c r="Q2" s="4">
@@ -2774,15 +3368,15 @@
         <v>17</v>
       </c>
       <c r="T2" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U2" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V2" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W2" s="4" t="s">
@@ -2800,11 +3394,11 @@
         <v>46237</v>
       </c>
       <c r="B3" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C3" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -2812,7 +3406,7 @@
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G3" s="10">
@@ -2825,7 +3419,7 @@
         <v>519</v>
       </c>
       <c r="J3" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>9.3211981887903514E-2</v>
       </c>
       <c r="K3" s="11">
@@ -2835,7 +3429,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M3" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N3" s="4">
@@ -2845,7 +3439,7 @@
         <v>153447</v>
       </c>
       <c r="P3" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>89</v>
       </c>
       <c r="Q3" s="4">
@@ -2858,15 +3452,15 @@
         <v>14</v>
       </c>
       <c r="T3" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U3" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V3" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W3" s="4" t="s">
@@ -2884,11 +3478,11 @@
         <v>46237</v>
       </c>
       <c r="B4" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C4" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -2896,7 +3490,7 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G4" s="10">
@@ -2909,7 +3503,7 @@
         <v>2245</v>
       </c>
       <c r="J4" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.5853646691834012E-2</v>
       </c>
       <c r="K4" s="11">
@@ -2919,7 +3513,7 @@
         <v>0.75</v>
       </c>
       <c r="M4" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N4" s="4">
@@ -2929,7 +3523,7 @@
         <v>11546</v>
       </c>
       <c r="P4" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>61</v>
       </c>
       <c r="Q4" s="4">
@@ -2942,15 +3536,15 @@
         <v>34</v>
       </c>
       <c r="T4" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U4" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V4" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W4" s="4" t="s">
@@ -2968,11 +3562,11 @@
         <v>46237</v>
       </c>
       <c r="B5" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C5" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -2980,7 +3574,7 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G5" s="10">
@@ -2993,7 +3587,7 @@
         <v>2509</v>
       </c>
       <c r="J5" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.7971096064583387E-2</v>
       </c>
       <c r="K5" s="11">
@@ -3003,7 +3597,7 @@
         <v>0.75</v>
       </c>
       <c r="M5" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N5" s="4">
@@ -3013,7 +3607,7 @@
         <v>117125</v>
       </c>
       <c r="P5" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>55</v>
       </c>
       <c r="Q5" s="4">
@@ -3026,15 +3620,15 @@
         <v>42</v>
       </c>
       <c r="T5" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U5" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V5" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W5" s="4" t="s">
@@ -3052,11 +3646,11 @@
         <v>46237</v>
       </c>
       <c r="B6" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C6" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3064,7 +3658,7 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G6" s="10">
@@ -3077,7 +3671,7 @@
         <v>1838</v>
       </c>
       <c r="J6" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.801281622473675E-2</v>
       </c>
       <c r="K6" s="11">
@@ -3087,7 +3681,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M6" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N6" s="4">
@@ -3097,7 +3691,7 @@
         <v>140635</v>
       </c>
       <c r="P6" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>64</v>
       </c>
       <c r="Q6" s="4">
@@ -3110,15 +3704,15 @@
         <v>2</v>
       </c>
       <c r="T6" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U6" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V6" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W6" s="4" t="s">
@@ -3136,11 +3730,11 @@
         <v>46237</v>
       </c>
       <c r="B7" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C7" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -3148,7 +3742,7 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G7" s="10">
@@ -3161,7 +3755,7 @@
         <v>2762</v>
       </c>
       <c r="J7" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.1196562302592621E-2</v>
       </c>
       <c r="K7" s="11">
@@ -3171,7 +3765,7 @@
         <v>0.75</v>
       </c>
       <c r="M7" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N7" s="4">
@@ -3181,7 +3775,7 @@
         <v>278800</v>
       </c>
       <c r="P7" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>45</v>
       </c>
       <c r="Q7" s="4">
@@ -3194,15 +3788,15 @@
         <v>22</v>
       </c>
       <c r="T7" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U7" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V7" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W7" s="4" t="s">
@@ -3220,11 +3814,11 @@
         <v>46237</v>
       </c>
       <c r="B8" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C8" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -3232,7 +3826,7 @@
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
       </c>
       <c r="G8" s="10">
@@ -3245,7 +3839,7 @@
         <v>402</v>
       </c>
       <c r="J8" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.8128172372508483E-2</v>
       </c>
       <c r="K8" s="11">
@@ -3255,7 +3849,7 @@
         <v>0.75694444444444442</v>
       </c>
       <c r="M8" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46527777777777773</v>
       </c>
       <c r="N8" s="4">
@@ -3265,7 +3859,7 @@
         <v>273946</v>
       </c>
       <c r="P8" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>143</v>
       </c>
       <c r="Q8" s="4">
@@ -3278,15 +3872,15 @@
         <v>7</v>
       </c>
       <c r="T8" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U8" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V8" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W8" s="4" t="s">
@@ -3304,11 +3898,11 @@
         <v>46237</v>
       </c>
       <c r="B9" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C9" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -3316,7 +3910,7 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G9" s="10">
@@ -3329,7 +3923,7 @@
         <v>859</v>
       </c>
       <c r="J9" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.1286896194604435E-2</v>
       </c>
       <c r="K9" s="11">
@@ -3339,7 +3933,7 @@
         <v>0.75347222222222221</v>
       </c>
       <c r="M9" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46180555555555552</v>
       </c>
       <c r="N9" s="4">
@@ -3349,7 +3943,7 @@
         <v>302272</v>
       </c>
       <c r="P9" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>136</v>
       </c>
       <c r="Q9" s="4">
@@ -3362,15 +3956,15 @@
         <v>30</v>
       </c>
       <c r="T9" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U9" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V9" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W9" s="4" t="s">
@@ -3388,11 +3982,11 @@
         <v>46237</v>
       </c>
       <c r="B10" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C10" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -3400,7 +3994,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Geber</v>
       </c>
       <c r="G10" s="10">
@@ -3413,7 +4007,7 @@
         <v>101</v>
       </c>
       <c r="J10" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.0499533457146589E-2</v>
       </c>
       <c r="K10" s="11">
@@ -3423,13 +4017,13 @@
         <v>0.75</v>
       </c>
       <c r="M10" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>0</v>
       </c>
       <c r="Q10" s="4">
@@ -3442,15 +4036,15 @@
         <v>6</v>
       </c>
       <c r="T10" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U10" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V10" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W10" s="4" t="s">
@@ -3468,11 +4062,11 @@
         <v>46237</v>
       </c>
       <c r="B11" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C11" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -3480,7 +4074,7 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G11" s="10">
@@ -3493,7 +4087,7 @@
         <v>2812</v>
       </c>
       <c r="J11" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.6423066134030865E-2</v>
       </c>
       <c r="K11" s="11">
@@ -3503,7 +4097,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M11" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N11" s="4">
@@ -3513,7 +4107,7 @@
         <v>289406</v>
       </c>
       <c r="P11" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>36</v>
       </c>
       <c r="Q11" s="4">
@@ -3526,15 +4120,15 @@
         <v>7</v>
       </c>
       <c r="T11" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U11" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V11" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W11" s="4" t="s">
@@ -3552,11 +4146,11 @@
         <v>46237</v>
       </c>
       <c r="B12" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C12" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -3564,7 +4158,7 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G12" s="10">
@@ -3577,7 +4171,7 @@
         <v>4822</v>
       </c>
       <c r="J12" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.17851393945457206</v>
       </c>
       <c r="K12" s="11">
@@ -3587,7 +4181,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M12" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333337</v>
       </c>
       <c r="N12" s="4">
@@ -3597,7 +4191,7 @@
         <v>102859</v>
       </c>
       <c r="P12" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>31</v>
       </c>
       <c r="Q12" s="4">
@@ -3610,15 +4204,15 @@
         <v>6</v>
       </c>
       <c r="T12" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U12" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V12" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W12" s="4" t="s">
@@ -3636,11 +4230,11 @@
         <v>46238</v>
       </c>
       <c r="B13" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C13" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -3648,7 +4242,7 @@
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G13" s="10">
@@ -3661,7 +4255,7 @@
         <v>1533</v>
       </c>
       <c r="J13" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.8873290920448027E-2</v>
       </c>
       <c r="K13" s="11">
@@ -3671,7 +4265,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="M13" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666663</v>
       </c>
       <c r="N13" s="4">
@@ -3681,7 +4275,7 @@
         <v>117070</v>
       </c>
       <c r="P13" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>61</v>
       </c>
       <c r="Q13" s="4">
@@ -3694,15 +4288,15 @@
         <v>33</v>
       </c>
       <c r="T13" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U13" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V13" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W13" s="4" t="s">
@@ -3720,11 +4314,11 @@
         <v>46239</v>
       </c>
       <c r="B14" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C14" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -3732,7 +4326,7 @@
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G14" s="10">
@@ -3745,7 +4339,7 @@
         <v>4963</v>
       </c>
       <c r="J14" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.1476123237158002E-2</v>
       </c>
       <c r="K14" s="11">
@@ -3755,7 +4349,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M14" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N14" s="4">
@@ -3765,7 +4359,7 @@
         <v>302430</v>
       </c>
       <c r="P14" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>158</v>
       </c>
       <c r="Q14" s="4">
@@ -3778,15 +4372,15 @@
         <v>26</v>
       </c>
       <c r="T14" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U14" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V14" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W14" s="4" t="s">
@@ -3804,11 +4398,11 @@
         <v>46239</v>
       </c>
       <c r="B15" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C15" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -3816,7 +4410,7 @@
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G15" s="10">
@@ -3829,7 +4423,7 @@
         <v>591</v>
       </c>
       <c r="J15" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.7918005242363216E-2</v>
       </c>
       <c r="K15" s="11">
@@ -3839,7 +4433,7 @@
         <v>0.76458333333333328</v>
       </c>
       <c r="M15" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.51458333333333328</v>
       </c>
       <c r="N15" s="4">
@@ -3849,7 +4443,7 @@
         <v>11570</v>
       </c>
       <c r="P15" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>24</v>
       </c>
       <c r="Q15" s="4">
@@ -3862,15 +4456,15 @@
         <v>24</v>
       </c>
       <c r="T15" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U15" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V15" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W15" s="4" t="s">
@@ -3888,11 +4482,11 @@
         <v>46239</v>
       </c>
       <c r="B16" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C16" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -3900,7 +4494,7 @@
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G16" s="10">
@@ -3913,7 +4507,7 @@
         <v>4110</v>
       </c>
       <c r="J16" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.12070221234511309</v>
       </c>
       <c r="K16" s="11">
@@ -3923,7 +4517,7 @@
         <v>0.75</v>
       </c>
       <c r="M16" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N16" s="4">
@@ -3933,7 +4527,7 @@
         <v>140739</v>
       </c>
       <c r="P16" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>104</v>
       </c>
       <c r="Q16" s="4">
@@ -3943,16 +4537,19 @@
         <v>19</v>
       </c>
       <c r="S16" s="4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T16" s="12">
-        <v>0</v>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
       </c>
       <c r="U16" s="13">
-        <v>1</v>
-      </c>
-      <c r="V16" s="14" t="s">
-        <v>65</v>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="V16" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
       </c>
       <c r="W16" s="4" t="s">
         <v>40</v>
@@ -3969,11 +4566,11 @@
         <v>46239</v>
       </c>
       <c r="B17" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C17" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -3981,7 +4578,7 @@
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G17" s="10">
@@ -3994,7 +4591,7 @@
         <v>4914</v>
       </c>
       <c r="J17" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>9.5632556871945273E-2</v>
       </c>
       <c r="K17" s="11">
@@ -4004,7 +4601,7 @@
         <v>0.75</v>
       </c>
       <c r="M17" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N17" s="4">
@@ -4014,7 +4611,7 @@
         <v>102890</v>
       </c>
       <c r="P17" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>21</v>
       </c>
       <c r="Q17" s="4">
@@ -4027,15 +4624,15 @@
         <v>8</v>
       </c>
       <c r="T17" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U17" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V17" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W17" s="4" t="s">
@@ -4053,11 +4650,11 @@
         <v>46239</v>
       </c>
       <c r="B18" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C18" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -4065,7 +4662,7 @@
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G18" s="10">
@@ -4078,7 +4675,7 @@
         <v>1482</v>
       </c>
       <c r="J18" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.5057524904112608E-2</v>
       </c>
       <c r="K18" s="11">
@@ -4088,7 +4685,7 @@
         <v>0.75694444444444442</v>
       </c>
       <c r="M18" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46527777777777773</v>
       </c>
       <c r="N18" s="4">
@@ -4098,7 +4695,7 @@
         <v>123287</v>
       </c>
       <c r="P18" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>67</v>
       </c>
       <c r="Q18" s="4">
@@ -4111,15 +4708,15 @@
         <v>19</v>
       </c>
       <c r="T18" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U18" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V18" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W18" s="4" t="s">
@@ -4137,11 +4734,11 @@
         <v>46239</v>
       </c>
       <c r="B19" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C19" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -4149,7 +4746,7 @@
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G19" s="10">
@@ -4162,7 +4759,7 @@
         <v>33</v>
       </c>
       <c r="J19" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>8.005985954856347E-2</v>
       </c>
       <c r="K19" s="11">
@@ -4172,7 +4769,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="M19" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="N19" s="4">
@@ -4182,7 +4779,7 @@
         <v>153483</v>
       </c>
       <c r="P19" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>35</v>
       </c>
       <c r="Q19" s="4">
@@ -4195,15 +4792,15 @@
         <v>3</v>
       </c>
       <c r="T19" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U19" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V19" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W19" s="4" t="s">
@@ -4221,11 +4818,11 @@
         <v>46239</v>
       </c>
       <c r="B20" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C20" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -4233,7 +4830,7 @@
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G20" s="10">
@@ -4246,7 +4843,7 @@
         <v>363</v>
       </c>
       <c r="J20" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.8301509044720737E-2</v>
       </c>
       <c r="K20" s="11">
@@ -4256,7 +4853,7 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="M20" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.11805555555555558</v>
       </c>
       <c r="N20" s="4">
@@ -4266,7 +4863,7 @@
         <v>153515</v>
       </c>
       <c r="P20" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>32</v>
       </c>
       <c r="Q20" s="4">
@@ -4279,15 +4876,15 @@
         <v>7</v>
       </c>
       <c r="T20" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U20" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V20" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W20" s="4" t="s">
@@ -4305,11 +4902,11 @@
         <v>46239</v>
       </c>
       <c r="B21" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C21" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -4317,7 +4914,7 @@
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G21" s="10">
@@ -4330,7 +4927,7 @@
         <v>2449</v>
       </c>
       <c r="J21" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.5232407837382614E-2</v>
       </c>
       <c r="K21" s="11">
@@ -4340,7 +4937,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="M21" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.47916666666666669</v>
       </c>
       <c r="N21" s="4">
@@ -4350,7 +4947,7 @@
         <v>278869</v>
       </c>
       <c r="P21" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>69</v>
       </c>
       <c r="Q21" s="4">
@@ -4363,15 +4960,15 @@
         <v>43</v>
       </c>
       <c r="T21" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U21" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V21" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W21" s="4" t="s">
@@ -4389,11 +4986,11 @@
         <v>46239</v>
       </c>
       <c r="B22" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C22" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -4401,7 +4998,7 @@
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G22" s="10">
@@ -4414,7 +5011,7 @@
         <v>2178</v>
       </c>
       <c r="J22" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.9317278939742877E-2</v>
       </c>
       <c r="K22" s="11">
@@ -4424,7 +5021,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M22" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N22" s="4">
@@ -4434,7 +5031,7 @@
         <v>117184</v>
       </c>
       <c r="P22" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>59</v>
       </c>
       <c r="Q22" s="4">
@@ -4447,15 +5044,15 @@
         <v>27</v>
       </c>
       <c r="T22" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U22" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V22" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W22" s="4" t="s">
@@ -4473,11 +5070,11 @@
         <v>46239</v>
       </c>
       <c r="B23" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C23" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -4485,7 +5082,7 @@
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
       </c>
       <c r="G23" s="10">
@@ -4498,7 +5095,7 @@
         <v>247</v>
       </c>
       <c r="J23" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>3.0523748058616632E-2</v>
       </c>
       <c r="K23" s="11">
@@ -4508,7 +5105,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="M23" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.43749999999999994</v>
       </c>
       <c r="N23" s="4">
@@ -4518,7 +5115,7 @@
         <v>273990</v>
       </c>
       <c r="P23" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>43</v>
       </c>
       <c r="Q23" s="4">
@@ -4531,15 +5128,15 @@
         <v>3</v>
       </c>
       <c r="T23" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U23" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V23" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W23" s="4" t="s">
@@ -4557,11 +5154,11 @@
         <v>46239</v>
       </c>
       <c r="B24" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C24" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -4569,7 +5166,7 @@
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G24" s="10">
@@ -4582,7 +5179,7 @@
         <v>2160</v>
       </c>
       <c r="J24" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.243385320181317E-2</v>
       </c>
       <c r="K24" s="11">
@@ -4592,7 +5189,7 @@
         <v>0.75</v>
       </c>
       <c r="M24" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N24" s="4">
@@ -4602,7 +5199,7 @@
         <v>289546</v>
       </c>
       <c r="P24" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>140</v>
       </c>
       <c r="Q24" s="4">
@@ -4615,15 +5212,15 @@
         <v>16</v>
       </c>
       <c r="T24" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U24" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V24" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W24" s="4" t="s">
@@ -4641,11 +5238,11 @@
         <v>46240</v>
       </c>
       <c r="B25" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C25" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
@@ -4653,7 +5250,7 @@
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G25" s="10">
@@ -4666,7 +5263,7 @@
         <v>7696</v>
       </c>
       <c r="J25" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.15509193746303343</v>
       </c>
       <c r="K25" s="11">
@@ -4676,7 +5273,7 @@
         <v>0.75</v>
       </c>
       <c r="M25" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N25" s="4">
@@ -4686,7 +5283,7 @@
         <v>102921</v>
       </c>
       <c r="P25" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>31</v>
       </c>
       <c r="Q25" s="4">
@@ -4699,15 +5296,15 @@
         <v>5</v>
       </c>
       <c r="T25" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U25" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V25" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W25" s="4" t="s">
@@ -4725,11 +5322,11 @@
         <v>46240</v>
       </c>
       <c r="B26" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C26" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -4737,7 +5334,7 @@
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G26" s="10">
@@ -4750,7 +5347,7 @@
         <v>1526</v>
       </c>
       <c r="J26" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.2526266263374371E-2</v>
       </c>
       <c r="K26" s="11">
@@ -4760,7 +5357,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M26" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N26" s="4">
@@ -4770,7 +5367,7 @@
         <v>117242</v>
       </c>
       <c r="P26" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>58</v>
       </c>
       <c r="Q26" s="4">
@@ -4783,15 +5380,15 @@
         <v>37</v>
       </c>
       <c r="T26" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U26" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V26" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W26" s="4" t="s">
@@ -4809,11 +5406,11 @@
         <v>46240</v>
       </c>
       <c r="B27" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C27" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
@@ -4821,7 +5418,7 @@
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
       </c>
       <c r="G27" s="10">
@@ -4834,7 +5431,7 @@
         <v>2144</v>
       </c>
       <c r="J27" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.5512345675149408E-2</v>
       </c>
       <c r="K27" s="11">
@@ -4844,7 +5441,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M27" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N27" s="4">
@@ -4854,7 +5451,7 @@
         <v>274022</v>
       </c>
       <c r="P27" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>32</v>
       </c>
       <c r="Q27" s="4">
@@ -4867,15 +5464,15 @@
         <v>3</v>
       </c>
       <c r="T27" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U27" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V27" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W27" s="4" t="s">
@@ -4893,11 +5490,11 @@
         <v>46240</v>
       </c>
       <c r="B28" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C28" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D28" s="4" t="s">
@@ -4905,7 +5502,7 @@
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G28" s="10">
@@ -4918,7 +5515,7 @@
         <v>1550</v>
       </c>
       <c r="J28" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.2649551333773442E-2</v>
       </c>
       <c r="K28" s="11">
@@ -4928,7 +5525,7 @@
         <v>0.75</v>
       </c>
       <c r="M28" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N28" s="4">
@@ -4938,7 +5535,7 @@
         <v>302561</v>
       </c>
       <c r="P28" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>131</v>
       </c>
       <c r="Q28" s="4">
@@ -4951,15 +5548,15 @@
         <v>24</v>
       </c>
       <c r="T28" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U28" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V28" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W28" s="4" t="s">
@@ -4977,11 +5574,11 @@
         <v>46240</v>
       </c>
       <c r="B29" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C29" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
@@ -4989,7 +5586,7 @@
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G29" s="10">
@@ -5002,7 +5599,7 @@
         <v>930</v>
       </c>
       <c r="J29" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.4511708776887772E-2</v>
       </c>
       <c r="K29" s="11">
@@ -5012,7 +5609,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M29" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N29" s="4">
@@ -5022,7 +5619,7 @@
         <v>123356</v>
       </c>
       <c r="P29" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>69</v>
       </c>
       <c r="Q29" s="4">
@@ -5035,15 +5632,15 @@
         <v>17</v>
       </c>
       <c r="T29" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U29" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V29" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W29" s="4" t="s">
@@ -5061,11 +5658,11 @@
         <v>46240</v>
       </c>
       <c r="B30" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C30" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -5073,7 +5670,7 @@
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G30" s="10">
@@ -5086,7 +5683,7 @@
         <v>995</v>
       </c>
       <c r="J30" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.2589214004699781E-2</v>
       </c>
       <c r="K30" s="11">
@@ -5096,7 +5693,7 @@
         <v>0.79305555555555551</v>
       </c>
       <c r="M30" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.50138888888888888</v>
       </c>
       <c r="N30" s="4">
@@ -5106,7 +5703,7 @@
         <v>11703</v>
       </c>
       <c r="P30" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>146</v>
       </c>
       <c r="Q30" s="4">
@@ -5119,15 +5716,15 @@
         <v>32</v>
       </c>
       <c r="T30" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U30" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V30" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W30" s="4" t="s">
@@ -5145,11 +5742,11 @@
         <v>46240</v>
       </c>
       <c r="B31" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C31" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -5157,7 +5754,7 @@
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G31" s="10">
@@ -5170,7 +5767,7 @@
         <v>1140</v>
       </c>
       <c r="J31" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.6454013822434876E-2</v>
       </c>
       <c r="K31" s="11">
@@ -5180,7 +5777,7 @@
         <v>0.625</v>
       </c>
       <c r="M31" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.375</v>
       </c>
       <c r="N31" s="4">
@@ -5190,7 +5787,7 @@
         <v>102972</v>
       </c>
       <c r="P31" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>51</v>
       </c>
       <c r="Q31" s="4">
@@ -5203,15 +5800,15 @@
         <v>1</v>
       </c>
       <c r="T31" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U31" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V31" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W31" s="4" t="s">
@@ -5229,11 +5826,11 @@
         <v>46240</v>
       </c>
       <c r="B32" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C32" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -5241,7 +5838,7 @@
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G32" s="10">
@@ -5254,7 +5851,7 @@
         <v>4100</v>
       </c>
       <c r="J32" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.3085232759453084E-2</v>
       </c>
       <c r="K32" s="11">
@@ -5264,7 +5861,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M32" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333337</v>
       </c>
       <c r="N32" s="4">
@@ -5274,7 +5871,7 @@
         <v>289691</v>
       </c>
       <c r="P32" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>145</v>
       </c>
       <c r="Q32" s="4">
@@ -5287,15 +5884,15 @@
         <v>8</v>
       </c>
       <c r="T32" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U32" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V32" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W32" s="4" t="s">
@@ -5313,11 +5910,11 @@
         <v>46240</v>
       </c>
       <c r="B33" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C33" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -5325,7 +5922,7 @@
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G33" s="10">
@@ -5338,7 +5935,7 @@
         <v>3580</v>
       </c>
       <c r="J33" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.13168376334262982</v>
       </c>
       <c r="K33" s="11">
@@ -5348,7 +5945,7 @@
         <v>0.72361111111111109</v>
       </c>
       <c r="M33" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41805555555555551</v>
       </c>
       <c r="N33" s="4">
@@ -5358,7 +5955,7 @@
         <v>278928</v>
       </c>
       <c r="P33" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>59</v>
       </c>
       <c r="Q33" s="4">
@@ -5371,15 +5968,15 @@
         <v>11</v>
       </c>
       <c r="T33" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U33" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V33" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W33" s="4" t="s">
@@ -5397,11 +5994,11 @@
         <v>46240</v>
       </c>
       <c r="B34" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C34" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -5409,7 +6006,7 @@
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G34" s="10">
@@ -5422,7 +6019,7 @@
         <v>184</v>
       </c>
       <c r="J34" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.11132403849056244</v>
       </c>
       <c r="K34" s="11">
@@ -5432,7 +6029,7 @@
         <v>0.71875</v>
       </c>
       <c r="M34" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.42708333333333331</v>
       </c>
       <c r="N34" s="4">
@@ -5442,7 +6039,7 @@
         <v>153588</v>
       </c>
       <c r="P34" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>73</v>
       </c>
       <c r="Q34" s="4">
@@ -5455,15 +6052,15 @@
         <v>7</v>
       </c>
       <c r="T34" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U34" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V34" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W34" s="4" t="s">
@@ -5481,11 +6078,11 @@
         <v>46241</v>
       </c>
       <c r="B35" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C35" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -5493,7 +6090,7 @@
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G35" s="10">
@@ -5506,7 +6103,7 @@
         <v>150</v>
       </c>
       <c r="J35" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.0295813380813876E-2</v>
       </c>
       <c r="K35" s="11">
@@ -5516,7 +6113,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M35" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N35" s="4">
@@ -5526,7 +6123,7 @@
         <v>153646</v>
       </c>
       <c r="P35" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>58</v>
       </c>
       <c r="Q35" s="4">
@@ -5539,15 +6136,15 @@
         <v>1</v>
       </c>
       <c r="T35" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U35" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V35" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W35" s="4" t="s">
@@ -5565,11 +6162,11 @@
         <v>46241</v>
       </c>
       <c r="B36" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C36" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -5577,7 +6174,7 @@
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G36" s="10">
@@ -5590,7 +6187,7 @@
         <v>2213</v>
       </c>
       <c r="J36" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>3.9133768959316008E-2</v>
       </c>
       <c r="K36" s="11">
@@ -5600,7 +6197,7 @@
         <v>0.75694444444444442</v>
       </c>
       <c r="M36" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.50694444444444442</v>
       </c>
       <c r="N36" s="4">
@@ -5610,7 +6207,7 @@
         <v>103105</v>
       </c>
       <c r="P36" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>133</v>
       </c>
       <c r="Q36" s="4">
@@ -5623,15 +6220,15 @@
         <v>2</v>
       </c>
       <c r="T36" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U36" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V36" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W36" s="4" t="s">
@@ -5649,11 +6246,11 @@
         <v>46241</v>
       </c>
       <c r="B37" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C37" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -5661,7 +6258,7 @@
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G37" s="10">
@@ -5674,7 +6271,7 @@
         <v>690</v>
       </c>
       <c r="J37" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.9794312337643285E-2</v>
       </c>
       <c r="K37" s="11">
@@ -5684,7 +6281,7 @@
         <v>0.72222222222222221</v>
       </c>
       <c r="M37" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.43055555555555552</v>
       </c>
       <c r="N37" s="4">
@@ -5694,7 +6291,7 @@
         <v>123713</v>
       </c>
       <c r="P37" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>57</v>
       </c>
       <c r="Q37" s="4">
@@ -5707,15 +6304,15 @@
         <v>22</v>
       </c>
       <c r="T37" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U37" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V37" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W37" s="4" t="s">
@@ -5733,11 +6330,11 @@
         <v>46241</v>
       </c>
       <c r="B38" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C38" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -5745,7 +6342,7 @@
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G38" s="10">
@@ -5758,7 +6355,7 @@
         <v>1104</v>
       </c>
       <c r="J38" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.0101048633456673E-2</v>
       </c>
       <c r="K38" s="11">
@@ -5768,7 +6365,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M38" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N38" s="4">
@@ -5778,7 +6375,7 @@
         <v>289832</v>
       </c>
       <c r="P38" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>141</v>
       </c>
       <c r="Q38" s="4">
@@ -5788,16 +6385,19 @@
         <v>11</v>
       </c>
       <c r="S38" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" s="12">
-        <v>0</v>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
       </c>
       <c r="U38" s="13">
-        <v>1</v>
-      </c>
-      <c r="V38" s="14" t="s">
-        <v>65</v>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="V38" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
       </c>
       <c r="W38" s="4" t="s">
         <v>45</v>
@@ -5814,11 +6414,11 @@
         <v>46241</v>
       </c>
       <c r="B39" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C39" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -5826,7 +6426,7 @@
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G39" s="10">
@@ -5839,7 +6439,7 @@
         <v>1147</v>
       </c>
       <c r="J39" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.4404668547993117E-2</v>
       </c>
       <c r="K39" s="11">
@@ -5849,7 +6449,7 @@
         <v>0.70486111111111116</v>
       </c>
       <c r="M39" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41319444444444448</v>
       </c>
       <c r="N39" s="4">
@@ -5859,7 +6459,7 @@
         <v>140875</v>
       </c>
       <c r="P39" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>64</v>
       </c>
       <c r="Q39" s="4">
@@ -5872,15 +6472,15 @@
         <v>21</v>
       </c>
       <c r="T39" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U39" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V39" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W39" s="4" t="s">
@@ -5898,11 +6498,11 @@
         <v>46241</v>
       </c>
       <c r="B40" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C40" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -5910,7 +6510,7 @@
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G40" s="10">
@@ -5923,7 +6523,7 @@
         <v>893</v>
       </c>
       <c r="J40" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.3372065391069238E-2</v>
       </c>
       <c r="K40" s="11">
@@ -5933,7 +6533,7 @@
         <v>0.70625000000000004</v>
       </c>
       <c r="M40" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41458333333333336</v>
       </c>
       <c r="N40" s="4">
@@ -5943,7 +6543,7 @@
         <v>278977</v>
       </c>
       <c r="P40" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>49</v>
       </c>
       <c r="Q40" s="4">
@@ -5956,15 +6556,15 @@
         <v>25</v>
       </c>
       <c r="T40" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U40" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V40" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W40" s="4" t="s">
@@ -5982,11 +6582,11 @@
         <v>46241</v>
       </c>
       <c r="B41" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C41" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -5994,7 +6594,7 @@
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G41" s="10">
@@ -6007,7 +6607,7 @@
         <v>1145</v>
       </c>
       <c r="J41" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.1000445429325976</v>
       </c>
       <c r="K41" s="11">
@@ -6017,7 +6617,7 @@
         <v>0.75</v>
       </c>
       <c r="M41" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N41" s="4">
@@ -6027,7 +6627,7 @@
         <v>302691</v>
       </c>
       <c r="P41" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>130</v>
       </c>
       <c r="Q41" s="4">
@@ -6040,15 +6640,15 @@
         <v>19</v>
       </c>
       <c r="T41" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U41" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V41" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W41" s="4" t="s">
@@ -6066,11 +6666,11 @@
         <v>46241</v>
       </c>
       <c r="B42" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C42" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -6078,7 +6678,7 @@
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G42" s="10">
@@ -6091,7 +6691,7 @@
         <v>1408</v>
       </c>
       <c r="J42" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.2319140710337863E-2</v>
       </c>
       <c r="K42" s="11">
@@ -6101,7 +6701,7 @@
         <v>0.79861111111111116</v>
       </c>
       <c r="M42" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.50694444444444442</v>
       </c>
       <c r="N42" s="4">
@@ -6111,7 +6711,7 @@
         <v>11777</v>
       </c>
       <c r="P42" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>74</v>
       </c>
       <c r="Q42" s="4">
@@ -6121,16 +6721,18 @@
         <v>25</v>
       </c>
       <c r="S42" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T42" s="12">
-        <v>0</v>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
       </c>
       <c r="U42" s="13">
-        <v>1</v>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.96</v>
       </c>
       <c r="V42" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W42" s="4" t="s">
@@ -6148,11 +6750,11 @@
         <v>46241</v>
       </c>
       <c r="B43" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C43" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -6160,7 +6762,7 @@
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G43" s="10">
@@ -6173,7 +6775,7 @@
         <v>942</v>
       </c>
       <c r="J43" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.2777754915126558E-2</v>
       </c>
       <c r="K43" s="11">
@@ -6183,7 +6785,7 @@
         <v>0.75</v>
       </c>
       <c r="M43" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444442</v>
       </c>
       <c r="N43" s="4">
@@ -6193,7 +6795,7 @@
         <v>117317</v>
       </c>
       <c r="P43" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>75</v>
       </c>
       <c r="Q43" s="4">
@@ -6206,15 +6808,15 @@
         <v>41</v>
       </c>
       <c r="T43" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U43" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V43" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W43" s="4" t="s">
@@ -6232,11 +6834,11 @@
         <v>46242</v>
       </c>
       <c r="B44" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C44" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -6244,7 +6846,7 @@
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G44" s="10">
@@ -6257,7 +6859,7 @@
         <v>497</v>
       </c>
       <c r="J44" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>8.5907826939101609E-2</v>
       </c>
       <c r="K44" s="11">
@@ -6267,7 +6869,7 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="M44" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4513888888888889</v>
       </c>
       <c r="N44" s="4">
@@ -6277,7 +6879,7 @@
         <v>117363</v>
       </c>
       <c r="P44" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>46</v>
       </c>
       <c r="Q44" s="4">
@@ -6290,15 +6892,15 @@
         <v>20</v>
       </c>
       <c r="T44" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U44" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V44" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W44" s="4" t="s">
@@ -6316,11 +6918,11 @@
         <v>46244</v>
       </c>
       <c r="B45" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C45" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -6328,7 +6930,7 @@
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G45" s="10">
@@ -6341,7 +6943,7 @@
         <v>92</v>
       </c>
       <c r="J45" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.4487920819350032E-2</v>
       </c>
       <c r="K45" s="11">
@@ -6351,7 +6953,7 @@
         <v>0.43541666666666667</v>
       </c>
       <c r="M45" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.14374999999999999</v>
       </c>
       <c r="N45" s="4">
@@ -6361,7 +6963,7 @@
         <v>153677</v>
       </c>
       <c r="P45" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>31</v>
       </c>
       <c r="Q45" s="4">
@@ -6374,15 +6976,15 @@
         <v>2</v>
       </c>
       <c r="T45" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U45" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V45" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W45" s="4" t="s">
@@ -6400,11 +7002,11 @@
         <v>46244</v>
       </c>
       <c r="B46" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C46" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -6412,7 +7014,7 @@
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G46" s="10">
@@ -6425,7 +7027,7 @@
         <v>4465</v>
       </c>
       <c r="J46" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.5527467697819776E-2</v>
       </c>
       <c r="K46" s="11">
@@ -6435,7 +7037,7 @@
         <v>0.7319444444444444</v>
       </c>
       <c r="M46" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44027777777777771</v>
       </c>
       <c r="N46" s="4">
@@ -6445,7 +7047,7 @@
         <v>103127</v>
       </c>
       <c r="P46" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>22</v>
       </c>
       <c r="Q46" s="4">
@@ -6458,15 +7060,15 @@
         <v>1</v>
       </c>
       <c r="T46" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U46" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V46" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W46" s="4" t="s">
@@ -6484,11 +7086,11 @@
         <v>46244</v>
       </c>
       <c r="B47" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C47" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -6496,7 +7098,7 @@
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G47" s="10">
@@ -6509,7 +7111,7 @@
         <v>540</v>
       </c>
       <c r="J47" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.3542810705775762E-2</v>
       </c>
       <c r="K47" s="11">
@@ -6519,7 +7121,7 @@
         <v>0.72569444444444442</v>
       </c>
       <c r="M47" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.43402777777777773</v>
       </c>
       <c r="N47" s="4">
@@ -6529,7 +7131,7 @@
         <v>153723</v>
       </c>
       <c r="P47" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>46</v>
       </c>
       <c r="Q47" s="4">
@@ -6539,16 +7141,19 @@
         <v>11</v>
       </c>
       <c r="S47" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T47" s="12">
-        <v>0</v>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
       </c>
       <c r="U47" s="13">
-        <v>1</v>
-      </c>
-      <c r="V47" s="14" t="s">
-        <v>65</v>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="V47" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
       </c>
       <c r="W47" s="4" t="s">
         <v>45</v>
@@ -6565,11 +7170,11 @@
         <v>46244</v>
       </c>
       <c r="B48" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C48" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
@@ -6577,7 +7182,7 @@
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G48" s="10">
@@ -6590,7 +7195,7 @@
         <v>1636</v>
       </c>
       <c r="J48" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.3844036212106065E-2</v>
       </c>
       <c r="K48" s="11">
@@ -6600,7 +7205,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M48" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N48" s="4">
@@ -6610,7 +7215,7 @@
         <v>302761</v>
       </c>
       <c r="P48" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>63</v>
       </c>
       <c r="Q48" s="4">
@@ -6623,15 +7228,15 @@
         <v>21</v>
       </c>
       <c r="T48" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U48" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V48" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W48" s="4" t="s">
@@ -6649,11 +7254,11 @@
         <v>46244</v>
       </c>
       <c r="B49" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C49" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -6661,7 +7266,7 @@
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G49" s="10">
@@ -6674,7 +7279,7 @@
         <v>2866</v>
       </c>
       <c r="J49" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.1605803212827671E-2</v>
       </c>
       <c r="K49" s="11">
@@ -6684,7 +7289,7 @@
         <v>0.71736111111111112</v>
       </c>
       <c r="M49" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.42569444444444443</v>
       </c>
       <c r="N49" s="4">
@@ -6694,7 +7299,7 @@
         <v>11840</v>
       </c>
       <c r="P49" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>63</v>
       </c>
       <c r="Q49" s="4">
@@ -6707,15 +7312,15 @@
         <v>20</v>
       </c>
       <c r="T49" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U49" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V49" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W49" s="4" t="s">
@@ -6733,11 +7338,11 @@
         <v>46244</v>
       </c>
       <c r="B50" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C50" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -6745,7 +7350,7 @@
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G50" s="10">
@@ -6758,7 +7363,7 @@
         <v>2970</v>
       </c>
       <c r="J50" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.4715311893779669E-2</v>
       </c>
       <c r="K50" s="11">
@@ -6768,7 +7373,7 @@
         <v>0.81736111111111109</v>
       </c>
       <c r="M50" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.52569444444444446</v>
       </c>
       <c r="N50" s="4">
@@ -6778,7 +7383,7 @@
         <v>279059</v>
       </c>
       <c r="P50" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>82</v>
       </c>
       <c r="Q50" s="4">
@@ -6788,16 +7393,19 @@
         <v>23</v>
       </c>
       <c r="S50" s="4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="T50" s="12">
-        <v>0</v>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
       </c>
       <c r="U50" s="13">
-        <v>1</v>
-      </c>
-      <c r="V50" s="14" t="s">
-        <v>65</v>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="V50" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
       </c>
       <c r="W50" s="4" t="s">
         <v>40</v>
@@ -6809,16 +7417,16 @@
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="17.25" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>46244</v>
       </c>
       <c r="B51" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C51" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
@@ -6826,10 +7434,10 @@
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
-      <c r="G51" s="17">
+      <c r="G51" s="10">
         <v>15692.95</v>
       </c>
       <c r="H51" s="10">
@@ -6839,7 +7447,7 @@
         <v>3125</v>
       </c>
       <c r="J51" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>3.8986176321872963E-2</v>
       </c>
       <c r="K51" s="11">
@@ -6849,7 +7457,7 @@
         <v>0.71597222222222223</v>
       </c>
       <c r="M51" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44513888888888892</v>
       </c>
       <c r="N51" s="4">
@@ -6859,7 +7467,7 @@
         <v>117491</v>
       </c>
       <c r="P51" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>128</v>
       </c>
       <c r="Q51" s="4">
@@ -6872,15 +7480,15 @@
         <v>3</v>
       </c>
       <c r="T51" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U51" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V51" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W51" s="4" t="s">
@@ -6898,11 +7506,11 @@
         <v>46244</v>
       </c>
       <c r="B52" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C52" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
@@ -6910,7 +7518,7 @@
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G52" s="10">
@@ -6923,7 +7531,7 @@
         <v>440</v>
       </c>
       <c r="J52" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.5706575522457566E-2</v>
       </c>
       <c r="K52" s="11">
@@ -6933,7 +7541,7 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="M52" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46874999999999994</v>
       </c>
       <c r="N52" s="4">
@@ -6943,7 +7551,7 @@
         <v>140931</v>
       </c>
       <c r="P52" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>117</v>
       </c>
       <c r="Q52" s="4">
@@ -6956,15 +7564,15 @@
         <v>7</v>
       </c>
       <c r="T52" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U52" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V52" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W52" s="4" t="s">
@@ -6982,11 +7590,11 @@
         <v>46244</v>
       </c>
       <c r="B53" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C53" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
@@ -6994,7 +7602,7 @@
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G53" s="10">
@@ -7007,7 +7615,7 @@
         <v>541</v>
       </c>
       <c r="J53" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.15234943420450589</v>
       </c>
       <c r="K53" s="11">
@@ -7017,7 +7625,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M53" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N53" s="4">
@@ -7027,7 +7635,7 @@
         <v>289852</v>
       </c>
       <c r="P53" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>79</v>
       </c>
       <c r="Q53" s="4">
@@ -7040,15 +7648,15 @@
         <v>9</v>
       </c>
       <c r="T53" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U53" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V53" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W53" s="4" t="s">
@@ -7066,11 +7674,11 @@
         <v>46244</v>
       </c>
       <c r="B54" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C54" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
@@ -7078,7 +7686,7 @@
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G54" s="10">
@@ -7091,7 +7699,7 @@
         <v>2718</v>
       </c>
       <c r="J54" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>8.4941538193435001E-2</v>
       </c>
       <c r="K54" s="11">
@@ -7101,7 +7709,7 @@
         <v>0.76180555555555551</v>
       </c>
       <c r="M54" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.47013888888888883</v>
       </c>
       <c r="N54" s="4">
@@ -7111,7 +7719,7 @@
         <v>123539</v>
       </c>
       <c r="P54" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>81</v>
       </c>
       <c r="Q54" s="4">
@@ -7124,15 +7732,15 @@
         <v>20</v>
       </c>
       <c r="T54" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U54" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V54" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W54" s="4" t="s">
@@ -7150,11 +7758,11 @@
         <v>46244</v>
       </c>
       <c r="B55" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C55" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
@@ -7162,7 +7770,7 @@
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Geber</v>
       </c>
       <c r="G55" s="10">
@@ -7175,7 +7783,7 @@
         <v>4993</v>
       </c>
       <c r="J55" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.7379244811118066E-2</v>
       </c>
       <c r="K55" s="11">
@@ -7185,7 +7793,7 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="M55" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4513888888888889</v>
       </c>
       <c r="N55" s="4">
@@ -7195,7 +7803,7 @@
         <v>364027</v>
       </c>
       <c r="P55" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>20</v>
       </c>
       <c r="Q55" s="4">
@@ -7208,15 +7816,15 @@
         <v>39</v>
       </c>
       <c r="T55" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U55" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V55" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W55" s="4" t="s">
@@ -7234,11 +7842,11 @@
         <v>46245</v>
       </c>
       <c r="B56" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C56" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
@@ -7246,7 +7854,7 @@
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G56" s="10">
@@ -7259,7 +7867,7 @@
         <v>1310</v>
       </c>
       <c r="J56" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.8118207921331757E-2</v>
       </c>
       <c r="K56" s="11">
@@ -7269,7 +7877,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M56" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N56" s="4">
@@ -7279,7 +7887,7 @@
         <v>11896</v>
       </c>
       <c r="P56" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>55</v>
       </c>
       <c r="Q56" s="4">
@@ -7292,15 +7900,15 @@
         <v>28</v>
       </c>
       <c r="T56" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U56" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V56" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W56" s="4" t="s">
@@ -7318,11 +7926,11 @@
         <v>46245</v>
       </c>
       <c r="B57" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C57" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
@@ -7330,7 +7938,7 @@
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G57" s="10">
@@ -7343,7 +7951,7 @@
         <v>664</v>
       </c>
       <c r="J57" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.9924817077331339E-2</v>
       </c>
       <c r="K57" s="11">
@@ -7353,7 +7961,7 @@
         <v>0.75</v>
       </c>
       <c r="M57" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N57" s="4">
@@ -7363,7 +7971,7 @@
         <v>289919</v>
       </c>
       <c r="P57" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>87</v>
       </c>
       <c r="Q57" s="4">
@@ -7376,15 +7984,15 @@
         <v>10</v>
       </c>
       <c r="T57" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U57" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V57" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W57" s="4" t="s">
@@ -7402,11 +8010,11 @@
         <v>46245</v>
       </c>
       <c r="B58" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C58" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D58" s="4" t="s">
@@ -7414,7 +8022,7 @@
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G58" s="10">
@@ -7427,7 +8035,7 @@
         <v>1764</v>
       </c>
       <c r="J58" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.7072686579120457E-2</v>
       </c>
       <c r="K58" s="11">
@@ -7437,7 +8045,7 @@
         <v>0.75694444444444442</v>
       </c>
       <c r="M58" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46527777777777773</v>
       </c>
       <c r="N58" s="4">
@@ -7447,7 +8055,7 @@
         <v>302814</v>
       </c>
       <c r="P58" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>53</v>
       </c>
       <c r="Q58" s="4">
@@ -7460,15 +8068,15 @@
         <v>22</v>
       </c>
       <c r="T58" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V58" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W58" s="4" t="s">
@@ -7486,11 +8094,11 @@
         <v>46245</v>
       </c>
       <c r="B59" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C59" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
@@ -7498,7 +8106,7 @@
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G59" s="10">
@@ -7511,7 +8119,7 @@
         <v>1345</v>
       </c>
       <c r="J59" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.11370733583018199</v>
       </c>
       <c r="K59" s="11">
@@ -7521,7 +8129,7 @@
         <v>0.75</v>
       </c>
       <c r="M59" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N59" s="4">
@@ -7531,7 +8139,7 @@
         <v>141128</v>
       </c>
       <c r="P59" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>197</v>
       </c>
       <c r="Q59" s="4">
@@ -7544,15 +8152,15 @@
         <v>17</v>
       </c>
       <c r="T59" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U59" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V59" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W59" s="4" t="s">
@@ -7570,11 +8178,11 @@
         <v>46245</v>
       </c>
       <c r="B60" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C60" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
@@ -7582,7 +8190,7 @@
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G60" s="10">
@@ -7595,7 +8203,7 @@
         <v>195</v>
       </c>
       <c r="J60" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.21166564277892039</v>
       </c>
       <c r="K60" s="11">
@@ -7605,7 +8213,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="M60" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.37499999999999994</v>
       </c>
       <c r="N60" s="4">
@@ -7613,7 +8221,7 @@
       </c>
       <c r="O60" s="4"/>
       <c r="P60" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>-15394</v>
       </c>
       <c r="Q60" s="4">
@@ -7626,15 +8234,15 @@
         <v>1</v>
       </c>
       <c r="T60" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U60" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V60" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W60" s="4" t="s">
@@ -7652,11 +8260,11 @@
         <v>46245</v>
       </c>
       <c r="B61" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C61" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
@@ -7664,7 +8272,7 @@
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G61" s="10">
@@ -7677,7 +8285,7 @@
         <v>1182</v>
       </c>
       <c r="J61" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.56520090909583232</v>
       </c>
       <c r="K61" s="11">
@@ -7687,7 +8295,7 @@
         <v>0.74652777777777779</v>
       </c>
       <c r="M61" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4548611111111111</v>
       </c>
       <c r="N61" s="4">
@@ -7697,7 +8305,7 @@
         <v>279145</v>
       </c>
       <c r="P61" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>86</v>
       </c>
       <c r="Q61" s="4">
@@ -7710,15 +8318,15 @@
         <v>30</v>
       </c>
       <c r="T61" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U61" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V61" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W61" s="4" t="s">
@@ -7736,11 +8344,11 @@
         <v>46245</v>
       </c>
       <c r="B62" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C62" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
@@ -7748,7 +8356,7 @@
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G62" s="10">
@@ -7761,7 +8369,7 @@
         <v>2473</v>
       </c>
       <c r="J62" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.581746264410369E-2</v>
       </c>
       <c r="K62" s="11">
@@ -7771,15 +8379,17 @@
         <v>0.75069444444444444</v>
       </c>
       <c r="M62" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45902777777777776</v>
       </c>
       <c r="N62" s="4">
-        <v>125534</v>
-      </c>
-      <c r="O62" s="4"/>
+        <v>123554</v>
+      </c>
+      <c r="O62" s="4">
+        <v>123596</v>
+      </c>
       <c r="P62" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>42</v>
       </c>
       <c r="Q62" s="4">
@@ -7792,15 +8402,15 @@
         <v>38</v>
       </c>
       <c r="T62" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>3</v>
       </c>
       <c r="U62" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>0.92682926829268297</v>
       </c>
       <c r="V62" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W62" s="4" t="s">
@@ -7818,11 +8428,11 @@
         <v>46245</v>
       </c>
       <c r="B63" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C63" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
@@ -7830,7 +8440,7 @@
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G63" s="10">
@@ -7843,7 +8453,7 @@
         <v>1306</v>
       </c>
       <c r="J63" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.0384568040795001E-2</v>
       </c>
       <c r="K63" s="11">
@@ -7853,7 +8463,7 @@
         <v>0.74375000000000002</v>
       </c>
       <c r="M63" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.49375000000000002</v>
       </c>
       <c r="N63" s="4">
@@ -7863,7 +8473,7 @@
         <v>117629</v>
       </c>
       <c r="P63" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>138</v>
       </c>
       <c r="Q63" s="4">
@@ -7873,16 +8483,18 @@
         <v>37</v>
       </c>
       <c r="S63" s="4">
-        <v>37</v>
-      </c>
-      <c r="T63" s="18">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="T63" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
       </c>
       <c r="U63" s="13">
-        <v>1</v>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.97297297297297303</v>
       </c>
       <c r="V63" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W63" s="4" t="s">
@@ -7900,11 +8512,11 @@
         <v>46245</v>
       </c>
       <c r="B64" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C64" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
@@ -7912,7 +8524,7 @@
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G64" s="10">
@@ -7925,7 +8537,7 @@
         <v>1858</v>
       </c>
       <c r="J64" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>1.6830067802879753E-2</v>
       </c>
       <c r="K64" s="11">
@@ -7935,7 +8547,7 @@
         <v>0.75</v>
       </c>
       <c r="M64" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N64" s="4">
@@ -7945,7 +8557,7 @@
         <v>103253</v>
       </c>
       <c r="P64" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>136</v>
       </c>
       <c r="Q64" s="4">
@@ -7958,15 +8570,15 @@
         <v>18</v>
       </c>
       <c r="T64" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U64" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V64" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W64" s="4" t="s">
@@ -7984,11 +8596,11 @@
         <v>46246</v>
       </c>
       <c r="B65" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C65" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
@@ -7996,7 +8608,7 @@
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G65" s="10">
@@ -8009,7 +8621,7 @@
         <v>1710</v>
       </c>
       <c r="J65" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.7499168012456398E-2</v>
       </c>
       <c r="K65" s="11">
@@ -8019,7 +8631,7 @@
         <v>0.75</v>
       </c>
       <c r="M65" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N65" s="4">
@@ -8029,7 +8641,7 @@
         <v>290052</v>
       </c>
       <c r="P65" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>133</v>
       </c>
       <c r="Q65" s="4">
@@ -8042,15 +8654,15 @@
         <v>14</v>
       </c>
       <c r="T65" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U65" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V65" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W65" s="4" t="s">
@@ -8068,11 +8680,11 @@
         <v>46246</v>
       </c>
       <c r="B66" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C66" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
@@ -8080,7 +8692,7 @@
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G66" s="10">
@@ -8093,7 +8705,7 @@
         <v>2403</v>
       </c>
       <c r="J66" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.5224679571740806E-2</v>
       </c>
       <c r="K66" s="11">
@@ -8103,7 +8715,7 @@
         <v>0.75</v>
       </c>
       <c r="M66" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N66" s="4">
@@ -8113,7 +8725,7 @@
         <v>302867</v>
       </c>
       <c r="P66" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>53</v>
       </c>
       <c r="Q66" s="4">
@@ -8126,15 +8738,15 @@
         <v>55</v>
       </c>
       <c r="T66" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U66" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V66" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W66" s="4" t="s">
@@ -8152,11 +8764,11 @@
         <v>46246</v>
       </c>
       <c r="B67" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C67" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
@@ -8164,7 +8776,7 @@
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G67" s="10">
@@ -8177,7 +8789,7 @@
         <v>2982</v>
       </c>
       <c r="J67" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.7366205707933949E-2</v>
       </c>
       <c r="K67" s="11">
@@ -8187,7 +8799,7 @@
         <v>0.75</v>
       </c>
       <c r="M67" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
       <c r="N67" s="4">
@@ -8197,7 +8809,7 @@
         <v>103402</v>
       </c>
       <c r="P67" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>149</v>
       </c>
       <c r="Q67" s="4">
@@ -8210,15 +8822,15 @@
         <v>13</v>
       </c>
       <c r="T67" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U67" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V67" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W67" s="4" t="s">
@@ -8236,11 +8848,11 @@
         <v>46246</v>
       </c>
       <c r="B68" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C68" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
@@ -8248,7 +8860,7 @@
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G68" s="10">
@@ -8261,7 +8873,7 @@
         <v>542</v>
       </c>
       <c r="J68" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.7001046814670322E-2</v>
       </c>
       <c r="K68" s="11">
@@ -8271,7 +8883,7 @@
         <v>0.67361111111111116</v>
       </c>
       <c r="M68" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.38194444444444448</v>
       </c>
       <c r="N68" s="4">
@@ -8281,7 +8893,7 @@
         <v>123626</v>
       </c>
       <c r="P68" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>30</v>
       </c>
       <c r="Q68" s="4">
@@ -8294,15 +8906,15 @@
         <v>5</v>
       </c>
       <c r="T68" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U68" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V68" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W68" s="4" t="s">
@@ -8320,11 +8932,11 @@
         <v>46246</v>
       </c>
       <c r="B69" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C69" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
@@ -8332,7 +8944,7 @@
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G69" s="10">
@@ -8345,7 +8957,7 @@
         <v>1332</v>
       </c>
       <c r="J69" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.7980011911240149E-2</v>
       </c>
       <c r="K69" s="11">
@@ -8355,7 +8967,7 @@
         <v>0.70138888888888884</v>
       </c>
       <c r="M69" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.40972222222222215</v>
       </c>
       <c r="N69" s="4">
@@ -8365,7 +8977,7 @@
         <v>141186</v>
       </c>
       <c r="P69" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>58</v>
       </c>
       <c r="Q69" s="4">
@@ -8378,15 +8990,15 @@
         <v>29</v>
       </c>
       <c r="T69" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U69" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V69" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W69" s="4" t="s">
@@ -8404,11 +9016,11 @@
         <v>46246</v>
       </c>
       <c r="B70" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C70" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
@@ -8416,7 +9028,7 @@
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G70" s="10">
@@ -8429,7 +9041,7 @@
         <v>507</v>
       </c>
       <c r="J70" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.12464334829467044</v>
       </c>
       <c r="K70" s="11">
@@ -8439,7 +9051,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M70" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N70" s="4">
@@ -8449,7 +9061,7 @@
         <v>153814</v>
       </c>
       <c r="P70" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>61</v>
       </c>
       <c r="Q70" s="4">
@@ -8462,15 +9074,15 @@
         <v>7</v>
       </c>
       <c r="T70" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U70" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V70" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W70" s="4" t="s">
@@ -8488,11 +9100,11 @@
         <v>46246</v>
       </c>
       <c r="B71" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C71" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
@@ -8500,7 +9112,7 @@
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G71" s="10">
@@ -8513,7 +9125,7 @@
         <v>523</v>
       </c>
       <c r="J71" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.0142230407586792E-2</v>
       </c>
       <c r="K71" s="11">
@@ -8523,7 +9135,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M71" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333337</v>
       </c>
       <c r="N71" s="4">
@@ -8533,7 +9145,7 @@
         <v>117763</v>
       </c>
       <c r="P71" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>134</v>
       </c>
       <c r="Q71" s="4">
@@ -8546,15 +9158,15 @@
         <v>14</v>
       </c>
       <c r="T71" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U71" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V71" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W71" s="4" t="s">
@@ -8572,11 +9184,11 @@
         <v>46246</v>
       </c>
       <c r="B72" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C72" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
@@ -8584,7 +9196,7 @@
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G72" s="10">
@@ -8597,7 +9209,7 @@
         <v>1171</v>
       </c>
       <c r="J72" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.110109089678568E-2</v>
       </c>
       <c r="K72" s="11">
@@ -8607,7 +9219,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M72" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N72" s="4">
@@ -8617,7 +9229,7 @@
         <v>11964</v>
       </c>
       <c r="P72" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>68</v>
       </c>
       <c r="Q72" s="4">
@@ -8630,15 +9242,15 @@
         <v>11</v>
       </c>
       <c r="T72" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U72" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V72" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W72" s="4" t="s">
@@ -8656,11 +9268,11 @@
         <v>46246</v>
       </c>
       <c r="B73" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C73" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
@@ -8668,7 +9280,7 @@
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G73" s="10">
@@ -8681,7 +9293,7 @@
         <v>1627</v>
       </c>
       <c r="J73" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.9530798248754022E-2</v>
       </c>
       <c r="K73" s="11">
@@ -8691,7 +9303,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="M73" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.49999999999999994</v>
       </c>
       <c r="N73" s="4">
@@ -8701,7 +9313,7 @@
         <v>279229</v>
       </c>
       <c r="P73" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>84</v>
       </c>
       <c r="Q73" s="4">
@@ -8714,15 +9326,15 @@
         <v>33</v>
       </c>
       <c r="T73" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U73" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V73" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W73" s="4" t="s">
@@ -8740,11 +9352,11 @@
         <v>46247</v>
       </c>
       <c r="B74" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C74" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
@@ -8752,7 +9364,7 @@
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
       <c r="G74" s="10">
@@ -8765,7 +9377,7 @@
         <v>772</v>
       </c>
       <c r="J74" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.4031982736457854E-2</v>
       </c>
       <c r="K74" s="11">
@@ -8775,7 +9387,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M74" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N74" s="4">
@@ -8785,7 +9397,7 @@
         <v>141261</v>
       </c>
       <c r="P74" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>75</v>
       </c>
       <c r="Q74" s="4">
@@ -8798,15 +9410,15 @@
         <v>13</v>
       </c>
       <c r="T74" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U74" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V74" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W74" s="4" t="s">
@@ -8824,11 +9436,11 @@
         <v>46247</v>
       </c>
       <c r="B75" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C75" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
@@ -8836,7 +9448,7 @@
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G75" s="10">
@@ -8849,7 +9461,7 @@
         <v>221</v>
       </c>
       <c r="J75" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.3821593575828695E-2</v>
       </c>
       <c r="K75" s="11">
@@ -8859,7 +9471,7 @@
         <v>0.73611111111111116</v>
       </c>
       <c r="M75" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
       <c r="N75" s="4">
@@ -8869,7 +9481,7 @@
         <v>153930</v>
       </c>
       <c r="P75" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>50</v>
       </c>
       <c r="Q75" s="4">
@@ -8882,15 +9494,15 @@
         <v>8</v>
       </c>
       <c r="T75" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U75" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V75" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W75" s="4" t="s">
@@ -8908,11 +9520,11 @@
         <v>46247</v>
       </c>
       <c r="B76" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C76" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D76" s="4" t="s">
@@ -8920,7 +9532,7 @@
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
       <c r="G76" s="10">
@@ -8933,7 +9545,7 @@
         <v>2008</v>
       </c>
       <c r="J76" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.8470350668902132E-2</v>
       </c>
       <c r="K76" s="11">
@@ -8943,7 +9555,7 @@
         <v>0.75</v>
       </c>
       <c r="M76" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N76" s="4">
@@ -8953,7 +9565,7 @@
         <v>302940</v>
       </c>
       <c r="P76" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>73</v>
       </c>
       <c r="Q76" s="4">
@@ -8966,15 +9578,15 @@
         <v>27</v>
       </c>
       <c r="T76" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U76" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V76" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W76" s="4" t="s">
@@ -8992,11 +9604,11 @@
         <v>46247</v>
       </c>
       <c r="B77" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C77" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
@@ -9004,7 +9616,7 @@
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
       </c>
       <c r="G77" s="10">
@@ -9017,7 +9629,7 @@
         <v>887</v>
       </c>
       <c r="J77" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>8.8333361297695562E-2</v>
       </c>
       <c r="K77" s="11">
@@ -9027,7 +9639,7 @@
         <v>0.75</v>
       </c>
       <c r="M77" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N77" s="4">
@@ -9037,7 +9649,7 @@
         <v>123706</v>
       </c>
       <c r="P77" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>79</v>
       </c>
       <c r="Q77" s="4">
@@ -9050,15 +9662,15 @@
         <v>11</v>
       </c>
       <c r="T77" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U77" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V77" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W77" s="4" t="s">
@@ -9076,11 +9688,11 @@
         <v>46247</v>
       </c>
       <c r="B78" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C78" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
@@ -9088,7 +9700,7 @@
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
       <c r="G78" s="10">
@@ -9101,7 +9713,7 @@
         <v>952</v>
       </c>
       <c r="J78" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.020803818242391E-2</v>
       </c>
       <c r="K78" s="11">
@@ -9111,7 +9723,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="M78" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.37499999999999994</v>
       </c>
       <c r="N78" s="4">
@@ -9121,7 +9733,7 @@
         <v>117817</v>
       </c>
       <c r="P78" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>54</v>
       </c>
       <c r="Q78" s="4">
@@ -9134,15 +9746,15 @@
         <v>18</v>
       </c>
       <c r="T78" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U78" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V78" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W78" s="4" t="s">
@@ -9160,11 +9772,11 @@
         <v>46247</v>
       </c>
       <c r="B79" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C79" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
@@ -9172,7 +9784,7 @@
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
       <c r="G79" s="10">
@@ -9185,7 +9797,7 @@
         <v>462</v>
       </c>
       <c r="J79" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>0.10280315113190275</v>
       </c>
       <c r="K79" s="11">
@@ -9195,7 +9807,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="M79" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
       <c r="N79" s="4">
@@ -9205,7 +9817,7 @@
         <v>290094</v>
       </c>
       <c r="P79" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>42</v>
       </c>
       <c r="Q79" s="4">
@@ -9218,15 +9830,15 @@
         <v>3</v>
       </c>
       <c r="T79" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U79" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V79" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W79" s="4" t="s">
@@ -9244,11 +9856,11 @@
         <v>46247</v>
       </c>
       <c r="B80" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C80" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
@@ -9256,7 +9868,7 @@
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
       <c r="G80" s="10">
@@ -9269,7 +9881,7 @@
         <v>13.8</v>
       </c>
       <c r="J80" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.7475198064449927E-2</v>
       </c>
       <c r="K80" s="11">
@@ -9279,7 +9891,7 @@
         <v>0.45763888888888887</v>
       </c>
       <c r="M80" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.16597222222222219</v>
       </c>
       <c r="N80" s="4">
@@ -9289,7 +9901,7 @@
         <v>153845</v>
       </c>
       <c r="P80" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>31</v>
       </c>
       <c r="Q80" s="4">
@@ -9302,15 +9914,15 @@
         <v>1</v>
       </c>
       <c r="T80" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U80" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V80" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W80" s="4" t="s">
@@ -9328,11 +9940,11 @@
         <v>46247</v>
       </c>
       <c r="B81" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C81" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
@@ -9340,7 +9952,7 @@
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
       <c r="G81" s="10">
@@ -9353,7 +9965,7 @@
         <v>7812</v>
       </c>
       <c r="J81" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.8402750030586195E-2</v>
       </c>
       <c r="K81" s="11">
@@ -9363,7 +9975,7 @@
         <v>0.75</v>
       </c>
       <c r="M81" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="N81" s="4">
@@ -9373,7 +9985,7 @@
         <v>103436</v>
       </c>
       <c r="P81" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>34</v>
       </c>
       <c r="Q81" s="4">
@@ -9386,15 +9998,15 @@
         <v>10</v>
       </c>
       <c r="T81" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U81" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V81" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W81" s="4" t="s">
@@ -9412,11 +10024,11 @@
         <v>46247</v>
       </c>
       <c r="B82" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C82" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
@@ -9424,7 +10036,7 @@
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
       </c>
       <c r="G82" s="10">
@@ -9437,7 +10049,7 @@
         <v>3473</v>
       </c>
       <c r="J82" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.5259348986576894E-2</v>
       </c>
       <c r="K82" s="11">
@@ -9447,7 +10059,7 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="M82" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4513888888888889</v>
       </c>
       <c r="N82" s="4">
@@ -9457,7 +10069,7 @@
         <v>279279</v>
       </c>
       <c r="P82" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>50</v>
       </c>
       <c r="Q82" s="4">
@@ -9470,15 +10082,15 @@
         <v>17</v>
       </c>
       <c r="T82" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U82" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V82" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W82" s="4" t="s">
@@ -9496,11 +10108,11 @@
         <v>46247</v>
       </c>
       <c r="B83" s="16">
-        <f>YEAR([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
       <c r="C83" s="16">
-        <f>MONTH([1]!Tabela32[[#This Row],[Data]])</f>
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
@@ -9508,7 +10120,7 @@
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4" t="str">
-        <f>IFERROR(VLOOKUP([1]!Tabela32[[#This Row],[Placa]],[1]Planilha2!$A$1:$B$12,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
       <c r="G83" s="10">
@@ -9521,7 +10133,7 @@
         <v>1212</v>
       </c>
       <c r="J83" s="9">
-        <f>IFERROR([1]!Tabela32[[#This Row],[Valor Frete]]/[1]!Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.1820002896484857E-2</v>
       </c>
       <c r="K83" s="11">
@@ -9531,7 +10143,7 @@
         <v>0.71736111111111112</v>
       </c>
       <c r="M83" s="15">
-        <f>[1]!Tabela32[[#This Row],[Hr Chegada]]-[1]!Tabela32[[#This Row],[Hr Saida]]</f>
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46736111111111112</v>
       </c>
       <c r="N83" s="4">
@@ -9541,7 +10153,7 @@
         <v>12099</v>
       </c>
       <c r="P83" s="4">
-        <f>[1]!Tabela32[[#This Row],[Km Chegada]]-[1]!Tabela32[[#This Row],[Km Saída]]</f>
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
         <v>135</v>
       </c>
       <c r="Q83" s="4">
@@ -9554,15 +10166,15 @@
         <v>24</v>
       </c>
       <c r="T83" s="12">
-        <f>[1]!Tabela32[[#This Row],[Entregas]]-[1]!Tabela32[[#This Row],[Realizadas]]</f>
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
       <c r="U83" s="13">
-        <f>[1]!Tabela32[[#This Row],[Realizadas]]/[1]!Tabela32[[#This Row],[Entregas]]</f>
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
       <c r="V83" s="14" t="str">
-        <f>IF([1]!Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
       <c r="W83" s="4" t="s">
@@ -9575,8 +10187,932 @@
         <v>38</v>
       </c>
     </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B84" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C84" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G84" s="10">
+        <v>7378.67</v>
+      </c>
+      <c r="H84" s="10">
+        <v>97331.41</v>
+      </c>
+      <c r="I84" s="4">
+        <v>795</v>
+      </c>
+      <c r="J84" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5809751446115903E-2</v>
+      </c>
+      <c r="K84" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L84" s="15">
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="M84" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="N84" s="4">
+        <v>123706</v>
+      </c>
+      <c r="O84" s="4">
+        <v>123852</v>
+      </c>
+      <c r="P84" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>146</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>158</v>
+      </c>
+      <c r="R84" s="4">
+        <v>19</v>
+      </c>
+      <c r="S84" s="4">
+        <v>19</v>
+      </c>
+      <c r="T84" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U84" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V84" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W84" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X84" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B85" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C85" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G85" s="10">
+        <v>11533.88</v>
+      </c>
+      <c r="H85" s="10">
+        <v>122470.23</v>
+      </c>
+      <c r="I85" s="4">
+        <v>2305</v>
+      </c>
+      <c r="J85" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.4177009384239743E-2</v>
+      </c>
+      <c r="K85" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L85" s="15">
+        <v>0.74791666666666667</v>
+      </c>
+      <c r="M85" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="N85" s="4">
+        <v>141361</v>
+      </c>
+      <c r="O85" s="4">
+        <v>141412</v>
+      </c>
+      <c r="P85" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>356</v>
+      </c>
+      <c r="R85" s="4">
+        <v>18</v>
+      </c>
+      <c r="S85" s="4">
+        <v>18</v>
+      </c>
+      <c r="T85" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U85" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V85" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W85" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X85" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B86" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C86" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G86" s="10">
+        <v>10059.02</v>
+      </c>
+      <c r="H86" s="10">
+        <v>66344.72</v>
+      </c>
+      <c r="I86" s="4">
+        <v>5603</v>
+      </c>
+      <c r="J86" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.15161749118844725</v>
+      </c>
+      <c r="K86" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L86" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="M86" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.20833333333333331</v>
+      </c>
+      <c r="N86" s="4">
+        <v>117817</v>
+      </c>
+      <c r="O86" s="4">
+        <v>117886</v>
+      </c>
+      <c r="P86" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>69</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>561</v>
+      </c>
+      <c r="R86" s="4">
+        <v>2</v>
+      </c>
+      <c r="S86" s="4">
+        <v>2</v>
+      </c>
+      <c r="T86" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U86" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V86" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X86" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B87" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C87" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G87" s="10">
+        <v>6929.72</v>
+      </c>
+      <c r="H87" s="10">
+        <v>109427.11</v>
+      </c>
+      <c r="I87" s="4">
+        <v>1223</v>
+      </c>
+      <c r="J87" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3327268717962126E-2</v>
+      </c>
+      <c r="K87" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L87" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M87" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="N87" s="4">
+        <v>279314</v>
+      </c>
+      <c r="O87" s="4">
+        <v>279422</v>
+      </c>
+      <c r="P87" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>108</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>155</v>
+      </c>
+      <c r="R87" s="4">
+        <v>23</v>
+      </c>
+      <c r="S87" s="4">
+        <v>20</v>
+      </c>
+      <c r="T87" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>3</v>
+      </c>
+      <c r="U87" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="V87" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W87" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X87" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y87" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B88" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C88" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G88" s="10">
+        <v>7158.89</v>
+      </c>
+      <c r="H88" s="10">
+        <v>169228.66</v>
+      </c>
+      <c r="I88" s="4">
+        <v>1333</v>
+      </c>
+      <c r="J88" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2303059068127112E-2</v>
+      </c>
+      <c r="K88" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L88" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M88" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N88" s="4">
+        <v>302940</v>
+      </c>
+      <c r="O88" s="4">
+        <v>303019</v>
+      </c>
+      <c r="P88" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>79</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>237</v>
+      </c>
+      <c r="R88" s="4">
+        <v>22</v>
+      </c>
+      <c r="S88" s="4">
+        <v>22</v>
+      </c>
+      <c r="T88" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U88" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V88" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W88" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X88" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B89" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C89" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G89" s="10">
+        <v>14499.96</v>
+      </c>
+      <c r="H89" s="10">
+        <v>338284.13</v>
+      </c>
+      <c r="I89" s="4">
+        <v>2232</v>
+      </c>
+      <c r="J89" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2863258172944736E-2</v>
+      </c>
+      <c r="K89" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="15">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M89" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="N89" s="4">
+        <v>12099</v>
+      </c>
+      <c r="O89" s="4">
+        <v>12226</v>
+      </c>
+      <c r="P89" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>127</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>48</v>
+      </c>
+      <c r="R89" s="4">
+        <v>9</v>
+      </c>
+      <c r="S89" s="4">
+        <v>9</v>
+      </c>
+      <c r="T89" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U89" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V89" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W89" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X89" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B90" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C90" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G90" s="10">
+        <v>11679.11</v>
+      </c>
+      <c r="H90" s="10">
+        <v>836250.49</v>
+      </c>
+      <c r="I90" s="4">
+        <v>1540</v>
+      </c>
+      <c r="J90" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.396604263873137E-2</v>
+      </c>
+      <c r="K90" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L90" s="15">
+        <v>0.75138888888888888</v>
+      </c>
+      <c r="M90" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="N90" s="4">
+        <v>103436</v>
+      </c>
+      <c r="O90" s="4">
+        <v>103478</v>
+      </c>
+      <c r="P90" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>87</v>
+      </c>
+      <c r="R90" s="4">
+        <v>8</v>
+      </c>
+      <c r="S90" s="4">
+        <v>8</v>
+      </c>
+      <c r="T90" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U90" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V90" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W90" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X90" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B91" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C91" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G91" s="10">
+        <v>6830.4</v>
+      </c>
+      <c r="H91" s="10">
+        <v>91300.7</v>
+      </c>
+      <c r="I91" s="4">
+        <v>1245</v>
+      </c>
+      <c r="J91" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4812131779931582E-2</v>
+      </c>
+      <c r="K91" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L91" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M91" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N91" s="4">
+        <v>270091</v>
+      </c>
+      <c r="O91" s="4">
+        <v>270160</v>
+      </c>
+      <c r="P91" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>69</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>211</v>
+      </c>
+      <c r="R91" s="4">
+        <v>20</v>
+      </c>
+      <c r="S91" s="4">
+        <v>20</v>
+      </c>
+      <c r="T91" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U91" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V91" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X91" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B92" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C92" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G92" s="10">
+        <v>3443.35</v>
+      </c>
+      <c r="H92" s="10">
+        <v>88816.89</v>
+      </c>
+      <c r="I92" s="4">
+        <v>999</v>
+      </c>
+      <c r="J92" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8769089978268771E-2</v>
+      </c>
+      <c r="K92" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L92" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M92" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43749999999999994</v>
+      </c>
+      <c r="N92" s="4">
+        <v>117886</v>
+      </c>
+      <c r="O92" s="4">
+        <v>117926</v>
+      </c>
+      <c r="P92" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>239</v>
+      </c>
+      <c r="R92" s="4">
+        <v>3</v>
+      </c>
+      <c r="S92" s="4">
+        <v>3</v>
+      </c>
+      <c r="T92" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U92" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V92" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W92" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X92" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A93" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B93" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C93" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G93" s="10">
+        <v>3838.27</v>
+      </c>
+      <c r="H93" s="10">
+        <v>249155.96</v>
+      </c>
+      <c r="I93" s="4">
+        <v>766</v>
+      </c>
+      <c r="J93" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.5405090048819223E-2</v>
+      </c>
+      <c r="K93" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L93" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M93" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N93" s="4">
+        <v>274120</v>
+      </c>
+      <c r="O93" s="4">
+        <v>274151</v>
+      </c>
+      <c r="P93" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>238</v>
+      </c>
+      <c r="R93" s="4">
+        <v>6</v>
+      </c>
+      <c r="S93" s="4">
+        <v>6</v>
+      </c>
+      <c r="T93" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U93" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V93" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W93" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X93" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A94" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B94" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C94" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G94" s="10">
+        <v>3065.33</v>
+      </c>
+      <c r="H94" s="10">
+        <v>154957.76999999999</v>
+      </c>
+      <c r="I94" s="4">
+        <v>487</v>
+      </c>
+      <c r="J94" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.9781712140023697E-2</v>
+      </c>
+      <c r="K94" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L94" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="M94" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.31249999999999994</v>
+      </c>
+      <c r="N94" s="4">
+        <v>153930</v>
+      </c>
+      <c r="O94" s="4">
+        <v>153980</v>
+      </c>
+      <c r="P94" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>3</v>
+      </c>
+      <c r="R94" s="4">
+        <v>3</v>
+      </c>
+      <c r="S94" s="4">
+        <v>3</v>
+      </c>
+      <c r="T94" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U94" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V94" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W94" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X94" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J83">
+  <conditionalFormatting sqref="J2:J94">
     <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -9584,7 +11120,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U83">
+  <conditionalFormatting sqref="U2:U94">
     <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -9607,7 +11143,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V83">
+  <conditionalFormatting sqref="V2:V94">
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -9633,7 +11169,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D64</xm:sqref>
+          <xm:sqref>D2:D94</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23669BD7-D23B-4EB9-BFD2-B42016D79CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4F86E4-9780-4DDF-92DE-A5ABE4EFF93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -441,7 +441,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,9 +494,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -506,1049 +503,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="156">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b/>
@@ -1866,7 +821,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1918,8 +872,63 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1952,7 +961,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2038,24 +1046,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -2071,8 +1062,25 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -2153,6 +1161,456 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2167,94 +1625,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="155" dataDxfId="153" headerRowBorderDxfId="154" tableBorderDxfId="152" totalsRowBorderDxfId="151" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V7" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="150"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="149"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="148"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="147"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="146" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="145" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="144"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="143" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="142"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="141"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="140">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="139" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="138" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="137"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="136"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="135"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="134">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="133" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="132" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="131"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="130"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="129"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y94" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y94" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47" headerRowCellStyle="Normal 2 2 2">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Porcentagem">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3147,38 +2605,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H7">
-    <cfRule type="cellIs" dxfId="128" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R7">
-    <cfRule type="cellIs" dxfId="126" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S7">
-    <cfRule type="expression" dxfId="119" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3187,7 +2645,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4020,11 +3478,15 @@
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="N10" s="4">
+        <v>363975</v>
+      </c>
+      <c r="O10" s="4">
+        <v>364007</v>
+      </c>
       <c r="P10" s="4">
         <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q10" s="4">
         <v>101</v>
@@ -8217,12 +7679,14 @@
         <v>0.37499999999999994</v>
       </c>
       <c r="N60" s="4">
-        <v>15394</v>
-      </c>
-      <c r="O60" s="4"/>
+        <v>153694</v>
+      </c>
+      <c r="O60" s="4">
+        <v>153753</v>
+      </c>
       <c r="P60" s="4">
         <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
-        <v>-15394</v>
+        <v>59</v>
       </c>
       <c r="Q60" s="4">
         <v>31</v>
@@ -10191,11 +9655,11 @@
       <c r="A84" s="8">
         <v>46248</v>
       </c>
-      <c r="B84" s="18">
+      <c r="B84" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C84" s="18">
+      <c r="C84" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10275,11 +9739,11 @@
       <c r="A85" s="8">
         <v>46248</v>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C85" s="18">
+      <c r="C85" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10359,11 +9823,11 @@
       <c r="A86" s="8">
         <v>46248</v>
       </c>
-      <c r="B86" s="18">
+      <c r="B86" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C86" s="18">
+      <c r="C86" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10443,11 +9907,11 @@
       <c r="A87" s="8">
         <v>46248</v>
       </c>
-      <c r="B87" s="18">
+      <c r="B87" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C87" s="18">
+      <c r="C87" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10527,11 +9991,11 @@
       <c r="A88" s="8">
         <v>46248</v>
       </c>
-      <c r="B88" s="18">
+      <c r="B88" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C88" s="18">
+      <c r="C88" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10611,11 +10075,11 @@
       <c r="A89" s="8">
         <v>46248</v>
       </c>
-      <c r="B89" s="18">
+      <c r="B89" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C89" s="18">
+      <c r="C89" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10695,11 +10159,11 @@
       <c r="A90" s="8">
         <v>46248</v>
       </c>
-      <c r="B90" s="18">
+      <c r="B90" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C90" s="18">
+      <c r="C90" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10779,11 +10243,11 @@
       <c r="A91" s="8">
         <v>46248</v>
       </c>
-      <c r="B91" s="18">
+      <c r="B91" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C91" s="18">
+      <c r="C91" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10863,11 +10327,11 @@
       <c r="A92" s="8">
         <v>46248</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -10947,11 +10411,11 @@
       <c r="A93" s="8">
         <v>46248</v>
       </c>
-      <c r="B93" s="18">
+      <c r="B93" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C93" s="18">
+      <c r="C93" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11031,11 +10495,11 @@
       <c r="A94" s="8">
         <v>46248</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C94" s="18">
+      <c r="C94" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4F86E4-9780-4DDF-92DE-A5ABE4EFF93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8073647-AD7E-4439-9028-E51DFFB9AC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="66">
   <si>
     <t>Data</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Rosinaldo</t>
+  </si>
+  <si>
+    <t>Marituba</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,6 +497,9 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -503,84 +509,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="79">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="145">
     <dxf>
       <font>
         <b/>
@@ -1101,6 +1030,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1118,13 +1054,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1162,6 +1091,545 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1625,94 +2093,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V7" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y94" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y105" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36" headerRowCellStyle="Neutro">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Porcentagem">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29" dataCellStyle="Hiperlink"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28" dataCellStyle="Hiperlink"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14" dataCellStyle="Moeda [0]">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2605,38 +3073,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H7">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R7">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S7">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -2645,7 +3113,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2659,7 +3127,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y94"/>
+  <dimension ref="A1:Y105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -10575,8 +11043,932 @@
         <v>0</v>
       </c>
     </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A95" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B95" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C95" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G95" s="10">
+        <v>12467.2</v>
+      </c>
+      <c r="H95" s="10">
+        <v>206725.72</v>
+      </c>
+      <c r="I95" s="4">
+        <v>2674</v>
+      </c>
+      <c r="J95" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0307928786026241E-2</v>
+      </c>
+      <c r="K95" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L95" s="15">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="M95" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="N95" s="4">
+        <v>12226</v>
+      </c>
+      <c r="O95" s="4">
+        <v>12296</v>
+      </c>
+      <c r="P95" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>70</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>318</v>
+      </c>
+      <c r="R95" s="4">
+        <v>26</v>
+      </c>
+      <c r="S95" s="4">
+        <v>26</v>
+      </c>
+      <c r="T95" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U95" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V95" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W95" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X95" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A96" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B96" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C96" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G96" s="10">
+        <v>1414.74</v>
+      </c>
+      <c r="H96" s="10">
+        <v>19675.72</v>
+      </c>
+      <c r="I96" s="4">
+        <v>168</v>
+      </c>
+      <c r="J96" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.1902832526586066E-2</v>
+      </c>
+      <c r="K96" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L96" s="15">
+        <v>0.71319444444444446</v>
+      </c>
+      <c r="M96" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="N96" s="4">
+        <v>154010</v>
+      </c>
+      <c r="O96" s="4">
+        <v>154047</v>
+      </c>
+      <c r="P96" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q96" s="4">
+        <v>21</v>
+      </c>
+      <c r="R96" s="4">
+        <v>5</v>
+      </c>
+      <c r="S96" s="4">
+        <v>5</v>
+      </c>
+      <c r="T96" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U96" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V96" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W96" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X96" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A97" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B97" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C97" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G97" s="10">
+        <v>8731.2199999999993</v>
+      </c>
+      <c r="H97" s="10">
+        <v>97372.43</v>
+      </c>
+      <c r="I97" s="4">
+        <v>1226</v>
+      </c>
+      <c r="J97" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.966829727880879E-2</v>
+      </c>
+      <c r="K97" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L97" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M97" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45138888888888884</v>
+      </c>
+      <c r="N97" s="4">
+        <v>290160</v>
+      </c>
+      <c r="O97" s="4">
+        <v>290216</v>
+      </c>
+      <c r="P97" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q97" s="4">
+        <v>251</v>
+      </c>
+      <c r="R97" s="4">
+        <v>12</v>
+      </c>
+      <c r="S97" s="4">
+        <v>12</v>
+      </c>
+      <c r="T97" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U97" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V97" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W97" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X97" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y97" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A98" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B98" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C98" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G98" s="10">
+        <v>9371.58</v>
+      </c>
+      <c r="H98" s="10">
+        <v>129112.22</v>
+      </c>
+      <c r="I98" s="4">
+        <v>1696</v>
+      </c>
+      <c r="J98" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.2584763858912812E-2</v>
+      </c>
+      <c r="K98" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L98" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M98" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="N98" s="4">
+        <v>274171</v>
+      </c>
+      <c r="O98" s="4">
+        <v>274288</v>
+      </c>
+      <c r="P98" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>117</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>111</v>
+      </c>
+      <c r="R98" s="4">
+        <v>23</v>
+      </c>
+      <c r="S98" s="4">
+        <v>23</v>
+      </c>
+      <c r="T98" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U98" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V98" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W98" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X98" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A99" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B99" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C99" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G99" s="10">
+        <v>13727.72</v>
+      </c>
+      <c r="H99" s="10">
+        <v>302941.99</v>
+      </c>
+      <c r="I99" s="4">
+        <v>1917</v>
+      </c>
+      <c r="J99" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5314682193775775E-2</v>
+      </c>
+      <c r="K99" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L99" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M99" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N99" s="4">
+        <v>103436</v>
+      </c>
+      <c r="O99" s="4">
+        <v>103460</v>
+      </c>
+      <c r="P99" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>24</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>954</v>
+      </c>
+      <c r="R99" s="4">
+        <v>12</v>
+      </c>
+      <c r="S99" s="4">
+        <v>12</v>
+      </c>
+      <c r="T99" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U99" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V99" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W99" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X99" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A100" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B100" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C100" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G100" s="10">
+        <v>8590.7999999999993</v>
+      </c>
+      <c r="H100" s="10">
+        <v>130505.5</v>
+      </c>
+      <c r="I100" s="4">
+        <v>1513</v>
+      </c>
+      <c r="J100" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5827110734796607E-2</v>
+      </c>
+      <c r="K100" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L100" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M100" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="N100" s="4">
+        <v>141412</v>
+      </c>
+      <c r="O100" s="4">
+        <v>141515</v>
+      </c>
+      <c r="P100" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>103</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>327</v>
+      </c>
+      <c r="R100" s="4">
+        <v>21</v>
+      </c>
+      <c r="S100" s="4">
+        <v>20</v>
+      </c>
+      <c r="T100" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U100" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="V100" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W100" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X100" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y100" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A101" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B101" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C101" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G101" s="10">
+        <v>7088.01</v>
+      </c>
+      <c r="H101" s="10">
+        <v>135271.22</v>
+      </c>
+      <c r="I101" s="4">
+        <v>796</v>
+      </c>
+      <c r="J101" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2398507236055089E-2</v>
+      </c>
+      <c r="K101" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L101" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M101" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N101" s="4">
+        <v>303019</v>
+      </c>
+      <c r="O101" s="4">
+        <v>303081</v>
+      </c>
+      <c r="P101" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>168</v>
+      </c>
+      <c r="R101" s="4">
+        <v>17</v>
+      </c>
+      <c r="S101" s="4">
+        <v>17</v>
+      </c>
+      <c r="T101" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U101" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V101" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X101" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A102" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B102" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C102" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G102" s="10">
+        <v>6420.79</v>
+      </c>
+      <c r="H102" s="10">
+        <v>126316.72</v>
+      </c>
+      <c r="I102" s="4">
+        <v>1373</v>
+      </c>
+      <c r="J102" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0830879712519449E-2</v>
+      </c>
+      <c r="K102" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L102" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M102" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="N102" s="4">
+        <v>117926</v>
+      </c>
+      <c r="O102" s="4">
+        <v>118030</v>
+      </c>
+      <c r="P102" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>104</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>178</v>
+      </c>
+      <c r="R102" s="4">
+        <v>21</v>
+      </c>
+      <c r="S102" s="4">
+        <v>21</v>
+      </c>
+      <c r="T102" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U102" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V102" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W102" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X102" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A103" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B103" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C103" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G103" s="10">
+        <v>8907.3799999999992</v>
+      </c>
+      <c r="H103" s="10">
+        <v>156529.39000000001</v>
+      </c>
+      <c r="I103" s="4">
+        <v>1950</v>
+      </c>
+      <c r="J103" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.690547953965705E-2</v>
+      </c>
+      <c r="K103" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L103" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M103" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333337</v>
+      </c>
+      <c r="N103" s="4">
+        <v>123852</v>
+      </c>
+      <c r="O103" s="4">
+        <v>124001</v>
+      </c>
+      <c r="P103" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>149</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>326</v>
+      </c>
+      <c r="R103" s="4">
+        <v>14</v>
+      </c>
+      <c r="S103" s="4">
+        <v>14</v>
+      </c>
+      <c r="T103" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U103" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V103" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W103" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X103" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A104" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B104" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C104" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G104" s="10">
+        <v>594.54999999999995</v>
+      </c>
+      <c r="H104" s="10">
+        <v>8970</v>
+      </c>
+      <c r="I104" s="4">
+        <v>12</v>
+      </c>
+      <c r="J104" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.628205128205128E-2</v>
+      </c>
+      <c r="K104" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L104" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M104" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="N104" s="4">
+        <v>279422</v>
+      </c>
+      <c r="O104" s="4">
+        <v>279465</v>
+      </c>
+      <c r="P104" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>5</v>
+      </c>
+      <c r="R104" s="4">
+        <v>1</v>
+      </c>
+      <c r="S104" s="4">
+        <v>1</v>
+      </c>
+      <c r="T104" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U104" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V104" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W104" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X104" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A105" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B105" s="18">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C105" s="18">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G105" s="10">
+        <v>766.59</v>
+      </c>
+      <c r="H105" s="10">
+        <v>47250.12</v>
+      </c>
+      <c r="I105" s="4">
+        <v>54</v>
+      </c>
+      <c r="J105" s="9">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.6224085780099606E-2</v>
+      </c>
+      <c r="K105" s="11">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="L105" s="15">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="M105" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="N105" s="4">
+        <v>153980</v>
+      </c>
+      <c r="O105" s="4">
+        <v>154010</v>
+      </c>
+      <c r="P105" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>21</v>
+      </c>
+      <c r="R105" s="4">
+        <v>1</v>
+      </c>
+      <c r="S105" s="4">
+        <v>1</v>
+      </c>
+      <c r="T105" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U105" s="13">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V105" s="14" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W105" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X105" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J94">
+  <conditionalFormatting sqref="J2:J105">
     <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -10584,7 +11976,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U94">
+  <conditionalFormatting sqref="U2:U105">
     <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -10607,7 +11999,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V94">
+  <conditionalFormatting sqref="V2:V105">
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -10633,7 +12025,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D94</xm:sqref>
+          <xm:sqref>D2:D105</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8073647-AD7E-4439-9028-E51DFFB9AC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D384658A-289E-4275-A46F-9E758CBAB810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="66">
   <si>
     <t>Data</t>
   </si>
@@ -444,7 +444,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,10 +494,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -509,7 +518,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="123">
     <dxf>
       <font>
         <b/>
@@ -1476,160 +1485,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2093,50 +1948,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="122" dataDxfId="120" headerRowBorderDxfId="121" tableBorderDxfId="119" totalsRowBorderDxfId="118" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V7" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="117"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="116"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="115"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="114"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="113" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="112" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="111"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="110" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="109"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="108"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="107">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="106" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="105" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="104"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="103"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="102"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="101">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="100" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="99" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="98"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="97"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y105" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36" headerRowCellStyle="Neutro">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y114" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
@@ -2150,8 +2005,8 @@
     <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29" dataCellStyle="Hiperlink"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28" dataCellStyle="Hiperlink"/>
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28"/>
     <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
     <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
@@ -2175,7 +2030,7 @@
     <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14" dataCellStyle="Moeda [0]">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
@@ -2962,7 +2817,7 @@
       <c r="V5" s="5"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="A6" s="8">
         <v>46247</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3030,16 +2885,28 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="9" t="e">
+      <c r="D7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="10">
+        <v>8639.84</v>
+      </c>
+      <c r="F7" s="10">
+        <v>131603.82</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1536</v>
+      </c>
+      <c r="H7" s="9">
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
-        <v>#DIV/0!</v>
+        <v>6.5650373978506094E-2</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -3047,64 +2914,78 @@
         <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
         <v>0</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="9" t="e">
+      <c r="L7" s="10">
+        <v>500</v>
+      </c>
+      <c r="M7" s="9">
         <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+        <v>5.7871442063741924E-2</v>
+      </c>
+      <c r="N7" s="4">
+        <v>194</v>
+      </c>
+      <c r="O7" s="4">
+        <v>31</v>
+      </c>
+      <c r="P7" s="4">
+        <v>31</v>
+      </c>
       <c r="Q7" s="12">
         <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="R7" s="13" t="e">
+      <c r="R7" s="13">
         <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" s="14" t="e">
+        <v>1</v>
+      </c>
+      <c r="S7" s="14" t="str">
         <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="5"/>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" s="4">
+        <v>1</v>
+      </c>
+      <c r="V7" s="5">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H7">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="94" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R7">
-    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="93" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="92" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="91" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="90" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S7">
-    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3113,7 +2994,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3127,7 +3008,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y105"/>
+  <dimension ref="A1:Y114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -11047,11 +10928,11 @@
       <c r="A95" s="8">
         <v>46251</v>
       </c>
-      <c r="B95" s="18">
+      <c r="B95" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C95" s="18">
+      <c r="C95" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11131,11 +11012,11 @@
       <c r="A96" s="8">
         <v>46251</v>
       </c>
-      <c r="B96" s="18">
+      <c r="B96" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C96" s="18">
+      <c r="C96" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11215,11 +11096,11 @@
       <c r="A97" s="8">
         <v>46251</v>
       </c>
-      <c r="B97" s="18">
+      <c r="B97" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C97" s="18">
+      <c r="C97" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11299,11 +11180,11 @@
       <c r="A98" s="8">
         <v>46251</v>
       </c>
-      <c r="B98" s="18">
+      <c r="B98" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C98" s="18">
+      <c r="C98" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11383,11 +11264,11 @@
       <c r="A99" s="8">
         <v>46251</v>
       </c>
-      <c r="B99" s="18">
+      <c r="B99" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C99" s="18">
+      <c r="C99" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11467,11 +11348,11 @@
       <c r="A100" s="8">
         <v>46251</v>
       </c>
-      <c r="B100" s="18">
+      <c r="B100" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C100" s="18">
+      <c r="C100" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11551,11 +11432,11 @@
       <c r="A101" s="8">
         <v>46251</v>
       </c>
-      <c r="B101" s="18">
+      <c r="B101" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C101" s="18">
+      <c r="C101" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11635,11 +11516,11 @@
       <c r="A102" s="8">
         <v>46251</v>
       </c>
-      <c r="B102" s="18">
+      <c r="B102" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C102" s="18">
+      <c r="C102" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11719,11 +11600,11 @@
       <c r="A103" s="8">
         <v>46251</v>
       </c>
-      <c r="B103" s="18">
+      <c r="B103" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C103" s="18">
+      <c r="C103" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11803,11 +11684,11 @@
       <c r="A104" s="8">
         <v>46251</v>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C104" s="18">
+      <c r="C104" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11887,11 +11768,11 @@
       <c r="A105" s="8">
         <v>46251</v>
       </c>
-      <c r="B105" s="18">
+      <c r="B105" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C105" s="18">
+      <c r="C105" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11967,8 +11848,764 @@
         <v>0</v>
       </c>
     </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A106" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B106" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C106" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G106" s="10">
+        <v>5034.3</v>
+      </c>
+      <c r="H106" s="10">
+        <v>94735.22</v>
+      </c>
+      <c r="I106" s="4">
+        <v>638</v>
+      </c>
+      <c r="J106" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.314074322094782E-2</v>
+      </c>
+      <c r="K106" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L106" s="15">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="M106" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="N106" s="4">
+        <v>274288</v>
+      </c>
+      <c r="O106" s="4">
+        <v>274431</v>
+      </c>
+      <c r="P106" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>143</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>162</v>
+      </c>
+      <c r="R106" s="4">
+        <v>10</v>
+      </c>
+      <c r="S106" s="4">
+        <v>10</v>
+      </c>
+      <c r="T106" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U106" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V106" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W106" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X106" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A107" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B107" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C107" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G107" s="10">
+        <v>9312.91</v>
+      </c>
+      <c r="H107" s="10">
+        <v>151403.81</v>
+      </c>
+      <c r="I107" s="4">
+        <v>1578</v>
+      </c>
+      <c r="J107" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1510407168749587E-2</v>
+      </c>
+      <c r="K107" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L107" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M107" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N107" s="4">
+        <v>141515</v>
+      </c>
+      <c r="O107" s="4">
+        <v>141651</v>
+      </c>
+      <c r="P107" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>136</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>97</v>
+      </c>
+      <c r="R107" s="4">
+        <v>26</v>
+      </c>
+      <c r="S107" s="4">
+        <v>26</v>
+      </c>
+      <c r="T107" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U107" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V107" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W107" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X107" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y107" s="5">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A108" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B108" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C108" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G108" s="10">
+        <v>5003.6899999999996</v>
+      </c>
+      <c r="H108" s="10">
+        <v>108954.02</v>
+      </c>
+      <c r="I108" s="4">
+        <v>902</v>
+      </c>
+      <c r="J108" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5924785519616436E-2</v>
+      </c>
+      <c r="K108" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L108" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M108" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N108" s="4">
+        <v>124001</v>
+      </c>
+      <c r="O108" s="4">
+        <v>124044</v>
+      </c>
+      <c r="P108" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q108" s="4">
+        <v>171</v>
+      </c>
+      <c r="R108" s="4">
+        <v>16</v>
+      </c>
+      <c r="S108" s="4">
+        <v>16</v>
+      </c>
+      <c r="T108" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U108" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V108" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W108" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X108" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A109" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B109" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C109" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G109" s="21">
+        <v>6107.34</v>
+      </c>
+      <c r="H109" s="21">
+        <v>220201.19</v>
+      </c>
+      <c r="I109" s="4">
+        <v>619</v>
+      </c>
+      <c r="J109" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.773527245697446E-2</v>
+      </c>
+      <c r="K109" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L109" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M109" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="N109" s="4">
+        <v>290216</v>
+      </c>
+      <c r="O109" s="4">
+        <v>290259</v>
+      </c>
+      <c r="P109" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q109" s="4">
+        <v>263</v>
+      </c>
+      <c r="R109" s="4">
+        <v>6</v>
+      </c>
+      <c r="S109" s="4">
+        <v>6</v>
+      </c>
+      <c r="T109" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U109" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V109" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W109" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X109" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A110" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B110" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C110" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G110" s="21">
+        <v>8968.25</v>
+      </c>
+      <c r="H110" s="21">
+        <v>121071.14</v>
+      </c>
+      <c r="I110" s="4">
+        <v>1152</v>
+      </c>
+      <c r="J110" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4074217852413055E-2</v>
+      </c>
+      <c r="K110" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L110" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M110" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N110" s="4">
+        <v>303081</v>
+      </c>
+      <c r="O110" s="4">
+        <v>303134</v>
+      </c>
+      <c r="P110" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>168</v>
+      </c>
+      <c r="R110" s="4">
+        <v>20</v>
+      </c>
+      <c r="S110" s="4">
+        <v>20</v>
+      </c>
+      <c r="T110" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U110" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V110" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W110" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X110" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A111" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B111" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C111" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G111" s="21">
+        <v>13448.98</v>
+      </c>
+      <c r="H111" s="21">
+        <v>203621.83</v>
+      </c>
+      <c r="I111" s="4">
+        <v>2812</v>
+      </c>
+      <c r="J111" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.6048812153392394E-2</v>
+      </c>
+      <c r="K111" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L111" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M111" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N111" s="4">
+        <v>12296</v>
+      </c>
+      <c r="O111" s="4">
+        <v>12350</v>
+      </c>
+      <c r="P111" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q111" s="4">
+        <v>345</v>
+      </c>
+      <c r="R111" s="4">
+        <v>18</v>
+      </c>
+      <c r="S111" s="4">
+        <v>18</v>
+      </c>
+      <c r="T111" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U111" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V111" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W111" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X111" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y111" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A112" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B112" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C112" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G112" s="21">
+        <v>16015.07</v>
+      </c>
+      <c r="H112" s="21">
+        <v>218177.17</v>
+      </c>
+      <c r="I112" s="4">
+        <v>4279</v>
+      </c>
+      <c r="J112" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.340396797703444E-2</v>
+      </c>
+      <c r="K112" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="L112" s="15">
+        <v>0.71111111111111114</v>
+      </c>
+      <c r="M112" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46111111111111114</v>
+      </c>
+      <c r="N112" s="4">
+        <v>103560</v>
+      </c>
+      <c r="O112" s="4">
+        <v>103696</v>
+      </c>
+      <c r="P112" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>136</v>
+      </c>
+      <c r="Q112" s="4">
+        <v>299</v>
+      </c>
+      <c r="R112" s="4">
+        <v>24</v>
+      </c>
+      <c r="S112" s="4">
+        <v>24</v>
+      </c>
+      <c r="T112" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U112" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V112" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W112" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X112" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y112" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A113" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B113" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C113" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G113" s="21">
+        <v>6269.27</v>
+      </c>
+      <c r="H113" s="21">
+        <v>193795.68</v>
+      </c>
+      <c r="I113" s="4">
+        <v>1326</v>
+      </c>
+      <c r="J113" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2349895518826839E-2</v>
+      </c>
+      <c r="K113" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L113" s="15">
+        <v>0.70972222222222225</v>
+      </c>
+      <c r="M113" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41805555555555557</v>
+      </c>
+      <c r="N113" s="4">
+        <v>118030</v>
+      </c>
+      <c r="O113" s="4">
+        <v>118116</v>
+      </c>
+      <c r="P113" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>86</v>
+      </c>
+      <c r="Q113" s="4">
+        <v>110</v>
+      </c>
+      <c r="R113" s="4">
+        <v>27</v>
+      </c>
+      <c r="S113" s="4">
+        <v>27</v>
+      </c>
+      <c r="T113" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U113" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V113" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W113" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X113" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A114" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B114" s="17">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C114" s="17">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G114" s="21">
+        <v>1959.35</v>
+      </c>
+      <c r="H114" s="21">
+        <v>24688.86</v>
+      </c>
+      <c r="I114" s="4">
+        <v>251</v>
+      </c>
+      <c r="J114" s="18">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.9361704023596061E-2</v>
+      </c>
+      <c r="K114" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L114" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M114" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37499999999999994</v>
+      </c>
+      <c r="N114" s="4">
+        <v>154047</v>
+      </c>
+      <c r="O114" s="4">
+        <v>154091</v>
+      </c>
+      <c r="P114" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>44</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>75</v>
+      </c>
+      <c r="R114" s="4">
+        <v>3</v>
+      </c>
+      <c r="S114" s="4">
+        <v>3</v>
+      </c>
+      <c r="T114" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U114" s="19">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V114" s="20" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W114" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X114" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J105">
+  <conditionalFormatting sqref="J2:J114">
     <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -11976,7 +12613,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U105">
+  <conditionalFormatting sqref="U2:U114">
     <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -11999,7 +12636,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V105">
+  <conditionalFormatting sqref="V2:V114">
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -12025,7 +12662,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D105</xm:sqref>
+          <xm:sqref>D2:D114</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D384658A-289E-4275-A46F-9E758CBAB810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B3D4D4-BBB8-450A-BEA5-807D4E8FE5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="69">
   <si>
     <t>Data</t>
   </si>
@@ -241,6 +241,15 @@
   </si>
   <si>
     <t>Marituba</t>
+  </si>
+  <si>
+    <t>Santa Izabel</t>
+  </si>
+  <si>
+    <t>JVY9G53</t>
+  </si>
+  <si>
+    <t>Pedro</t>
   </si>
 </sst>
 </file>
@@ -444,7 +453,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -494,9 +503,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -509,6 +515,12 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -518,7 +530,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="123">
+  <dxfs count="134">
     <dxf>
       <font>
         <b/>
@@ -597,507 +609,81 @@
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
       <font>
-        <name val="Calibri"/>
+        <b/>
+        <color rgb="FFFF0000"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <name val="Calibri"/>
+        <b/>
+        <color rgb="FF00B050"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
+        <color rgb="FF00B050"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1647,7 +1233,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1699,8 +1284,63 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1733,7 +1373,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1819,24 +1458,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -1852,8 +1474,25 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -1934,6 +1573,456 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1948,94 +2037,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V7" totalsRowShown="0" headerRowDxfId="122" dataDxfId="120" headerRowBorderDxfId="121" tableBorderDxfId="119" totalsRowBorderDxfId="118" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V7" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V8" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="117"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="116"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="115"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="114"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="113" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="112" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="111"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="110" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="109"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="108"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="107">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="106" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="105" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="104"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="103"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="102"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="101">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="100" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="99" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="98"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="97"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="96"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y114" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2464,7 +2553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2952,40 +3041,102 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="10">
+        <v>8971</v>
+      </c>
+      <c r="F8" s="10">
+        <v>79084.990000000005</v>
+      </c>
+      <c r="G8" s="4">
+        <v>808</v>
+      </c>
+      <c r="H8" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>0.11343492614717407</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>500</v>
+      </c>
+      <c r="M8" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>5.5735146583435514E-2</v>
+      </c>
+      <c r="N8" s="4">
+        <v>165</v>
+      </c>
+      <c r="O8" s="4">
+        <v>14</v>
+      </c>
+      <c r="P8" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S8" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H7">
-    <cfRule type="cellIs" dxfId="95" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H8">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R7">
-    <cfRule type="cellIs" dxfId="93" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R8">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S7">
-    <cfRule type="expression" dxfId="86" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S8">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -2994,7 +3145,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3008,7 +3159,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y114"/>
+  <dimension ref="A1:Y127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -11852,11 +12003,11 @@
       <c r="A106" s="8">
         <v>46252</v>
       </c>
-      <c r="B106" s="17">
+      <c r="B106" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C106" s="17">
+      <c r="C106" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11877,7 +12028,7 @@
       <c r="I106" s="4">
         <v>638</v>
       </c>
-      <c r="J106" s="18">
+      <c r="J106" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>5.314074322094782E-2</v>
       </c>
@@ -11914,11 +12065,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U106" s="19">
+      <c r="U106" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V106" s="20" t="str">
+      <c r="V106" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -11936,11 +12087,11 @@
       <c r="A107" s="8">
         <v>46252</v>
       </c>
-      <c r="B107" s="17">
+      <c r="B107" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C107" s="17">
+      <c r="C107" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -11961,7 +12112,7 @@
       <c r="I107" s="4">
         <v>1578</v>
       </c>
-      <c r="J107" s="18">
+      <c r="J107" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.1510407168749587E-2</v>
       </c>
@@ -11998,11 +12149,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U107" s="19">
+      <c r="U107" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V107" s="20" t="str">
+      <c r="V107" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12020,11 +12171,11 @@
       <c r="A108" s="8">
         <v>46252</v>
       </c>
-      <c r="B108" s="17">
+      <c r="B108" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C108" s="17">
+      <c r="C108" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12045,7 +12196,7 @@
       <c r="I108" s="4">
         <v>902</v>
       </c>
-      <c r="J108" s="18">
+      <c r="J108" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>4.5924785519616436E-2</v>
       </c>
@@ -12082,11 +12233,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U108" s="19">
+      <c r="U108" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V108" s="20" t="str">
+      <c r="V108" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12104,11 +12255,11 @@
       <c r="A109" s="8">
         <v>46252</v>
       </c>
-      <c r="B109" s="17">
+      <c r="B109" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C109" s="17">
+      <c r="C109" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12120,16 +12271,16 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
-      <c r="G109" s="21">
+      <c r="G109" s="20">
         <v>6107.34</v>
       </c>
-      <c r="H109" s="21">
+      <c r="H109" s="20">
         <v>220201.19</v>
       </c>
       <c r="I109" s="4">
         <v>619</v>
       </c>
-      <c r="J109" s="18">
+      <c r="J109" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>2.773527245697446E-2</v>
       </c>
@@ -12166,11 +12317,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U109" s="19">
+      <c r="U109" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V109" s="20" t="str">
+      <c r="V109" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12188,11 +12339,11 @@
       <c r="A110" s="8">
         <v>46252</v>
       </c>
-      <c r="B110" s="17">
+      <c r="B110" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C110" s="17">
+      <c r="C110" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12204,16 +12355,16 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
-      <c r="G110" s="21">
+      <c r="G110" s="20">
         <v>8968.25</v>
       </c>
-      <c r="H110" s="21">
+      <c r="H110" s="20">
         <v>121071.14</v>
       </c>
       <c r="I110" s="4">
         <v>1152</v>
       </c>
-      <c r="J110" s="18">
+      <c r="J110" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.4074217852413055E-2</v>
       </c>
@@ -12250,11 +12401,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U110" s="19">
+      <c r="U110" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V110" s="20" t="str">
+      <c r="V110" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12272,11 +12423,11 @@
       <c r="A111" s="8">
         <v>46252</v>
       </c>
-      <c r="B111" s="17">
+      <c r="B111" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C111" s="17">
+      <c r="C111" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12288,16 +12439,16 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
-      <c r="G111" s="21">
+      <c r="G111" s="20">
         <v>13448.98</v>
       </c>
-      <c r="H111" s="21">
+      <c r="H111" s="20">
         <v>203621.83</v>
       </c>
       <c r="I111" s="4">
         <v>2812</v>
       </c>
-      <c r="J111" s="18">
+      <c r="J111" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>6.6048812153392394E-2</v>
       </c>
@@ -12334,11 +12485,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U111" s="19">
+      <c r="U111" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V111" s="20" t="str">
+      <c r="V111" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12356,11 +12507,11 @@
       <c r="A112" s="8">
         <v>46252</v>
       </c>
-      <c r="B112" s="17">
+      <c r="B112" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C112" s="17">
+      <c r="C112" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12372,16 +12523,16 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
-      <c r="G112" s="21">
+      <c r="G112" s="20">
         <v>16015.07</v>
       </c>
-      <c r="H112" s="21">
+      <c r="H112" s="20">
         <v>218177.17</v>
       </c>
       <c r="I112" s="4">
         <v>4279</v>
       </c>
-      <c r="J112" s="18">
+      <c r="J112" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.340396797703444E-2</v>
       </c>
@@ -12418,11 +12569,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U112" s="19">
+      <c r="U112" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V112" s="20" t="str">
+      <c r="V112" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12440,11 +12591,11 @@
       <c r="A113" s="8">
         <v>46252</v>
       </c>
-      <c r="B113" s="17">
+      <c r="B113" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C113" s="17">
+      <c r="C113" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12456,16 +12607,16 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
-      <c r="G113" s="21">
+      <c r="G113" s="20">
         <v>6269.27</v>
       </c>
-      <c r="H113" s="21">
+      <c r="H113" s="20">
         <v>193795.68</v>
       </c>
       <c r="I113" s="4">
         <v>1326</v>
       </c>
-      <c r="J113" s="18">
+      <c r="J113" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>3.2349895518826839E-2</v>
       </c>
@@ -12502,11 +12653,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U113" s="19">
+      <c r="U113" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V113" s="20" t="str">
+      <c r="V113" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12524,11 +12675,11 @@
       <c r="A114" s="8">
         <v>46252</v>
       </c>
-      <c r="B114" s="17">
+      <c r="B114" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C114" s="17">
+      <c r="C114" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12540,16 +12691,16 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
-      <c r="G114" s="21">
+      <c r="G114" s="20">
         <v>1959.35</v>
       </c>
-      <c r="H114" s="21">
+      <c r="H114" s="20">
         <v>24688.86</v>
       </c>
       <c r="I114" s="4">
         <v>251</v>
       </c>
-      <c r="J114" s="18">
+      <c r="J114" s="17">
         <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
         <v>7.9361704023596061E-2</v>
       </c>
@@ -12586,11 +12737,11 @@
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="U114" s="19">
+      <c r="U114" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
         <v>1</v>
       </c>
-      <c r="V114" s="20" t="str">
+      <c r="V114" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
@@ -12604,40 +12755,1132 @@
         <v>0</v>
       </c>
     </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A115" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B115" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C115" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G115" s="20">
+        <v>6952.52</v>
+      </c>
+      <c r="H115" s="20">
+        <v>192915.32</v>
+      </c>
+      <c r="I115" s="4">
+        <v>1241</v>
+      </c>
+      <c r="J115" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.6039232135633398E-2</v>
+      </c>
+      <c r="K115" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L115" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M115" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="N115" s="4">
+        <v>303134</v>
+      </c>
+      <c r="O115" s="4">
+        <v>303230</v>
+      </c>
+      <c r="P115" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>96</v>
+      </c>
+      <c r="Q115" s="4">
+        <v>213</v>
+      </c>
+      <c r="R115" s="4">
+        <v>23</v>
+      </c>
+      <c r="S115" s="4">
+        <v>23</v>
+      </c>
+      <c r="T115" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U115" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V115" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W115" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X115" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A116" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B116" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C116" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G116" s="20">
+        <v>677.17</v>
+      </c>
+      <c r="H116" s="20">
+        <v>22770.12</v>
+      </c>
+      <c r="I116" s="4">
+        <v>39</v>
+      </c>
+      <c r="J116" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.9739412879686185E-2</v>
+      </c>
+      <c r="K116" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L116" s="15">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="M116" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="N116" s="4">
+        <v>454091</v>
+      </c>
+      <c r="O116" s="4">
+        <v>454122</v>
+      </c>
+      <c r="P116" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q116" s="4">
+        <v>15</v>
+      </c>
+      <c r="R116" s="4">
+        <v>1</v>
+      </c>
+      <c r="S116" s="4">
+        <v>1</v>
+      </c>
+      <c r="T116" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U116" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V116" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W116" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X116" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A117" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B117" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C117" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G117" s="20">
+        <v>2289.52</v>
+      </c>
+      <c r="H117" s="10">
+        <v>121897.1</v>
+      </c>
+      <c r="I117" s="4">
+        <v>196</v>
+      </c>
+      <c r="J117" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.8782399253140559E-2</v>
+      </c>
+      <c r="K117" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L117" s="15">
+        <v>0.60972222222222228</v>
+      </c>
+      <c r="M117" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.31805555555555559</v>
+      </c>
+      <c r="N117" s="4">
+        <v>141658</v>
+      </c>
+      <c r="O117" s="4">
+        <v>141687</v>
+      </c>
+      <c r="P117" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>29</v>
+      </c>
+      <c r="Q117" s="4">
+        <v>64</v>
+      </c>
+      <c r="R117" s="4">
+        <v>2</v>
+      </c>
+      <c r="S117" s="4">
+        <v>2</v>
+      </c>
+      <c r="T117" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U117" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V117" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W117" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X117" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A118" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B118" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C118" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G118" s="10">
+        <v>5043.58</v>
+      </c>
+      <c r="H118" s="10">
+        <v>73083.77</v>
+      </c>
+      <c r="I118" s="4">
+        <v>579</v>
+      </c>
+      <c r="J118" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9010944564025636E-2</v>
+      </c>
+      <c r="K118" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L118" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M118" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40277777777777773</v>
+      </c>
+      <c r="N118" s="4">
+        <v>124054</v>
+      </c>
+      <c r="O118" s="4">
+        <v>124126</v>
+      </c>
+      <c r="P118" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>72</v>
+      </c>
+      <c r="Q118" s="4">
+        <v>84</v>
+      </c>
+      <c r="R118" s="4">
+        <v>11</v>
+      </c>
+      <c r="S118" s="4">
+        <v>11</v>
+      </c>
+      <c r="T118" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U118" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V118" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W118" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X118" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A119" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B119" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C119" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G119" s="10">
+        <v>5680.05</v>
+      </c>
+      <c r="H119" s="10">
+        <v>66309.429999999993</v>
+      </c>
+      <c r="I119" s="4">
+        <v>612</v>
+      </c>
+      <c r="J119" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.5659762118299024E-2</v>
+      </c>
+      <c r="K119" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L119" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M119" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N119" s="4">
+        <v>118116</v>
+      </c>
+      <c r="O119" s="4">
+        <v>118171</v>
+      </c>
+      <c r="P119" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q119" s="4">
+        <v>97</v>
+      </c>
+      <c r="R119" s="4">
+        <v>15</v>
+      </c>
+      <c r="S119" s="4">
+        <v>15</v>
+      </c>
+      <c r="T119" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U119" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V119" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W119" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X119" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A120" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B120" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C120" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G120" s="10">
+        <v>5601.85</v>
+      </c>
+      <c r="H120" s="10">
+        <v>85430.56</v>
+      </c>
+      <c r="I120" s="4">
+        <v>429</v>
+      </c>
+      <c r="J120" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5571968625747046E-2</v>
+      </c>
+      <c r="K120" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L120" s="15">
+        <v>0.72986111111111107</v>
+      </c>
+      <c r="M120" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="N120" s="4">
+        <v>274432</v>
+      </c>
+      <c r="O120" s="4">
+        <v>274573</v>
+      </c>
+      <c r="P120" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>141</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>179</v>
+      </c>
+      <c r="R120" s="4">
+        <v>16</v>
+      </c>
+      <c r="S120" s="4">
+        <v>16</v>
+      </c>
+      <c r="T120" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U120" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V120" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W120" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X120" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A121" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B121" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C121" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G121" s="10">
+        <v>34859.64</v>
+      </c>
+      <c r="H121" s="4">
+        <v>798551.77</v>
+      </c>
+      <c r="I121" s="4">
+        <v>7054</v>
+      </c>
+      <c r="J121" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3653575522097955E-2</v>
+      </c>
+      <c r="K121" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L121" s="15">
+        <v>0.72152777777777777</v>
+      </c>
+      <c r="M121" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45069444444444445</v>
+      </c>
+      <c r="N121" s="4">
+        <v>103696</v>
+      </c>
+      <c r="O121" s="4">
+        <v>103825</v>
+      </c>
+      <c r="P121" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>129</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>78</v>
+      </c>
+      <c r="R121" s="4">
+        <v>8</v>
+      </c>
+      <c r="S121" s="4">
+        <v>8</v>
+      </c>
+      <c r="T121" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U121" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V121" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W121" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X121" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A122" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B122" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C122" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G122" s="10">
+        <v>1490.48</v>
+      </c>
+      <c r="H122" s="10">
+        <v>3647.1</v>
+      </c>
+      <c r="I122" s="4">
+        <v>60</v>
+      </c>
+      <c r="J122" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.40867538592306218</v>
+      </c>
+      <c r="K122" s="11">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L122" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M122" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N122" s="4">
+        <v>1129</v>
+      </c>
+      <c r="O122" s="4">
+        <v>1164</v>
+      </c>
+      <c r="P122" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>46</v>
+      </c>
+      <c r="R122" s="4">
+        <v>1</v>
+      </c>
+      <c r="S122" s="4">
+        <v>1</v>
+      </c>
+      <c r="T122" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U122" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V122" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W122" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X122" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A123" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B123" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C123" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Geber</v>
+      </c>
+      <c r="G123" s="10">
+        <v>46053.04</v>
+      </c>
+      <c r="H123" s="10">
+        <v>990964.92</v>
+      </c>
+      <c r="I123" s="4">
+        <v>7519</v>
+      </c>
+      <c r="J123" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.6472926609753246E-2</v>
+      </c>
+      <c r="K123" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L123" s="15">
+        <v>0.75208333333333333</v>
+      </c>
+      <c r="M123" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41875000000000001</v>
+      </c>
+      <c r="N123" s="4">
+        <v>364560</v>
+      </c>
+      <c r="O123" s="4">
+        <v>364587</v>
+      </c>
+      <c r="P123" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>27</v>
+      </c>
+      <c r="Q123" s="4">
+        <v>815</v>
+      </c>
+      <c r="R123" s="4">
+        <v>12</v>
+      </c>
+      <c r="S123" s="4">
+        <v>12</v>
+      </c>
+      <c r="T123" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U123" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V123" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W123" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X123" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y123" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B124" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C124" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G124" s="10">
+        <v>13745.64</v>
+      </c>
+      <c r="H124" s="10">
+        <v>269560.2</v>
+      </c>
+      <c r="I124" s="4">
+        <v>3145</v>
+      </c>
+      <c r="J124" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0992839447366482E-2</v>
+      </c>
+      <c r="K124" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L124" s="15">
+        <v>0.77847222222222223</v>
+      </c>
+      <c r="M124" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48680555555555555</v>
+      </c>
+      <c r="N124" s="4">
+        <v>290259</v>
+      </c>
+      <c r="O124" s="4">
+        <v>290312</v>
+      </c>
+      <c r="P124" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>6</v>
+      </c>
+      <c r="R124" s="4">
+        <v>1</v>
+      </c>
+      <c r="S124" s="4">
+        <v>1</v>
+      </c>
+      <c r="T124" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U124" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V124" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W124" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X124" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B125" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C125" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G125" s="10">
+        <v>1288.17</v>
+      </c>
+      <c r="H125" s="10">
+        <v>30521.66</v>
+      </c>
+      <c r="I125" s="4">
+        <v>225</v>
+      </c>
+      <c r="J125" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2205109420654058E-2</v>
+      </c>
+      <c r="K125" s="11">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L125" s="15">
+        <v>0.82152777777777775</v>
+      </c>
+      <c r="M125" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17569444444444438</v>
+      </c>
+      <c r="N125" s="4">
+        <v>141697</v>
+      </c>
+      <c r="O125" s="4">
+        <v>141737</v>
+      </c>
+      <c r="P125" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q125" s="4">
+        <v>52</v>
+      </c>
+      <c r="R125" s="4">
+        <v>5</v>
+      </c>
+      <c r="S125" s="4">
+        <v>5</v>
+      </c>
+      <c r="T125" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U125" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V125" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W125" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X125" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y125" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A126" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B126" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C126" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G126" s="10">
+        <v>5348.55</v>
+      </c>
+      <c r="H126" s="10">
+        <v>100934.61</v>
+      </c>
+      <c r="I126" s="4">
+        <v>1593</v>
+      </c>
+      <c r="J126" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2990247844619406E-2</v>
+      </c>
+      <c r="K126" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L126" s="15">
+        <v>0.74097222222222225</v>
+      </c>
+      <c r="M126" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44930555555555557</v>
+      </c>
+      <c r="N126" s="4">
+        <v>12350</v>
+      </c>
+      <c r="O126" s="4">
+        <v>12400</v>
+      </c>
+      <c r="P126" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>314</v>
+      </c>
+      <c r="R126" s="4">
+        <v>13</v>
+      </c>
+      <c r="S126" s="4">
+        <v>13</v>
+      </c>
+      <c r="T126" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U126" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V126" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W126" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X126" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y126" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A127" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B127" s="21">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C127" s="21">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G127" s="10">
+        <v>1669.34</v>
+      </c>
+      <c r="H127" s="4">
+        <v>38591.550000000003</v>
+      </c>
+      <c r="I127" s="4">
+        <v>297</v>
+      </c>
+      <c r="J127" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3256619648601828E-2</v>
+      </c>
+      <c r="K127" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L127" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M127" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17708333333333326</v>
+      </c>
+      <c r="N127" s="4">
+        <v>454122</v>
+      </c>
+      <c r="O127" s="4">
+        <v>454209</v>
+      </c>
+      <c r="P127" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>87</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>45</v>
+      </c>
+      <c r="R127" s="4">
+        <v>1</v>
+      </c>
+      <c r="S127" s="4">
+        <v>1</v>
+      </c>
+      <c r="T127" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U127" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V127" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W127" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X127" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y127" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J114">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J127">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U114">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U127">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V114">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V127">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -12646,7 +13889,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12662,7 +13905,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D114</xm:sqref>
+          <xm:sqref>D2:D127</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B3D4D4-BBB8-450A-BEA5-807D4E8FE5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F9B2DC-5A4F-44D4-B2E9-086BD89E2BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -453,7 +453,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -515,9 +515,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -530,392 +527,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b/>
@@ -2037,94 +1649,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V8" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3042,7 +2654,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="A8" s="21">
         <v>46253</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -3105,38 +2717,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H8">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R8">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S8">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3145,7 +2757,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12759,11 +12371,11 @@
       <c r="A115" s="8">
         <v>46253</v>
       </c>
-      <c r="B115" s="21">
+      <c r="B115" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C115" s="21">
+      <c r="C115" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12843,11 +12455,11 @@
       <c r="A116" s="8">
         <v>46253</v>
       </c>
-      <c r="B116" s="21">
+      <c r="B116" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C116" s="21">
+      <c r="C116" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -12927,11 +12539,11 @@
       <c r="A117" s="8">
         <v>46253</v>
       </c>
-      <c r="B117" s="21">
+      <c r="B117" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C117" s="21">
+      <c r="C117" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13011,11 +12623,11 @@
       <c r="A118" s="8">
         <v>46253</v>
       </c>
-      <c r="B118" s="21">
+      <c r="B118" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C118" s="21">
+      <c r="C118" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13095,11 +12707,11 @@
       <c r="A119" s="8">
         <v>46253</v>
       </c>
-      <c r="B119" s="21">
+      <c r="B119" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C119" s="21">
+      <c r="C119" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13179,11 +12791,11 @@
       <c r="A120" s="8">
         <v>46253</v>
       </c>
-      <c r="B120" s="21">
+      <c r="B120" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C120" s="21">
+      <c r="C120" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13263,11 +12875,11 @@
       <c r="A121" s="8">
         <v>46253</v>
       </c>
-      <c r="B121" s="21">
+      <c r="B121" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C121" s="21">
+      <c r="C121" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13347,11 +12959,11 @@
       <c r="A122" s="8">
         <v>46253</v>
       </c>
-      <c r="B122" s="21">
+      <c r="B122" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C122" s="21">
+      <c r="C122" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13431,11 +13043,11 @@
       <c r="A123" s="8">
         <v>46253</v>
       </c>
-      <c r="B123" s="21">
+      <c r="B123" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C123" s="21">
+      <c r="C123" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13515,11 +13127,11 @@
       <c r="A124" s="8">
         <v>46253</v>
       </c>
-      <c r="B124" s="21">
+      <c r="B124" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C124" s="21">
+      <c r="C124" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13599,11 +13211,11 @@
       <c r="A125" s="8">
         <v>46253</v>
       </c>
-      <c r="B125" s="21">
+      <c r="B125" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C125" s="21">
+      <c r="C125" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13683,11 +13295,11 @@
       <c r="A126" s="8">
         <v>46253</v>
       </c>
-      <c r="B126" s="21">
+      <c r="B126" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C126" s="21">
+      <c r="C126" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13760,18 +13372,18 @@
         <v>2</v>
       </c>
       <c r="Y126" s="5">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <v>46253</v>
       </c>
-      <c r="B127" s="21">
+      <c r="B127" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C127" s="21">
+      <c r="C127" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -13849,38 +13461,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J127">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U127">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V127">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -13889,7 +13501,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\saidas_bel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F9B2DC-5A4F-44D4-B2E9-086BD89E2BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579DD06C-AC66-47DE-8C2D-CABEC6707E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -13351,19 +13351,19 @@
         <v>13</v>
       </c>
       <c r="S126" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T126" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U126" s="18">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>1</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="V126" s="19" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>Atendeu a Meta</v>
+        <v>Não Atendeu a Meta</v>
       </c>
       <c r="W126" s="4" t="s">
         <v>40</v>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\saidas_bel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579DD06C-AC66-47DE-8C2D-CABEC6707E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A730D91-EAC2-4BB9-AAEC-BA0D8AAECEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="71">
   <si>
     <t>Data</t>
   </si>
@@ -251,6 +251,12 @@
   <si>
     <t>Pedro</t>
   </si>
+  <si>
+    <t>10,13,5</t>
+  </si>
+  <si>
+    <t>belk</t>
+  </si>
 </sst>
 </file>
 
@@ -453,7 +459,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -518,6 +524,9 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -527,7 +536,392 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="134">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1649,94 +2043,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V8" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y148" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2717,38 +3111,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H8">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R8">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S8">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -2757,7 +3151,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2771,7 +3165,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y127"/>
+  <dimension ref="A1:Y148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -13398,7 +13792,7 @@
       <c r="G127" s="10">
         <v>1669.34</v>
       </c>
-      <c r="H127" s="4">
+      <c r="H127" s="10">
         <v>38591.550000000003</v>
       </c>
       <c r="I127" s="4">
@@ -13459,40 +13853,1804 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A128" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B128" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C128" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G128" s="10">
+        <v>2199.7600000000002</v>
+      </c>
+      <c r="H128" s="10">
+        <v>59957.51</v>
+      </c>
+      <c r="I128" s="4">
+        <v>359</v>
+      </c>
+      <c r="J128" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.6688648344469277E-2</v>
+      </c>
+      <c r="K128" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L128" s="15">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="M128" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15277777777777773</v>
+      </c>
+      <c r="N128" s="4">
+        <v>274573</v>
+      </c>
+      <c r="O128" s="4">
+        <v>274603</v>
+      </c>
+      <c r="P128" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>129</v>
+      </c>
+      <c r="R128" s="4">
+        <v>3</v>
+      </c>
+      <c r="S128" s="4">
+        <v>3</v>
+      </c>
+      <c r="T128" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U128" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V128" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W128" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X128" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A129" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B129" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C129" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G129" s="10">
+        <v>8081.76</v>
+      </c>
+      <c r="H129" s="10">
+        <v>383207.29</v>
+      </c>
+      <c r="I129" s="4">
+        <v>979</v>
+      </c>
+      <c r="J129" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.1089786679162604E-2</v>
+      </c>
+      <c r="K129" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L129" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M129" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37499999999999994</v>
+      </c>
+      <c r="N129" s="4">
+        <v>124126</v>
+      </c>
+      <c r="O129" s="4">
+        <v>124163</v>
+      </c>
+      <c r="P129" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>220</v>
+      </c>
+      <c r="R129" s="4">
+        <v>12</v>
+      </c>
+      <c r="S129" s="4">
+        <v>12</v>
+      </c>
+      <c r="T129" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U129" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V129" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W129" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X129" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y129" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A130" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B130" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C130" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G130" s="10">
+        <v>6967.71</v>
+      </c>
+      <c r="H130" s="10">
+        <v>158751.57</v>
+      </c>
+      <c r="I130" s="4">
+        <v>905</v>
+      </c>
+      <c r="J130" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3890652545987417E-2</v>
+      </c>
+      <c r="K130" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L130" s="15">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="M130" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="N130" s="4">
+        <v>303230</v>
+      </c>
+      <c r="O130" s="4">
+        <v>303285</v>
+      </c>
+      <c r="P130" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q130" s="4">
+        <v>218</v>
+      </c>
+      <c r="R130" s="4">
+        <v>18</v>
+      </c>
+      <c r="S130" s="4">
+        <v>18</v>
+      </c>
+      <c r="T130" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U130" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V130" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W130" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X130" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y130" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A131" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B131" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C131" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G131" s="10">
+        <v>7544.35</v>
+      </c>
+      <c r="H131" s="10">
+        <v>136955.37</v>
+      </c>
+      <c r="I131" s="4">
+        <v>823</v>
+      </c>
+      <c r="J131" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5086193407385201E-2</v>
+      </c>
+      <c r="K131" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L131" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M131" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="N131" s="4">
+        <v>103835</v>
+      </c>
+      <c r="O131" s="4">
+        <v>103967</v>
+      </c>
+      <c r="P131" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>132</v>
+      </c>
+      <c r="Q131" s="4">
+        <v>194</v>
+      </c>
+      <c r="R131" s="4">
+        <v>28</v>
+      </c>
+      <c r="S131" s="4">
+        <v>28</v>
+      </c>
+      <c r="T131" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U131" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V131" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W131" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X131" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A132" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B132" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C132" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G132" s="10">
+        <v>6276.2</v>
+      </c>
+      <c r="H132" s="10">
+        <v>154985.65</v>
+      </c>
+      <c r="I132" s="4">
+        <v>735</v>
+      </c>
+      <c r="J132" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0495361989964875E-2</v>
+      </c>
+      <c r="K132" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L132" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M132" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="N132" s="4">
+        <v>141738</v>
+      </c>
+      <c r="O132" s="4">
+        <v>141799</v>
+      </c>
+      <c r="P132" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>61</v>
+      </c>
+      <c r="Q132" s="4">
+        <v>263</v>
+      </c>
+      <c r="R132" s="4">
+        <v>24</v>
+      </c>
+      <c r="S132" s="4">
+        <v>24</v>
+      </c>
+      <c r="T132" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U132" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V132" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W132" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X132" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y132" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A133" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B133" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C133" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G133" s="10">
+        <v>4199.3599999999997</v>
+      </c>
+      <c r="H133" s="10">
+        <v>56016.05</v>
+      </c>
+      <c r="I133" s="4">
+        <v>583</v>
+      </c>
+      <c r="J133" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4967085326437685E-2</v>
+      </c>
+      <c r="K133" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L133" s="15">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="M133" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="N133" s="4">
+        <v>154209</v>
+      </c>
+      <c r="O133" s="4">
+        <v>154259</v>
+      </c>
+      <c r="P133" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q133" s="4">
+        <v>100</v>
+      </c>
+      <c r="R133" s="4">
+        <v>16</v>
+      </c>
+      <c r="S133" s="4">
+        <v>16</v>
+      </c>
+      <c r="T133" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U133" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V133" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W133" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X133" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y133" s="5">
+        <v>42.21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A134" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B134" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C134" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G134" s="10">
+        <v>9400.0400000000009</v>
+      </c>
+      <c r="H134" s="10">
+        <v>133865.57</v>
+      </c>
+      <c r="I134" s="4">
+        <v>1514</v>
+      </c>
+      <c r="J134" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.0219997569203191E-2</v>
+      </c>
+      <c r="K134" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L134" s="15">
+        <v>0.81319444444444444</v>
+      </c>
+      <c r="M134" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="N134" s="4">
+        <v>290312</v>
+      </c>
+      <c r="O134" s="4">
+        <v>290462</v>
+      </c>
+      <c r="P134" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>150</v>
+      </c>
+      <c r="Q134" s="4">
+        <v>166</v>
+      </c>
+      <c r="R134" s="4">
+        <v>19</v>
+      </c>
+      <c r="S134" s="4">
+        <v>14</v>
+      </c>
+      <c r="T134" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>5</v>
+      </c>
+      <c r="U134" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="V134" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W134" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X134" s="4">
+        <v>7</v>
+      </c>
+      <c r="Y134" s="5">
+        <v>38.130000000000003</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A135" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B135" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C135" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G135" s="10">
+        <v>7997.22</v>
+      </c>
+      <c r="H135" s="10">
+        <v>164530.65</v>
+      </c>
+      <c r="I135" s="4">
+        <v>1132</v>
+      </c>
+      <c r="J135" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8606262723693124E-2</v>
+      </c>
+      <c r="K135" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L135" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M135" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="N135" s="4">
+        <v>118171</v>
+      </c>
+      <c r="O135" s="4">
+        <v>118237</v>
+      </c>
+      <c r="P135" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q135" s="4">
+        <v>97</v>
+      </c>
+      <c r="R135" s="4">
+        <v>17</v>
+      </c>
+      <c r="S135" s="4">
+        <v>14</v>
+      </c>
+      <c r="T135" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>3</v>
+      </c>
+      <c r="U135" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="V135" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W135" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X135" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y135" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A136" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B136" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C136" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G136" s="10">
+        <v>7069.92</v>
+      </c>
+      <c r="H136" s="10">
+        <v>137083.25</v>
+      </c>
+      <c r="I136" s="4">
+        <v>1045</v>
+      </c>
+      <c r="J136" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.1573915850404772E-2</v>
+      </c>
+      <c r="K136" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L136" s="15">
+        <v>0.76180555555555551</v>
+      </c>
+      <c r="M136" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47013888888888883</v>
+      </c>
+      <c r="N136" s="4">
+        <v>12400</v>
+      </c>
+      <c r="O136" s="4">
+        <v>12456</v>
+      </c>
+      <c r="P136" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q136" s="4">
+        <v>217</v>
+      </c>
+      <c r="R136" s="4">
+        <v>29</v>
+      </c>
+      <c r="S136" s="4">
+        <v>29</v>
+      </c>
+      <c r="T136" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U136" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V136" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W136" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X136" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y136" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A137" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B137" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C137" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G137" s="10">
+        <v>2627.47</v>
+      </c>
+      <c r="H137" s="10">
+        <v>57743.38</v>
+      </c>
+      <c r="I137" s="4">
+        <v>446</v>
+      </c>
+      <c r="J137" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5502532065147552E-2</v>
+      </c>
+      <c r="K137" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="15">
+        <v>0.69374999999999998</v>
+      </c>
+      <c r="M137" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.19374999999999998</v>
+      </c>
+      <c r="N137" s="4">
+        <v>274600</v>
+      </c>
+      <c r="O137" s="4">
+        <v>274652</v>
+      </c>
+      <c r="P137" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q137" s="4">
+        <v>128</v>
+      </c>
+      <c r="R137" s="4">
+        <v>11</v>
+      </c>
+      <c r="S137" s="4">
+        <v>11</v>
+      </c>
+      <c r="T137" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U137" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V137" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W137" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X137" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A138" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B138" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C138" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G138" s="10">
+        <v>30511.18</v>
+      </c>
+      <c r="H138" s="10">
+        <v>631200.38</v>
+      </c>
+      <c r="I138" s="4">
+        <v>4591</v>
+      </c>
+      <c r="J138" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8338342255117149E-2</v>
+      </c>
+      <c r="K138" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L138" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="M138" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="N138" s="4">
+        <v>103967</v>
+      </c>
+      <c r="O138" s="4">
+        <v>104102</v>
+      </c>
+      <c r="P138" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>135</v>
+      </c>
+      <c r="Q138" s="4">
+        <v>110</v>
+      </c>
+      <c r="R138" s="4">
+        <v>24</v>
+      </c>
+      <c r="S138" s="4">
+        <v>24</v>
+      </c>
+      <c r="T138" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U138" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V138" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W138" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X138" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y138" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A139" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B139" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C139" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G139" s="10">
+        <v>3043.17</v>
+      </c>
+      <c r="H139" s="10">
+        <v>63774.15</v>
+      </c>
+      <c r="I139" s="4">
+        <v>323</v>
+      </c>
+      <c r="J139" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.7717923327868735E-2</v>
+      </c>
+      <c r="K139" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L139" s="15">
+        <v>0.66180555555555554</v>
+      </c>
+      <c r="M139" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37013888888888885</v>
+      </c>
+      <c r="N139" s="4">
+        <v>12456</v>
+      </c>
+      <c r="O139" s="4">
+        <v>12522</v>
+      </c>
+      <c r="P139" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q139" s="4">
+        <v>66</v>
+      </c>
+      <c r="R139" s="4">
+        <v>12</v>
+      </c>
+      <c r="S139" s="4">
+        <v>12</v>
+      </c>
+      <c r="T139" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U139" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V139" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W139" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X139" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y139" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A140" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B140" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C140" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G140" s="10">
+        <v>1644.73</v>
+      </c>
+      <c r="H140" s="10">
+        <v>61111.38</v>
+      </c>
+      <c r="I140" s="4">
+        <v>276</v>
+      </c>
+      <c r="J140" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.6913645216324687E-2</v>
+      </c>
+      <c r="K140" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L140" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="M140" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N140" s="4">
+        <v>274652</v>
+      </c>
+      <c r="O140" s="4">
+        <v>274700</v>
+      </c>
+      <c r="P140" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q140" s="4">
+        <v>56</v>
+      </c>
+      <c r="R140" s="4">
+        <v>3</v>
+      </c>
+      <c r="S140" s="4">
+        <v>3</v>
+      </c>
+      <c r="T140" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U140" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V140" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W140" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X140" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y140" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B141" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C141" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G141" s="10">
+        <v>5634.34</v>
+      </c>
+      <c r="H141" s="10">
+        <v>145684.98000000001</v>
+      </c>
+      <c r="I141" s="4">
+        <v>1005</v>
+      </c>
+      <c r="J141" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8674817403962988E-2</v>
+      </c>
+      <c r="K141" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L141" s="15">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="M141" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42083333333333334</v>
+      </c>
+      <c r="N141" s="4">
+        <v>118237</v>
+      </c>
+      <c r="O141" s="4">
+        <v>118332</v>
+      </c>
+      <c r="P141" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>95</v>
+      </c>
+      <c r="Q141" s="4">
+        <v>221</v>
+      </c>
+      <c r="R141" s="4">
+        <v>27</v>
+      </c>
+      <c r="S141" s="4">
+        <v>27</v>
+      </c>
+      <c r="T141" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U141" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V141" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W141" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X141" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y141" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A142" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B142" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C142" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G142" s="10">
+        <v>18367.5</v>
+      </c>
+      <c r="H142" s="10">
+        <v>285918.33</v>
+      </c>
+      <c r="I142" s="4">
+        <v>4968</v>
+      </c>
+      <c r="J142" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4240372416836652E-2</v>
+      </c>
+      <c r="K142" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L142" s="15">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="M142" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52777777777777768</v>
+      </c>
+      <c r="N142" s="4">
+        <v>141799</v>
+      </c>
+      <c r="O142" s="4">
+        <v>141859</v>
+      </c>
+      <c r="P142" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>60</v>
+      </c>
+      <c r="Q142" s="4">
+        <v>773</v>
+      </c>
+      <c r="R142" s="4">
+        <v>30</v>
+      </c>
+      <c r="S142" s="4">
+        <v>25</v>
+      </c>
+      <c r="T142" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>5</v>
+      </c>
+      <c r="U142" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="V142" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W142" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X142" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y142" s="5">
+        <v>9.1300000000000008</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A143" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B143" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C143" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G143" s="10">
+        <v>3355.34</v>
+      </c>
+      <c r="H143" s="10">
+        <v>45519.69</v>
+      </c>
+      <c r="I143" s="4">
+        <v>401</v>
+      </c>
+      <c r="J143" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3711837668490279E-2</v>
+      </c>
+      <c r="K143" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L143" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M143" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222215</v>
+      </c>
+      <c r="N143" s="4">
+        <v>279486</v>
+      </c>
+      <c r="O143" s="4">
+        <v>279543</v>
+      </c>
+      <c r="P143" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>57</v>
+      </c>
+      <c r="Q143" s="4">
+        <v>73</v>
+      </c>
+      <c r="R143" s="4">
+        <v>8</v>
+      </c>
+      <c r="S143" s="4">
+        <v>8</v>
+      </c>
+      <c r="T143" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U143" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V143" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W143" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X143" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y143" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A144" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B144" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C144" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G144" s="10">
+        <v>12213.47</v>
+      </c>
+      <c r="H144" s="10">
+        <v>219930.64</v>
+      </c>
+      <c r="I144" s="4">
+        <v>3470</v>
+      </c>
+      <c r="J144" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.553328085618265E-2</v>
+      </c>
+      <c r="K144" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L144" s="15">
+        <v>0.75069444444444444</v>
+      </c>
+      <c r="M144" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="N144" s="4">
+        <v>303285</v>
+      </c>
+      <c r="O144" s="4">
+        <v>303335</v>
+      </c>
+      <c r="P144" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q144" s="4">
+        <v>285</v>
+      </c>
+      <c r="R144" s="4">
+        <v>12</v>
+      </c>
+      <c r="S144" s="4">
+        <v>12</v>
+      </c>
+      <c r="T144" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U144" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V144" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W144" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X144" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B145" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C145" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G145" s="10">
+        <v>1386.09</v>
+      </c>
+      <c r="H145" s="10">
+        <v>40934.400000000001</v>
+      </c>
+      <c r="I145" s="4">
+        <v>61</v>
+      </c>
+      <c r="J145" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3861251172607874E-2</v>
+      </c>
+      <c r="K145" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L145" s="15">
+        <v>0.79722222222222228</v>
+      </c>
+      <c r="M145" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="N145" s="4">
+        <v>154259</v>
+      </c>
+      <c r="O145" s="4">
+        <v>154300</v>
+      </c>
+      <c r="P145" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>41</v>
+      </c>
+      <c r="Q145" s="4">
+        <v>64</v>
+      </c>
+      <c r="R145" s="4">
+        <v>2</v>
+      </c>
+      <c r="S145" s="4">
+        <v>2</v>
+      </c>
+      <c r="T145" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U145" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V145" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W145" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X145" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y145" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B146" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C146" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G146" s="10">
+        <v>11238.27</v>
+      </c>
+      <c r="H146" s="10">
+        <v>184739.8</v>
+      </c>
+      <c r="I146" s="4">
+        <v>2061</v>
+      </c>
+      <c r="J146" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0832966150228596E-2</v>
+      </c>
+      <c r="K146" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L146" s="15">
+        <v>0.76875000000000004</v>
+      </c>
+      <c r="M146" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="N146" s="4">
+        <v>124163</v>
+      </c>
+      <c r="O146" s="4">
+        <v>124246</v>
+      </c>
+      <c r="P146" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>83</v>
+      </c>
+      <c r="Q146" s="4">
+        <v>266</v>
+      </c>
+      <c r="R146" s="4">
+        <v>31</v>
+      </c>
+      <c r="S146" s="4">
+        <v>30</v>
+      </c>
+      <c r="T146" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U146" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="V146" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W146" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X146" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y146" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A147" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B147" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C147" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G147" s="10">
+        <v>1528.87</v>
+      </c>
+      <c r="H147" s="10">
+        <v>13798.57</v>
+      </c>
+      <c r="I147" s="4">
+        <v>310</v>
+      </c>
+      <c r="J147" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11079916252191349</v>
+      </c>
+      <c r="K147" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L147" s="15">
+        <v>0.73263888888888884</v>
+      </c>
+      <c r="M147" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44097222222222215</v>
+      </c>
+      <c r="N147" s="4">
+        <v>274652</v>
+      </c>
+      <c r="O147" s="4">
+        <v>274736</v>
+      </c>
+      <c r="P147" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>84</v>
+      </c>
+      <c r="Q147" s="4">
+        <v>50</v>
+      </c>
+      <c r="R147" s="4">
+        <v>2</v>
+      </c>
+      <c r="S147" s="4">
+        <v>2</v>
+      </c>
+      <c r="T147" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U147" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V147" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W147" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="X147" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A148" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B148" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C148" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G148" s="10">
+        <v>8121.49</v>
+      </c>
+      <c r="H148" s="10">
+        <v>159899.17000000001</v>
+      </c>
+      <c r="I148" s="4">
+        <v>1284</v>
+      </c>
+      <c r="J148" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0791320555322449E-2</v>
+      </c>
+      <c r="K148" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L148" s="15">
+        <v>0.59375</v>
+      </c>
+      <c r="M148" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="N148" s="4">
+        <v>274736</v>
+      </c>
+      <c r="O148" s="4">
+        <v>274865</v>
+      </c>
+      <c r="P148" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>129</v>
+      </c>
+      <c r="Q148" s="4">
+        <v>178</v>
+      </c>
+      <c r="R148" s="4">
+        <v>20</v>
+      </c>
+      <c r="S148" s="4">
+        <v>20</v>
+      </c>
+      <c r="T148" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U148" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V148" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W148" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X148" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y148" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J127">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J148">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U127">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U148">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V127">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V148">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -13501,7 +15659,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13517,7 +15675,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D127</xm:sqref>
+          <xm:sqref>D2:D148</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A730D91-EAC2-4BB9-AAEC-BA0D8AAECEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF29CE5-7E2C-4AFD-B2BE-771A2BCCA6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="72">
   <si>
     <t>Data</t>
   </si>
@@ -255,7 +255,10 @@
     <t>10,13,5</t>
   </si>
   <si>
-    <t>belk</t>
+    <t>13,13,13,13,13</t>
+  </si>
+  <si>
+    <t>13,13,13</t>
   </si>
 </sst>
 </file>
@@ -459,7 +462,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -524,9 +527,6 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -536,392 +536,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b/>
@@ -2043,94 +1658,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V8" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y148" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y158" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3111,38 +2726,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H8">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R8">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S8">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3151,7 +2766,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3165,7 +2780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y148"/>
+  <dimension ref="A1:Y158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -4505,25 +4120,25 @@
         <v>19</v>
       </c>
       <c r="S16" s="4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T16" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U16" s="13">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.89473684210526316</v>
+        <v>1</v>
       </c>
       <c r="V16" s="14" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>Não Atendeu a Meta</v>
+        <v>Atendeu a Meta</v>
       </c>
       <c r="W16" s="4" t="s">
         <v>40</v>
       </c>
       <c r="X16" s="4">
-        <v>179020.48859299999</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="5">
         <v>10</v>
@@ -5867,7 +5482,7 @@
         <v>42</v>
       </c>
       <c r="X32" s="4">
-        <v>113913</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="5">
         <v>0</v>
@@ -6353,19 +5968,19 @@
         <v>11</v>
       </c>
       <c r="S38" s="4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" s="13">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.90909090909090906</v>
+        <v>1</v>
       </c>
       <c r="V38" s="14" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>Não Atendeu a Meta</v>
+        <v>Atendeu a Meta</v>
       </c>
       <c r="W38" s="4" t="s">
         <v>45</v>
@@ -6689,15 +6304,15 @@
         <v>25</v>
       </c>
       <c r="S42" s="4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T42" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42" s="13">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="V42" s="14" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
@@ -7109,19 +6724,19 @@
         <v>11</v>
       </c>
       <c r="S47" s="4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T47" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U47" s="13">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.81818181818181823</v>
+        <v>1</v>
       </c>
       <c r="V47" s="14" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>Não Atendeu a Meta</v>
+        <v>Atendeu a Meta</v>
       </c>
       <c r="W47" s="4" t="s">
         <v>45</v>
@@ -7361,19 +6976,19 @@
         <v>23</v>
       </c>
       <c r="S50" s="4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T50" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U50" s="13">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.91304347826086951</v>
+        <v>1</v>
       </c>
       <c r="V50" s="14" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>Não Atendeu a Meta</v>
+        <v>Atendeu a Meta</v>
       </c>
       <c r="W50" s="4" t="s">
         <v>40</v>
@@ -8389,8 +8004,8 @@
       <c r="X62" s="4">
         <v>3</v>
       </c>
-      <c r="Y62" s="5">
-        <v>13</v>
+      <c r="Y62" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
@@ -8453,15 +8068,15 @@
         <v>37</v>
       </c>
       <c r="S63" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T63" s="12">
         <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U63" s="13">
         <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
-        <v>0.97297297297297303</v>
+        <v>1</v>
       </c>
       <c r="V63" s="14" t="str">
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
@@ -10489,8 +10104,8 @@
       <c r="X87" s="4">
         <v>3</v>
       </c>
-      <c r="Y87" s="5">
-        <v>13</v>
+      <c r="Y87" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.25">
@@ -14437,8 +14052,8 @@
       <c r="X134" s="4">
         <v>7</v>
       </c>
-      <c r="Y134" s="5">
-        <v>38.130000000000003</v>
+      <c r="Y134" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.25">
@@ -14521,8 +14136,8 @@
       <c r="X135" s="4">
         <v>3</v>
       </c>
-      <c r="Y135" s="5">
-        <v>13</v>
+      <c r="Y135" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.25">
@@ -14781,11 +14396,11 @@
       <c r="A139" s="8">
         <v>46255</v>
       </c>
-      <c r="B139" s="22">
+      <c r="B139" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C139" s="22">
+      <c r="C139" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -14865,11 +14480,11 @@
       <c r="A140" s="8">
         <v>46255</v>
       </c>
-      <c r="B140" s="22">
+      <c r="B140" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C140" s="22">
+      <c r="C140" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -14949,11 +14564,11 @@
       <c r="A141" s="8">
         <v>46255</v>
       </c>
-      <c r="B141" s="22">
+      <c r="B141" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C141" s="22">
+      <c r="C141" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15033,11 +14648,11 @@
       <c r="A142" s="8">
         <v>46255</v>
       </c>
-      <c r="B142" s="22">
+      <c r="B142" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C142" s="22">
+      <c r="C142" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15107,21 +14722,21 @@
         <v>45</v>
       </c>
       <c r="X142" s="4">
-        <v>6</v>
-      </c>
-      <c r="Y142" s="5">
-        <v>9.1300000000000008</v>
+        <v>5</v>
+      </c>
+      <c r="Y142" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <v>46255</v>
       </c>
-      <c r="B143" s="22">
+      <c r="B143" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C143" s="22">
+      <c r="C143" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15201,11 +14816,11 @@
       <c r="A144" s="8">
         <v>46255</v>
       </c>
-      <c r="B144" s="22">
+      <c r="B144" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C144" s="22">
+      <c r="C144" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15271,7 +14886,7 @@
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
-      <c r="W144" s="4" t="s">
+      <c r="W144" s="10" t="s">
         <v>40</v>
       </c>
       <c r="X144" s="4">
@@ -15285,11 +14900,11 @@
       <c r="A145" s="8">
         <v>46255</v>
       </c>
-      <c r="B145" s="22">
+      <c r="B145" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C145" s="22">
+      <c r="C145" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15369,11 +14984,11 @@
       <c r="A146" s="8">
         <v>46255</v>
       </c>
-      <c r="B146" s="22">
+      <c r="B146" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C146" s="22">
+      <c r="C146" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15453,11 +15068,11 @@
       <c r="A147" s="8">
         <v>46255</v>
       </c>
-      <c r="B147" s="22">
+      <c r="B147" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C147" s="22">
+      <c r="C147" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15523,8 +15138,8 @@
         <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
         <v>Atendeu a Meta</v>
       </c>
-      <c r="W147" s="4" t="s">
-        <v>70</v>
+      <c r="W147" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="X147" s="4">
         <v>0</v>
@@ -15537,11 +15152,11 @@
       <c r="A148" s="8">
         <v>46256</v>
       </c>
-      <c r="B148" s="22">
+      <c r="B148" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C148" s="22">
+      <c r="C148" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -15617,40 +15232,880 @@
         <v>0</v>
       </c>
     </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A149" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B149" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C149" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G149" s="10">
+        <v>1417.19</v>
+      </c>
+      <c r="H149" s="10">
+        <v>68719.899999999994</v>
+      </c>
+      <c r="I149" s="4">
+        <v>94</v>
+      </c>
+      <c r="J149" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.0622701721044415E-2</v>
+      </c>
+      <c r="K149" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L149" s="15">
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="M149" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.34583333333333327</v>
+      </c>
+      <c r="N149" s="4">
+        <v>274865</v>
+      </c>
+      <c r="O149" s="4">
+        <v>274901</v>
+      </c>
+      <c r="P149" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q149" s="4">
+        <v>2</v>
+      </c>
+      <c r="R149" s="4">
+        <v>2</v>
+      </c>
+      <c r="S149" s="4">
+        <v>2</v>
+      </c>
+      <c r="T149" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U149" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V149" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W149" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X149" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y149" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A150" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B150" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C150" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G150" s="10">
+        <v>13874.37</v>
+      </c>
+      <c r="H150" s="10">
+        <v>302315.42</v>
+      </c>
+      <c r="I150" s="4">
+        <v>2846</v>
+      </c>
+      <c r="J150" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5893689445282021E-2</v>
+      </c>
+      <c r="K150" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L150" s="15">
+        <v>0.7993055555555556</v>
+      </c>
+      <c r="M150" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50763888888888897</v>
+      </c>
+      <c r="N150" s="4">
+        <v>279544</v>
+      </c>
+      <c r="O150" s="4">
+        <v>279628</v>
+      </c>
+      <c r="P150" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>84</v>
+      </c>
+      <c r="Q150" s="4">
+        <v>441</v>
+      </c>
+      <c r="R150" s="4">
+        <v>49</v>
+      </c>
+      <c r="S150" s="4">
+        <v>49</v>
+      </c>
+      <c r="T150" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U150" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V150" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W150" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X150" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y150" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A151" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B151" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C151" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G151" s="10">
+        <v>12498.44</v>
+      </c>
+      <c r="H151" s="10">
+        <v>198626.17</v>
+      </c>
+      <c r="I151" s="4">
+        <v>2011</v>
+      </c>
+      <c r="J151" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.2924437399160441E-2</v>
+      </c>
+      <c r="K151" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L151" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M151" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444448</v>
+      </c>
+      <c r="N151" s="4">
+        <v>118332</v>
+      </c>
+      <c r="O151" s="4">
+        <v>118496</v>
+      </c>
+      <c r="P151" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>164</v>
+      </c>
+      <c r="Q151" s="4">
+        <v>265</v>
+      </c>
+      <c r="R151" s="4">
+        <v>26</v>
+      </c>
+      <c r="S151" s="4">
+        <v>26</v>
+      </c>
+      <c r="T151" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U151" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V151" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W151" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X151" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A152" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B152" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C152" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G152" s="10">
+        <v>7333</v>
+      </c>
+      <c r="H152" s="10">
+        <v>75924.73</v>
+      </c>
+      <c r="I152" s="4">
+        <v>657</v>
+      </c>
+      <c r="J152" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.6582496901865836E-2</v>
+      </c>
+      <c r="K152" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L152" s="15">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="M152" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="N152" s="4">
+        <v>141865</v>
+      </c>
+      <c r="O152" s="4">
+        <v>141946</v>
+      </c>
+      <c r="P152" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>81</v>
+      </c>
+      <c r="Q152" s="4">
+        <v>163</v>
+      </c>
+      <c r="R152" s="4">
+        <v>21</v>
+      </c>
+      <c r="S152" s="4">
+        <v>21</v>
+      </c>
+      <c r="T152" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U152" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V152" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W152" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X152" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y152" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B153" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C153" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G153" s="10">
+        <v>1107.99</v>
+      </c>
+      <c r="H153" s="10">
+        <v>18684.599999999999</v>
+      </c>
+      <c r="I153" s="4">
+        <v>92</v>
+      </c>
+      <c r="J153" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9299637134324526E-2</v>
+      </c>
+      <c r="K153" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L153" s="15">
+        <v>0.73541666666666672</v>
+      </c>
+      <c r="M153" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44375000000000003</v>
+      </c>
+      <c r="N153" s="4">
+        <v>154300</v>
+      </c>
+      <c r="O153" s="4">
+        <v>154398</v>
+      </c>
+      <c r="P153" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>98</v>
+      </c>
+      <c r="Q153" s="4">
+        <v>13</v>
+      </c>
+      <c r="R153" s="4">
+        <v>2</v>
+      </c>
+      <c r="S153" s="4">
+        <v>2</v>
+      </c>
+      <c r="T153" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U153" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V153" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W153" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X153" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A154" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B154" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C154" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G154" s="10">
+        <v>12805.43</v>
+      </c>
+      <c r="H154" s="10">
+        <v>336673.7</v>
+      </c>
+      <c r="I154" s="4">
+        <v>2326</v>
+      </c>
+      <c r="J154" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8035136097651821E-2</v>
+      </c>
+      <c r="K154" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L154" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M154" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49999999999999994</v>
+      </c>
+      <c r="N154" s="4">
+        <v>104102</v>
+      </c>
+      <c r="O154" s="4">
+        <v>104135</v>
+      </c>
+      <c r="P154" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>33</v>
+      </c>
+      <c r="Q154" s="4">
+        <v>395</v>
+      </c>
+      <c r="R154" s="4">
+        <v>8</v>
+      </c>
+      <c r="S154" s="4">
+        <v>8</v>
+      </c>
+      <c r="T154" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U154" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V154" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W154" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X154" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A155" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B155" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C155" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G155" s="10">
+        <v>6572.41</v>
+      </c>
+      <c r="H155" s="10">
+        <v>145386.14000000001</v>
+      </c>
+      <c r="I155" s="4">
+        <v>1089</v>
+      </c>
+      <c r="J155" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5206578838945716E-2</v>
+      </c>
+      <c r="K155" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L155" s="15">
+        <v>0.75555555555555554</v>
+      </c>
+      <c r="M155" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46388888888888885</v>
+      </c>
+      <c r="N155" s="4">
+        <v>12523</v>
+      </c>
+      <c r="O155" s="4">
+        <v>12589</v>
+      </c>
+      <c r="P155" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q155" s="4">
+        <v>199</v>
+      </c>
+      <c r="R155" s="4">
+        <v>20</v>
+      </c>
+      <c r="S155" s="4">
+        <v>20</v>
+      </c>
+      <c r="T155" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U155" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V155" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W155" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X155" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y155" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B156" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C156" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G156" s="10">
+        <v>4996.9399999999996</v>
+      </c>
+      <c r="H156" s="10">
+        <v>93418.03</v>
+      </c>
+      <c r="I156" s="4">
+        <v>1473</v>
+      </c>
+      <c r="J156" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3490102499485374E-2</v>
+      </c>
+      <c r="K156" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L156" s="15">
+        <v>0.74097222222222225</v>
+      </c>
+      <c r="M156" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44930555555555557</v>
+      </c>
+      <c r="N156" s="4">
+        <v>303335</v>
+      </c>
+      <c r="O156" s="4">
+        <v>303436</v>
+      </c>
+      <c r="P156" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>101</v>
+      </c>
+      <c r="Q156" s="4">
+        <v>116</v>
+      </c>
+      <c r="R156" s="4">
+        <v>15</v>
+      </c>
+      <c r="S156" s="4">
+        <v>15</v>
+      </c>
+      <c r="T156" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U156" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V156" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W156" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X156" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y156" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B157" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C157" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G157" s="10">
+        <v>7675.58</v>
+      </c>
+      <c r="H157" s="10">
+        <v>100507.22</v>
+      </c>
+      <c r="I157" s="4">
+        <v>1567</v>
+      </c>
+      <c r="J157" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.6368443978452494E-2</v>
+      </c>
+      <c r="K157" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L157" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M157" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N157" s="4">
+        <v>290485</v>
+      </c>
+      <c r="O157" s="4">
+        <v>290557</v>
+      </c>
+      <c r="P157" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>72</v>
+      </c>
+      <c r="Q157" s="4">
+        <v>69</v>
+      </c>
+      <c r="R157" s="4">
+        <v>5</v>
+      </c>
+      <c r="S157" s="4">
+        <v>5</v>
+      </c>
+      <c r="T157" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U157" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V157" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W157" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X157" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B158" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C158" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G158" s="10">
+        <v>6915.91</v>
+      </c>
+      <c r="H158" s="10">
+        <v>215754.15</v>
+      </c>
+      <c r="I158" s="4">
+        <v>1161</v>
+      </c>
+      <c r="J158" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2054586203787969E-2</v>
+      </c>
+      <c r="K158" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L158" s="15">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="M158" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="N158" s="4">
+        <v>124251</v>
+      </c>
+      <c r="O158" s="4">
+        <v>124299</v>
+      </c>
+      <c r="P158" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q158" s="4">
+        <v>200</v>
+      </c>
+      <c r="R158" s="4">
+        <v>15</v>
+      </c>
+      <c r="S158" s="4">
+        <v>15</v>
+      </c>
+      <c r="T158" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U158" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V158" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W158" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X158" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J148">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J158">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U148">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U158">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V148">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V158">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -15659,7 +16114,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15675,7 +16130,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D148</xm:sqref>
+          <xm:sqref>D2:D158</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF29CE5-7E2C-4AFD-B2BE-771A2BCCA6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE12AD7-F56F-4B18-8AAA-9C9C8EEA0A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="73">
   <si>
     <t>Data</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>13,13,13</t>
+  </si>
+  <si>
+    <t>13,13,13,38,38</t>
   </si>
 </sst>
 </file>
@@ -1658,8 +1661,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V8" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V8" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V9" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
@@ -1701,7 +1704,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y158" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y168" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
@@ -2174,7 +2177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2724,8 +2727,62 @@
       <c r="U8" s="4"/>
       <c r="V8" s="5"/>
     </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="10">
+        <v>12786.37</v>
+      </c>
+      <c r="F9" s="10">
+        <v>104458.62</v>
+      </c>
+      <c r="G9" s="4">
+        <v>633</v>
+      </c>
+      <c r="H9" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>0.12240607811973776</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S9" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H8">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -2733,7 +2790,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R8">
+  <conditionalFormatting sqref="R2:R9">
     <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -2756,7 +2813,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S8">
+  <conditionalFormatting sqref="S2:S9">
     <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
@@ -2780,7 +2837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y158"/>
+  <dimension ref="A1:Y168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -13969,7 +14026,7 @@
         <v>2</v>
       </c>
       <c r="Y133" s="5">
-        <v>42.21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.25">
@@ -16072,8 +16129,848 @@
         <v>0</v>
       </c>
     </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B159" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C159" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G159" s="10">
+        <v>14687.19</v>
+      </c>
+      <c r="H159" s="10">
+        <v>313360.65000000002</v>
+      </c>
+      <c r="I159" s="4">
+        <v>2095</v>
+      </c>
+      <c r="J159" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.6869924478392548E-2</v>
+      </c>
+      <c r="K159" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L159" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M159" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N159" s="4">
+        <v>118496</v>
+      </c>
+      <c r="O159" s="4">
+        <v>118661</v>
+      </c>
+      <c r="P159" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>165</v>
+      </c>
+      <c r="Q159" s="4">
+        <v>311</v>
+      </c>
+      <c r="R159" s="4">
+        <v>37</v>
+      </c>
+      <c r="S159" s="4">
+        <v>37</v>
+      </c>
+      <c r="T159" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U159" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V159" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W159" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X159" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B160" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C160" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G160" s="10">
+        <v>4179.62</v>
+      </c>
+      <c r="H160" s="10">
+        <v>71532.98</v>
+      </c>
+      <c r="I160" s="4">
+        <v>519</v>
+      </c>
+      <c r="J160" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8429272763416258E-2</v>
+      </c>
+      <c r="K160" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L160" s="15">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="M160" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46666666666666662</v>
+      </c>
+      <c r="N160" s="4">
+        <v>303436</v>
+      </c>
+      <c r="O160" s="4">
+        <v>303490</v>
+      </c>
+      <c r="P160" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q160" s="4">
+        <v>66</v>
+      </c>
+      <c r="R160" s="4">
+        <v>20</v>
+      </c>
+      <c r="S160" s="4">
+        <v>20</v>
+      </c>
+      <c r="T160" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U160" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V160" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W160" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X160" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y160" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B161" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C161" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G161" s="10">
+        <v>9947.27</v>
+      </c>
+      <c r="H161" s="10">
+        <v>188381.87</v>
+      </c>
+      <c r="I161" s="4">
+        <v>2322</v>
+      </c>
+      <c r="J161" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2803754416494542E-2</v>
+      </c>
+      <c r="K161" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L161" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M161" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="N161" s="4">
+        <v>12589</v>
+      </c>
+      <c r="O161" s="4">
+        <v>12644</v>
+      </c>
+      <c r="P161" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q161" s="4">
+        <v>165</v>
+      </c>
+      <c r="R161" s="4">
+        <v>20</v>
+      </c>
+      <c r="S161" s="4">
+        <v>17</v>
+      </c>
+      <c r="T161" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>3</v>
+      </c>
+      <c r="U161" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.85</v>
+      </c>
+      <c r="V161" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W161" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X161" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y161" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B162" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C162" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G162" s="10">
+        <v>10500.14</v>
+      </c>
+      <c r="H162" s="10">
+        <v>171291.32</v>
+      </c>
+      <c r="I162" s="4">
+        <v>1911</v>
+      </c>
+      <c r="J162" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1299895406258756E-2</v>
+      </c>
+      <c r="K162" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L162" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M162" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40277777777777773</v>
+      </c>
+      <c r="N162" s="4">
+        <v>279628</v>
+      </c>
+      <c r="O162" s="4">
+        <v>279682</v>
+      </c>
+      <c r="P162" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q162" s="4">
+        <v>218</v>
+      </c>
+      <c r="R162" s="4">
+        <v>36</v>
+      </c>
+      <c r="S162" s="4">
+        <v>36</v>
+      </c>
+      <c r="T162" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U162" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V162" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W162" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X162" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B163" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C163" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G163" s="10">
+        <v>3983.6</v>
+      </c>
+      <c r="H163" s="10">
+        <v>71972.31</v>
+      </c>
+      <c r="I163" s="4">
+        <v>412</v>
+      </c>
+      <c r="J163" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5349064105348296E-2</v>
+      </c>
+      <c r="K163" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L163" s="15">
+        <v>0.71875</v>
+      </c>
+      <c r="M163" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="N163" s="4">
+        <v>124299</v>
+      </c>
+      <c r="O163" s="4">
+        <v>124372</v>
+      </c>
+      <c r="P163" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>73</v>
+      </c>
+      <c r="Q163" s="4">
+        <v>91</v>
+      </c>
+      <c r="R163" s="4">
+        <v>17</v>
+      </c>
+      <c r="S163" s="4">
+        <v>17</v>
+      </c>
+      <c r="T163" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U163" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V163" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W163" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X163" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y163" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B164" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C164" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G164" s="10">
+        <v>1181</v>
+      </c>
+      <c r="H164" s="10">
+        <v>11744.12</v>
+      </c>
+      <c r="I164" s="4">
+        <v>103</v>
+      </c>
+      <c r="J164" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.10056096157055615</v>
+      </c>
+      <c r="K164" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L164" s="15">
+        <v>0.74861111111111112</v>
+      </c>
+      <c r="M164" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45694444444444443</v>
+      </c>
+      <c r="N164" s="4">
+        <v>154398</v>
+      </c>
+      <c r="O164" s="4">
+        <v>154444</v>
+      </c>
+      <c r="P164" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>46</v>
+      </c>
+      <c r="Q164" s="4">
+        <v>20</v>
+      </c>
+      <c r="R164" s="4">
+        <v>2</v>
+      </c>
+      <c r="S164" s="4">
+        <v>2</v>
+      </c>
+      <c r="T164" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U164" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V164" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W164" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X164" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y164" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B165" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C165" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G165" s="10">
+        <v>15587.3</v>
+      </c>
+      <c r="H165" s="10">
+        <v>254038.19</v>
+      </c>
+      <c r="I165" s="4">
+        <v>3476</v>
+      </c>
+      <c r="J165" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1358097378980694E-2</v>
+      </c>
+      <c r="K165" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L165" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M165" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N165" s="4">
+        <v>141946</v>
+      </c>
+      <c r="O165" s="4">
+        <v>142125</v>
+      </c>
+      <c r="P165" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>179</v>
+      </c>
+      <c r="Q165" s="4">
+        <v>286</v>
+      </c>
+      <c r="R165" s="4">
+        <v>18</v>
+      </c>
+      <c r="S165" s="4">
+        <v>18</v>
+      </c>
+      <c r="T165" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U165" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V165" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W165" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X165" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A166" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B166" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C166" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G166" s="10">
+        <v>26282.29</v>
+      </c>
+      <c r="H166" s="10">
+        <v>449177.83</v>
+      </c>
+      <c r="I166" s="4">
+        <v>4351</v>
+      </c>
+      <c r="J166" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8511992900451032E-2</v>
+      </c>
+      <c r="K166" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L166" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M166" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444448</v>
+      </c>
+      <c r="N166" s="4">
+        <v>104135</v>
+      </c>
+      <c r="O166" s="4">
+        <v>104265</v>
+      </c>
+      <c r="P166" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>130</v>
+      </c>
+      <c r="Q166" s="4">
+        <v>683</v>
+      </c>
+      <c r="R166" s="4">
+        <v>44</v>
+      </c>
+      <c r="S166" s="4">
+        <v>44</v>
+      </c>
+      <c r="T166" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U166" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V166" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W166" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X166" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A167" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B167" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C167" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G167" s="10">
+        <v>5299.47</v>
+      </c>
+      <c r="H167" s="10">
+        <v>135367.03</v>
+      </c>
+      <c r="I167" s="4">
+        <v>540</v>
+      </c>
+      <c r="J167" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.9148897630390506E-2</v>
+      </c>
+      <c r="K167" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L167" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M167" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N167" s="4">
+        <v>290557</v>
+      </c>
+      <c r="O167" s="4">
+        <v>290615</v>
+      </c>
+      <c r="P167" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>58</v>
+      </c>
+      <c r="Q167" s="4">
+        <v>105</v>
+      </c>
+      <c r="R167" s="4">
+        <v>7</v>
+      </c>
+      <c r="S167" s="4">
+        <v>7</v>
+      </c>
+      <c r="T167" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U167" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V167" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W167" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X167" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y167" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A168" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B168" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C168" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G168" s="10">
+        <v>4376.83</v>
+      </c>
+      <c r="H168" s="10">
+        <v>105895.2</v>
+      </c>
+      <c r="I168" s="4">
+        <v>391</v>
+      </c>
+      <c r="J168" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1331712863283701E-2</v>
+      </c>
+      <c r="K168" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L168" s="15">
+        <v>0.74861111111111112</v>
+      </c>
+      <c r="M168" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="N168" s="4">
+        <v>274901</v>
+      </c>
+      <c r="O168" s="4">
+        <v>274963</v>
+      </c>
+      <c r="P168" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q168" s="4">
+        <v>114</v>
+      </c>
+      <c r="R168" s="4">
+        <v>5</v>
+      </c>
+      <c r="S168" s="4">
+        <v>5</v>
+      </c>
+      <c r="T168" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U168" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V168" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W168" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X168" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y168" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J158">
+  <conditionalFormatting sqref="J2:J168">
     <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -16081,7 +16978,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U158">
+  <conditionalFormatting sqref="U2:U168">
     <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -16104,7 +17001,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V158">
+  <conditionalFormatting sqref="V2:V168">
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -16130,7 +17027,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D158</xm:sqref>
+          <xm:sqref>D2:D168</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE12AD7-F56F-4B18-8AAA-9C9C8EEA0A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702B49DF-A500-4711-B50C-361984ABC546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -310,7 +310,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,6 +321,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FF0070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF3F"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +471,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -528,6 +534,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1649,6 +1658,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF3F"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -16168,7 +16182,7 @@
       <c r="L159" s="15">
         <v>0.70833333333333337</v>
       </c>
-      <c r="M159" s="15">
+      <c r="M159" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
@@ -16252,7 +16266,7 @@
       <c r="L160" s="15">
         <v>0.7583333333333333</v>
       </c>
-      <c r="M160" s="15">
+      <c r="M160" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46666666666666662</v>
       </c>
@@ -16336,7 +16350,7 @@
       <c r="L161" s="15">
         <v>0.77083333333333337</v>
       </c>
-      <c r="M161" s="15">
+      <c r="M161" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
@@ -16420,7 +16434,7 @@
       <c r="L162" s="15">
         <v>0.69444444444444442</v>
       </c>
-      <c r="M162" s="15">
+      <c r="M162" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.40277777777777773</v>
       </c>
@@ -16504,7 +16518,7 @@
       <c r="L163" s="15">
         <v>0.71875</v>
       </c>
-      <c r="M163" s="15">
+      <c r="M163" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.42708333333333331</v>
       </c>
@@ -16588,7 +16602,7 @@
       <c r="L164" s="15">
         <v>0.74861111111111112</v>
       </c>
-      <c r="M164" s="15">
+      <c r="M164" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45694444444444443</v>
       </c>
@@ -16672,7 +16686,7 @@
       <c r="L165" s="15">
         <v>0.73611111111111116</v>
       </c>
-      <c r="M165" s="15">
+      <c r="M165" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
@@ -16756,7 +16770,7 @@
       <c r="L166" s="15">
         <v>0.74652777777777779</v>
       </c>
-      <c r="M166" s="15">
+      <c r="M166" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.47569444444444448</v>
       </c>
@@ -16840,7 +16854,7 @@
       <c r="L167" s="15">
         <v>0.73611111111111116</v>
       </c>
-      <c r="M167" s="15">
+      <c r="M167" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
@@ -16924,7 +16938,7 @@
       <c r="L168" s="15">
         <v>0.74861111111111112</v>
       </c>
-      <c r="M168" s="15">
+      <c r="M168" s="22">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4777777777777778</v>
       </c>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702B49DF-A500-4711-B50C-361984ABC546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAAF813-E518-41F9-8A7E-ED15A69A75D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="74">
   <si>
     <t>Data</t>
   </si>
@@ -263,6 +263,9 @@
   <si>
     <t>13,13,13,38,38</t>
   </si>
+  <si>
+    <t>13,13,13,13</t>
+  </si>
 </sst>
 </file>
 
@@ -310,7 +313,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -321,12 +324,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FF0070C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF3F"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,7 +533,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -548,7 +545,392 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="134">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1675,94 +2057,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V9" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y168" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y178" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2797,38 +3179,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -2837,7 +3219,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2851,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y168"/>
+  <dimension ref="A1:Y178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -16182,7 +16564,7 @@
       <c r="L159" s="15">
         <v>0.70833333333333337</v>
       </c>
-      <c r="M159" s="22">
+      <c r="M159" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.41666666666666669</v>
       </c>
@@ -16266,7 +16648,7 @@
       <c r="L160" s="15">
         <v>0.7583333333333333</v>
       </c>
-      <c r="M160" s="22">
+      <c r="M160" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.46666666666666662</v>
       </c>
@@ -16350,7 +16732,7 @@
       <c r="L161" s="15">
         <v>0.77083333333333337</v>
       </c>
-      <c r="M161" s="22">
+      <c r="M161" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.5</v>
       </c>
@@ -16434,7 +16816,7 @@
       <c r="L162" s="15">
         <v>0.69444444444444442</v>
       </c>
-      <c r="M162" s="22">
+      <c r="M162" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.40277777777777773</v>
       </c>
@@ -16518,7 +16900,7 @@
       <c r="L163" s="15">
         <v>0.71875</v>
       </c>
-      <c r="M163" s="22">
+      <c r="M163" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.42708333333333331</v>
       </c>
@@ -16602,7 +16984,7 @@
       <c r="L164" s="15">
         <v>0.74861111111111112</v>
       </c>
-      <c r="M164" s="22">
+      <c r="M164" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.45694444444444443</v>
       </c>
@@ -16686,7 +17068,7 @@
       <c r="L165" s="15">
         <v>0.73611111111111116</v>
       </c>
-      <c r="M165" s="22">
+      <c r="M165" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
@@ -16770,7 +17152,7 @@
       <c r="L166" s="15">
         <v>0.74652777777777779</v>
       </c>
-      <c r="M166" s="22">
+      <c r="M166" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.47569444444444448</v>
       </c>
@@ -16854,7 +17236,7 @@
       <c r="L167" s="15">
         <v>0.73611111111111116</v>
       </c>
-      <c r="M167" s="22">
+      <c r="M167" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.44444444444444448</v>
       </c>
@@ -16938,7 +17320,7 @@
       <c r="L168" s="15">
         <v>0.74861111111111112</v>
       </c>
-      <c r="M168" s="22">
+      <c r="M168" s="15">
         <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
         <v>0.4777777777777778</v>
       </c>
@@ -16983,40 +17365,879 @@
         <v>0</v>
       </c>
     </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A169" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B169" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C169" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G169" s="10">
+        <v>12218.41</v>
+      </c>
+      <c r="H169" s="10">
+        <v>181548.94</v>
+      </c>
+      <c r="I169" s="4">
+        <v>2195</v>
+      </c>
+      <c r="J169" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.7300916215759787E-2</v>
+      </c>
+      <c r="K169" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L169" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M169" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N169" s="4">
+        <v>274963</v>
+      </c>
+      <c r="O169" s="4">
+        <v>275086</v>
+      </c>
+      <c r="P169" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>123</v>
+      </c>
+      <c r="Q169" s="4">
+        <v>245</v>
+      </c>
+      <c r="R169" s="4">
+        <v>27</v>
+      </c>
+      <c r="S169" s="4">
+        <v>27</v>
+      </c>
+      <c r="T169" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U169" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V169" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W169" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X169" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A170" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B170" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C170" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G170" s="10">
+        <v>13755.4</v>
+      </c>
+      <c r="H170" s="10">
+        <v>327486.59999999998</v>
+      </c>
+      <c r="I170" s="4">
+        <v>3734</v>
+      </c>
+      <c r="J170" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.200293996762005E-2</v>
+      </c>
+      <c r="K170" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L170" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M170" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N170" s="4">
+        <v>12649</v>
+      </c>
+      <c r="O170" s="4">
+        <v>12703</v>
+      </c>
+      <c r="P170" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q170" s="4">
+        <v>232</v>
+      </c>
+      <c r="R170" s="4">
+        <v>15</v>
+      </c>
+      <c r="S170" s="4">
+        <v>11</v>
+      </c>
+      <c r="T170" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>4</v>
+      </c>
+      <c r="U170" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="V170" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W170" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X170" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y170" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B171" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C171" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G171" s="10">
+        <v>5154.3100000000004</v>
+      </c>
+      <c r="H171" s="10">
+        <v>162580.38</v>
+      </c>
+      <c r="I171" s="4">
+        <v>1284</v>
+      </c>
+      <c r="J171" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.1703148928548454E-2</v>
+      </c>
+      <c r="K171" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L171" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M171" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N171" s="4">
+        <v>290615</v>
+      </c>
+      <c r="O171" s="4">
+        <v>290711</v>
+      </c>
+      <c r="P171" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>96</v>
+      </c>
+      <c r="Q171" s="4">
+        <v>599</v>
+      </c>
+      <c r="R171" s="4">
+        <v>19</v>
+      </c>
+      <c r="S171" s="4">
+        <v>18</v>
+      </c>
+      <c r="T171" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U171" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="V171" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W171" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X171" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y171" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A172" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B172" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C172" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G172" s="10">
+        <v>13592.33</v>
+      </c>
+      <c r="H172" s="10">
+        <v>467084.96</v>
+      </c>
+      <c r="I172" s="4">
+        <v>1915</v>
+      </c>
+      <c r="J172" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.9100337548869051E-2</v>
+      </c>
+      <c r="K172" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L172" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M172" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N172" s="4">
+        <v>118662</v>
+      </c>
+      <c r="O172" s="4">
+        <v>118807</v>
+      </c>
+      <c r="P172" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>145</v>
+      </c>
+      <c r="Q172" s="4">
+        <v>103</v>
+      </c>
+      <c r="R172" s="4">
+        <v>27</v>
+      </c>
+      <c r="S172" s="4">
+        <v>27</v>
+      </c>
+      <c r="T172" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U172" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V172" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W172" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X172" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y172" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A173" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B173" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C173" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G173" s="10">
+        <v>11164.34</v>
+      </c>
+      <c r="H173" s="10">
+        <v>223093.9</v>
+      </c>
+      <c r="I173" s="4">
+        <v>2536</v>
+      </c>
+      <c r="J173" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.004323291672251E-2</v>
+      </c>
+      <c r="K173" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L173" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M173" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N173" s="4">
+        <v>124372</v>
+      </c>
+      <c r="O173" s="4">
+        <v>124456</v>
+      </c>
+      <c r="P173" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>84</v>
+      </c>
+      <c r="Q173" s="4">
+        <v>397</v>
+      </c>
+      <c r="R173" s="4">
+        <v>38</v>
+      </c>
+      <c r="S173" s="4">
+        <v>38</v>
+      </c>
+      <c r="T173" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U173" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V173" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W173" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X173" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y173" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A174" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B174" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C174" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G174" s="10">
+        <v>5030.4399999999996</v>
+      </c>
+      <c r="H174" s="10">
+        <v>68379.62</v>
+      </c>
+      <c r="I174" s="4">
+        <v>903</v>
+      </c>
+      <c r="J174" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3566363779149407E-2</v>
+      </c>
+      <c r="K174" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L174" s="15">
+        <v>0.68958333333333333</v>
+      </c>
+      <c r="M174" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39791666666666664</v>
+      </c>
+      <c r="N174" s="4">
+        <v>303490</v>
+      </c>
+      <c r="O174" s="4">
+        <v>303549</v>
+      </c>
+      <c r="P174" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q174" s="4">
+        <v>167</v>
+      </c>
+      <c r="R174" s="4">
+        <v>25</v>
+      </c>
+      <c r="S174" s="4">
+        <v>25</v>
+      </c>
+      <c r="T174" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U174" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V174" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W174" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X174" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y174" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A175" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B175" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C175" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G175" s="10">
+        <v>19932</v>
+      </c>
+      <c r="H175" s="10">
+        <v>485572.38</v>
+      </c>
+      <c r="I175" s="4">
+        <v>3236</v>
+      </c>
+      <c r="J175" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1048463258968722E-2</v>
+      </c>
+      <c r="K175" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L175" s="15">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="M175" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="N175" s="4">
+        <v>104265</v>
+      </c>
+      <c r="O175" s="4">
+        <v>104296</v>
+      </c>
+      <c r="P175" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q175" s="4">
+        <v>380</v>
+      </c>
+      <c r="R175" s="4">
+        <v>9</v>
+      </c>
+      <c r="S175" s="4">
+        <v>9</v>
+      </c>
+      <c r="T175" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U175" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V175" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W175" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X175" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A176" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B176" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C176" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G176" s="10">
+        <v>6734.86</v>
+      </c>
+      <c r="H176" s="10">
+        <v>128238.08</v>
+      </c>
+      <c r="I176" s="4">
+        <v>1226</v>
+      </c>
+      <c r="J176" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2518409508314531E-2</v>
+      </c>
+      <c r="K176" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L176" s="15">
+        <v>0.66736111111111107</v>
+      </c>
+      <c r="M176" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37569444444444439</v>
+      </c>
+      <c r="N176" s="4">
+        <v>279682</v>
+      </c>
+      <c r="O176" s="4">
+        <v>279735</v>
+      </c>
+      <c r="P176" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q176" s="4">
+        <v>156</v>
+      </c>
+      <c r="R176" s="4">
+        <v>26</v>
+      </c>
+      <c r="S176" s="4">
+        <v>26</v>
+      </c>
+      <c r="T176" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U176" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V176" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W176" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X176" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A177" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B177" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C177" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G177" s="10">
+        <v>7878.56</v>
+      </c>
+      <c r="H177" s="10">
+        <v>163243.06</v>
+      </c>
+      <c r="I177" s="4">
+        <v>1365</v>
+      </c>
+      <c r="J177" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8262756162497818E-2</v>
+      </c>
+      <c r="K177" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L177" s="15">
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="M177" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="N177" s="4">
+        <v>142126</v>
+      </c>
+      <c r="O177" s="4">
+        <v>142194</v>
+      </c>
+      <c r="P177" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>68</v>
+      </c>
+      <c r="Q177" s="4">
+        <v>153</v>
+      </c>
+      <c r="R177" s="4">
+        <v>35</v>
+      </c>
+      <c r="S177" s="4">
+        <v>35</v>
+      </c>
+      <c r="T177" s="12">
+        <v>0</v>
+      </c>
+      <c r="U177" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V177" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W177" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X177" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y177" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A178" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B178" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C178" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G178" s="10">
+        <v>4013.21</v>
+      </c>
+      <c r="H178" s="10">
+        <v>93726.55</v>
+      </c>
+      <c r="I178" s="4">
+        <v>619</v>
+      </c>
+      <c r="J178" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2818283613341147E-2</v>
+      </c>
+      <c r="K178" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L178" s="15">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="M178" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42638888888888887</v>
+      </c>
+      <c r="N178" s="4">
+        <v>154444</v>
+      </c>
+      <c r="O178" s="4">
+        <v>154519</v>
+      </c>
+      <c r="P178" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>75</v>
+      </c>
+      <c r="Q178" s="4">
+        <v>96</v>
+      </c>
+      <c r="R178" s="4">
+        <v>16</v>
+      </c>
+      <c r="S178" s="4">
+        <v>16</v>
+      </c>
+      <c r="T178" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U178" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V178" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W178" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X178" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y178" s="5">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J168">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J178">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U168">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U178">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V168">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V178">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -17025,7 +18246,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17041,7 +18262,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D168</xm:sqref>
+          <xm:sqref>D2:D178</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAAF813-E518-41F9-8A7E-ED15A69A75D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB57189-72DA-4DC5-BE02-5D40F68E3BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="74">
   <si>
     <t>Data</t>
   </si>
@@ -2100,7 +2100,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y178" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y189" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
@@ -3233,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y178"/>
+  <dimension ref="A1:Y189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -17369,11 +17369,11 @@
       <c r="A169" s="8">
         <v>46260</v>
       </c>
-      <c r="B169" s="22">
+      <c r="B169" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C169" s="22">
+      <c r="C169" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17453,11 +17453,11 @@
       <c r="A170" s="8">
         <v>46260</v>
       </c>
-      <c r="B170" s="22">
+      <c r="B170" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C170" s="22">
+      <c r="C170" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17537,11 +17537,11 @@
       <c r="A171" s="8">
         <v>46260</v>
       </c>
-      <c r="B171" s="22">
+      <c r="B171" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C171" s="22">
+      <c r="C171" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17621,11 +17621,11 @@
       <c r="A172" s="8">
         <v>46260</v>
       </c>
-      <c r="B172" s="22">
+      <c r="B172" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C172" s="22">
+      <c r="C172" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17705,11 +17705,11 @@
       <c r="A173" s="8">
         <v>46260</v>
       </c>
-      <c r="B173" s="22">
+      <c r="B173" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C173" s="22">
+      <c r="C173" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17789,11 +17789,11 @@
       <c r="A174" s="8">
         <v>46260</v>
       </c>
-      <c r="B174" s="22">
+      <c r="B174" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C174" s="22">
+      <c r="C174" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17873,11 +17873,11 @@
       <c r="A175" s="8">
         <v>46260</v>
       </c>
-      <c r="B175" s="22">
+      <c r="B175" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C175" s="22">
+      <c r="C175" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -17957,11 +17957,11 @@
       <c r="A176" s="8">
         <v>46260</v>
       </c>
-      <c r="B176" s="22">
+      <c r="B176" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C176" s="22">
+      <c r="C176" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18041,11 +18041,11 @@
       <c r="A177" s="8">
         <v>46260</v>
       </c>
-      <c r="B177" s="22">
+      <c r="B177" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C177" s="22">
+      <c r="C177" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18124,11 +18124,11 @@
       <c r="A178" s="8">
         <v>46260</v>
       </c>
-      <c r="B178" s="22">
+      <c r="B178" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C178" s="22">
+      <c r="C178" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18204,8 +18204,932 @@
         <v>38</v>
       </c>
     </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A179" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B179" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C179" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G179" s="10">
+        <v>13574.29</v>
+      </c>
+      <c r="H179" s="10">
+        <v>255882.02</v>
+      </c>
+      <c r="I179" s="4">
+        <v>3406</v>
+      </c>
+      <c r="J179" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3049018449987231E-2</v>
+      </c>
+      <c r="K179" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L179" s="15">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="M179" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="N179" s="4">
+        <v>12703</v>
+      </c>
+      <c r="O179" s="4">
+        <v>12748</v>
+      </c>
+      <c r="P179" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>45</v>
+      </c>
+      <c r="Q179" s="4">
+        <v>225</v>
+      </c>
+      <c r="R179" s="4">
+        <v>11</v>
+      </c>
+      <c r="S179" s="4">
+        <v>10</v>
+      </c>
+      <c r="T179" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U179" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="V179" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W179" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X179" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y179" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A180" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B180" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C180" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G180" s="10">
+        <v>10379.049999999999</v>
+      </c>
+      <c r="H180" s="10">
+        <v>142041.26999999999</v>
+      </c>
+      <c r="I180" s="4">
+        <v>2375</v>
+      </c>
+      <c r="J180" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3070664603322677E-2</v>
+      </c>
+      <c r="K180" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L180" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M180" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444448</v>
+      </c>
+      <c r="N180" s="4">
+        <v>104296</v>
+      </c>
+      <c r="O180" s="4">
+        <v>104428</v>
+      </c>
+      <c r="P180" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>132</v>
+      </c>
+      <c r="Q180" s="4">
+        <v>311</v>
+      </c>
+      <c r="R180" s="4">
+        <v>23</v>
+      </c>
+      <c r="S180" s="4">
+        <v>23</v>
+      </c>
+      <c r="T180" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U180" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V180" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W180" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X180" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A181" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B181" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C181" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G181" s="10">
+        <v>2983.9</v>
+      </c>
+      <c r="H181" s="10">
+        <v>61363.38</v>
+      </c>
+      <c r="I181" s="4">
+        <v>328</v>
+      </c>
+      <c r="J181" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.862672167015572E-2</v>
+      </c>
+      <c r="K181" s="11">
+        <v>0.29375000000000001</v>
+      </c>
+      <c r="L181" s="15">
+        <v>0.69513888888888886</v>
+      </c>
+      <c r="M181" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40138888888888885</v>
+      </c>
+      <c r="N181" s="4">
+        <v>154519</v>
+      </c>
+      <c r="O181" s="4">
+        <v>154573</v>
+      </c>
+      <c r="P181" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q181" s="4">
+        <v>27</v>
+      </c>
+      <c r="R181" s="4">
+        <v>4</v>
+      </c>
+      <c r="S181" s="4">
+        <v>4</v>
+      </c>
+      <c r="T181" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U181" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V181" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W181" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X181" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y181" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A182" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B182" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C182" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G182" s="10">
+        <v>4640.72</v>
+      </c>
+      <c r="H182" s="10">
+        <v>48679.42</v>
+      </c>
+      <c r="I182" s="4">
+        <v>658</v>
+      </c>
+      <c r="J182" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.5332277993451855E-2</v>
+      </c>
+      <c r="K182" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L182" s="15">
+        <v>0.7055555555555556</v>
+      </c>
+      <c r="M182" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41388888888888892</v>
+      </c>
+      <c r="N182" s="4">
+        <v>142194</v>
+      </c>
+      <c r="O182" s="4">
+        <v>142266</v>
+      </c>
+      <c r="P182" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>72</v>
+      </c>
+      <c r="Q182" s="4">
+        <v>73</v>
+      </c>
+      <c r="R182" s="4">
+        <v>14</v>
+      </c>
+      <c r="S182" s="4">
+        <v>14</v>
+      </c>
+      <c r="T182" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U182" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V182" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W182" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X182" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y182" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A183" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B183" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C183" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G183" s="10">
+        <v>5647.33</v>
+      </c>
+      <c r="H183" s="10">
+        <v>196173.22</v>
+      </c>
+      <c r="I183" s="4">
+        <v>1142</v>
+      </c>
+      <c r="J183" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.8787466505367041E-2</v>
+      </c>
+      <c r="K183" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L183" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M183" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="N183" s="4">
+        <v>290711</v>
+      </c>
+      <c r="O183" s="4">
+        <v>290754</v>
+      </c>
+      <c r="P183" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q183" s="4">
+        <v>8</v>
+      </c>
+      <c r="R183" s="4">
+        <v>2</v>
+      </c>
+      <c r="S183" s="4">
+        <v>2</v>
+      </c>
+      <c r="T183" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U183" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V183" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W183" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X183" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A184" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B184" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C184" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G184" s="10">
+        <v>4475.83</v>
+      </c>
+      <c r="H184" s="10">
+        <v>93265.65</v>
+      </c>
+      <c r="I184" s="4">
+        <v>811</v>
+      </c>
+      <c r="J184" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.7990122837293259E-2</v>
+      </c>
+      <c r="K184" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L184" s="15">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="M184" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="N184" s="4">
+        <v>303545</v>
+      </c>
+      <c r="O184" s="4">
+        <v>303614</v>
+      </c>
+      <c r="P184" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>69</v>
+      </c>
+      <c r="Q184" s="4">
+        <v>15</v>
+      </c>
+      <c r="R184" s="4">
+        <v>17</v>
+      </c>
+      <c r="S184" s="4">
+        <v>17</v>
+      </c>
+      <c r="T184" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U184" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V184" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W184" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X184" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y184" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A185" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B185" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C185" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G185" s="10">
+        <v>13667.92</v>
+      </c>
+      <c r="H185" s="10">
+        <v>774683.57</v>
+      </c>
+      <c r="I185" s="4">
+        <v>1644</v>
+      </c>
+      <c r="J185" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.764322948013471E-2</v>
+      </c>
+      <c r="K185" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L185" s="15">
+        <v>0.81319444444444444</v>
+      </c>
+      <c r="M185" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="N185" s="4">
+        <v>124456</v>
+      </c>
+      <c r="O185" s="4">
+        <v>124533</v>
+      </c>
+      <c r="P185" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>77</v>
+      </c>
+      <c r="Q185" s="4">
+        <v>339</v>
+      </c>
+      <c r="R185" s="4">
+        <v>19</v>
+      </c>
+      <c r="S185" s="4">
+        <v>19</v>
+      </c>
+      <c r="T185" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U185" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V185" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W185" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X185" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y185" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A186" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B186" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C186" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G186" s="10">
+        <v>17143.009999999998</v>
+      </c>
+      <c r="H186" s="10">
+        <v>562507.4</v>
+      </c>
+      <c r="I186" s="4">
+        <v>3400</v>
+      </c>
+      <c r="J186" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.0476061292704769E-2</v>
+      </c>
+      <c r="K186" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L186" s="15">
+        <v>0.80833333333333335</v>
+      </c>
+      <c r="M186" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51666666666666661</v>
+      </c>
+      <c r="N186" s="4">
+        <v>275086</v>
+      </c>
+      <c r="O186" s="4">
+        <v>275128</v>
+      </c>
+      <c r="P186" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q186" s="4">
+        <v>29</v>
+      </c>
+      <c r="R186" s="4">
+        <v>2</v>
+      </c>
+      <c r="S186" s="4">
+        <v>2</v>
+      </c>
+      <c r="T186" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U186" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V186" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W186" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X186" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A187" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B187" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C187" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G187" s="10">
+        <v>6777.03</v>
+      </c>
+      <c r="H187" s="10">
+        <v>122575.76</v>
+      </c>
+      <c r="I187" s="4">
+        <v>2780</v>
+      </c>
+      <c r="J187" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5288500760672418E-2</v>
+      </c>
+      <c r="K187" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L187" s="15">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="M187" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.26944444444444443</v>
+      </c>
+      <c r="N187" s="4">
+        <v>279735</v>
+      </c>
+      <c r="O187" s="4">
+        <v>279789</v>
+      </c>
+      <c r="P187" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q187" s="4">
+        <v>862</v>
+      </c>
+      <c r="R187" s="4">
+        <v>10</v>
+      </c>
+      <c r="S187" s="4">
+        <v>10</v>
+      </c>
+      <c r="T187" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U187" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V187" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W187" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X187" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A188" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B188" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C188" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G188" s="10">
+        <v>1369.54</v>
+      </c>
+      <c r="H188" s="10">
+        <v>66487.78</v>
+      </c>
+      <c r="I188" s="4">
+        <v>534</v>
+      </c>
+      <c r="J188" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.0598371610542569E-2</v>
+      </c>
+      <c r="K188" s="11">
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="L188" s="15">
+        <v>0.71388888888888891</v>
+      </c>
+      <c r="M188" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.13819444444444451</v>
+      </c>
+      <c r="N188" s="4">
+        <v>279789</v>
+      </c>
+      <c r="O188" s="4">
+        <v>279821</v>
+      </c>
+      <c r="P188" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>32</v>
+      </c>
+      <c r="Q188" s="4">
+        <v>13</v>
+      </c>
+      <c r="R188" s="4">
+        <v>3</v>
+      </c>
+      <c r="S188" s="4">
+        <v>3</v>
+      </c>
+      <c r="T188" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U188" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V188" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W188" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X188" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y188" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A189" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B189" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C189" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G189" s="10">
+        <v>8498.7800000000007</v>
+      </c>
+      <c r="H189" s="10">
+        <v>82910.05</v>
+      </c>
+      <c r="I189" s="4">
+        <v>1499</v>
+      </c>
+      <c r="J189" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.10250602912433415</v>
+      </c>
+      <c r="K189" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L189" s="15">
+        <v>0.73055555555555551</v>
+      </c>
+      <c r="M189" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41805555555555551</v>
+      </c>
+      <c r="N189" s="4">
+        <v>118807</v>
+      </c>
+      <c r="O189" s="4">
+        <v>118863</v>
+      </c>
+      <c r="P189" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q189" s="4">
+        <v>199</v>
+      </c>
+      <c r="R189" s="4">
+        <v>17</v>
+      </c>
+      <c r="S189" s="4">
+        <v>17</v>
+      </c>
+      <c r="T189" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U189" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V189" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W189" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X189" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y189" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J178">
+  <conditionalFormatting sqref="J2:J189">
     <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -18213,7 +19137,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U178">
+  <conditionalFormatting sqref="U2:U189">
     <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -18236,7 +19160,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V178">
+  <conditionalFormatting sqref="V2:V189">
     <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -18262,7 +19186,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D178</xm:sqref>
+          <xm:sqref>D2:D189</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB57189-72DA-4DC5-BE02-5D40F68E3BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE75427-6500-4E3C-8C33-06492279968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="74">
   <si>
     <t>Data</t>
   </si>
@@ -622,6 +622,509 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1248,509 +1751,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2100,51 +2100,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y189" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y197" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3179,38 +3179,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3219,7 +3219,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3233,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y189"/>
+  <dimension ref="A1:Y197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -18208,11 +18208,11 @@
       <c r="A179" s="8">
         <v>46261</v>
       </c>
-      <c r="B179" s="22">
+      <c r="B179" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C179" s="22">
+      <c r="C179" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18292,11 +18292,11 @@
       <c r="A180" s="8">
         <v>46261</v>
       </c>
-      <c r="B180" s="22">
+      <c r="B180" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C180" s="22">
+      <c r="C180" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18376,11 +18376,11 @@
       <c r="A181" s="8">
         <v>46261</v>
       </c>
-      <c r="B181" s="22">
+      <c r="B181" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C181" s="22">
+      <c r="C181" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18460,11 +18460,11 @@
       <c r="A182" s="8">
         <v>46261</v>
       </c>
-      <c r="B182" s="22">
+      <c r="B182" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C182" s="22">
+      <c r="C182" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18544,11 +18544,11 @@
       <c r="A183" s="8">
         <v>46261</v>
       </c>
-      <c r="B183" s="22">
+      <c r="B183" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C183" s="22">
+      <c r="C183" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18628,11 +18628,11 @@
       <c r="A184" s="8">
         <v>46261</v>
       </c>
-      <c r="B184" s="22">
+      <c r="B184" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C184" s="22">
+      <c r="C184" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18712,11 +18712,11 @@
       <c r="A185" s="8">
         <v>46261</v>
       </c>
-      <c r="B185" s="22">
+      <c r="B185" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C185" s="22">
+      <c r="C185" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18796,11 +18796,11 @@
       <c r="A186" s="8">
         <v>46261</v>
       </c>
-      <c r="B186" s="22">
+      <c r="B186" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C186" s="22">
+      <c r="C186" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18880,11 +18880,11 @@
       <c r="A187" s="8">
         <v>46261</v>
       </c>
-      <c r="B187" s="22">
+      <c r="B187" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C187" s="22">
+      <c r="C187" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -18964,11 +18964,11 @@
       <c r="A188" s="8">
         <v>46261</v>
       </c>
-      <c r="B188" s="22">
+      <c r="B188" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C188" s="22">
+      <c r="C188" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19048,11 +19048,11 @@
       <c r="A189" s="8">
         <v>46261</v>
       </c>
-      <c r="B189" s="22">
+      <c r="B189" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C189" s="22">
+      <c r="C189" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19128,40 +19128,712 @@
         <v>0</v>
       </c>
     </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A190" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B190" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C190" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G190" s="10">
+        <v>5645.21</v>
+      </c>
+      <c r="H190" s="10">
+        <v>103589.13</v>
+      </c>
+      <c r="I190" s="4">
+        <v>851</v>
+      </c>
+      <c r="J190" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4496161904246131E-2</v>
+      </c>
+      <c r="K190" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L190" s="15">
+        <v>0.80972222222222223</v>
+      </c>
+      <c r="M190" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49722222222222223</v>
+      </c>
+      <c r="N190" s="4">
+        <v>303614</v>
+      </c>
+      <c r="O190" s="4">
+        <v>303693</v>
+      </c>
+      <c r="P190" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>79</v>
+      </c>
+      <c r="Q190" s="4">
+        <v>199</v>
+      </c>
+      <c r="R190" s="4">
+        <v>18</v>
+      </c>
+      <c r="S190" s="4">
+        <v>18</v>
+      </c>
+      <c r="T190" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U190" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V190" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W190" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X190" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A191" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B191" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C191" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G191" s="10">
+        <v>17517.86</v>
+      </c>
+      <c r="H191" s="10">
+        <v>415120.14</v>
+      </c>
+      <c r="I191" s="4">
+        <v>95</v>
+      </c>
+      <c r="J191" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2199494343974735E-2</v>
+      </c>
+      <c r="K191" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L191" s="15">
+        <v>0.69930555555555551</v>
+      </c>
+      <c r="M191" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4284722222222222</v>
+      </c>
+      <c r="N191" s="4">
+        <v>104425</v>
+      </c>
+      <c r="O191" s="4">
+        <v>104557</v>
+      </c>
+      <c r="P191" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>132</v>
+      </c>
+      <c r="Q191" s="4">
+        <v>95</v>
+      </c>
+      <c r="R191" s="4">
+        <v>18</v>
+      </c>
+      <c r="S191" s="4">
+        <v>18</v>
+      </c>
+      <c r="T191" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U191" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V191" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W191" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X191" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y191" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A192" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B192" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C192" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G192" s="10">
+        <v>6881.98</v>
+      </c>
+      <c r="H192" s="10">
+        <v>61042.18</v>
+      </c>
+      <c r="I192" s="4">
+        <v>704</v>
+      </c>
+      <c r="J192" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.1127413863659522</v>
+      </c>
+      <c r="K192" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L192" s="15">
+        <v>0.74375000000000002</v>
+      </c>
+      <c r="M192" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="N192" s="4">
+        <v>275128</v>
+      </c>
+      <c r="O192" s="4">
+        <v>275155</v>
+      </c>
+      <c r="P192" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>27</v>
+      </c>
+      <c r="Q192" s="4">
+        <v>206</v>
+      </c>
+      <c r="R192" s="4">
+        <v>10</v>
+      </c>
+      <c r="S192" s="4">
+        <v>10</v>
+      </c>
+      <c r="T192" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U192" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V192" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W192" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X192" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y192" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A193" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B193" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C193" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G193" s="10">
+        <v>1513.17</v>
+      </c>
+      <c r="H193" s="10">
+        <v>76194</v>
+      </c>
+      <c r="I193" s="4">
+        <v>132</v>
+      </c>
+      <c r="J193" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.9859437751004017E-2</v>
+      </c>
+      <c r="K193" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L193" s="15">
+        <v>0.62638888888888888</v>
+      </c>
+      <c r="M193" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3347222222222222</v>
+      </c>
+      <c r="N193" s="4">
+        <v>154573</v>
+      </c>
+      <c r="O193" s="4">
+        <v>154633</v>
+      </c>
+      <c r="P193" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>60</v>
+      </c>
+      <c r="Q193" s="4">
+        <v>2</v>
+      </c>
+      <c r="R193" s="4">
+        <v>1</v>
+      </c>
+      <c r="S193" s="4">
+        <v>1</v>
+      </c>
+      <c r="T193" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U193" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V193" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W193" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X193" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A194" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B194" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C194" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G194" s="10">
+        <v>11698.62</v>
+      </c>
+      <c r="H194" s="10">
+        <v>195730.85</v>
+      </c>
+      <c r="I194" s="4">
+        <v>133</v>
+      </c>
+      <c r="J194" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9768912258849338E-2</v>
+      </c>
+      <c r="K194" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L194" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M194" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="N194" s="4">
+        <v>290754</v>
+      </c>
+      <c r="O194" s="4">
+        <v>290910</v>
+      </c>
+      <c r="P194" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>156</v>
+      </c>
+      <c r="Q194" s="4">
+        <v>133</v>
+      </c>
+      <c r="R194" s="4">
+        <v>12</v>
+      </c>
+      <c r="S194" s="4">
+        <v>12</v>
+      </c>
+      <c r="T194" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U194" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V194" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W194" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X194" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y194" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A195" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B195" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C195" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G195" s="10">
+        <v>6956.26</v>
+      </c>
+      <c r="H195" s="10">
+        <v>135818.84</v>
+      </c>
+      <c r="I195" s="4">
+        <v>1302</v>
+      </c>
+      <c r="J195" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.1217194904624425E-2</v>
+      </c>
+      <c r="K195" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L195" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M195" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42361111111111116</v>
+      </c>
+      <c r="N195" s="4">
+        <v>124533</v>
+      </c>
+      <c r="O195" s="4">
+        <v>124600</v>
+      </c>
+      <c r="P195" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q195" s="4">
+        <v>225</v>
+      </c>
+      <c r="R195" s="4">
+        <v>18</v>
+      </c>
+      <c r="S195" s="4">
+        <v>18</v>
+      </c>
+      <c r="T195" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U195" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V195" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W195" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X195" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A196" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B196" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C196" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G196" s="10">
+        <v>10088.56</v>
+      </c>
+      <c r="H196" s="10">
+        <v>153429.60999999999</v>
+      </c>
+      <c r="I196" s="4">
+        <v>1820</v>
+      </c>
+      <c r="J196" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5753670363888697E-2</v>
+      </c>
+      <c r="K196" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L196" s="15">
+        <v>0.77361111111111114</v>
+      </c>
+      <c r="M196" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50277777777777777</v>
+      </c>
+      <c r="N196" s="4">
+        <v>279821</v>
+      </c>
+      <c r="O196" s="4">
+        <v>279874</v>
+      </c>
+      <c r="P196" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q196" s="4">
+        <v>259</v>
+      </c>
+      <c r="R196" s="4">
+        <v>22</v>
+      </c>
+      <c r="S196" s="4">
+        <v>22</v>
+      </c>
+      <c r="T196" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U196" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V196" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W196" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X196" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y196" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A197" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B197" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C197" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G197" s="10">
+        <v>15330.37</v>
+      </c>
+      <c r="H197" s="10">
+        <v>125063.67</v>
+      </c>
+      <c r="I197" s="4">
+        <v>2172</v>
+      </c>
+      <c r="J197" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.12258052238511792</v>
+      </c>
+      <c r="K197" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L197" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M197" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N197" s="4">
+        <v>12748</v>
+      </c>
+      <c r="O197" s="4">
+        <v>12802</v>
+      </c>
+      <c r="P197" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q197" s="4">
+        <v>250</v>
+      </c>
+      <c r="R197" s="4">
+        <v>23</v>
+      </c>
+      <c r="S197" s="4">
+        <v>23</v>
+      </c>
+      <c r="T197" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U197" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V197" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W197" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X197" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y197" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J189">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J197">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U189">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U197">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V189">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V197">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -19170,7 +19842,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19186,7 +19858,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D189</xm:sqref>
+          <xm:sqref>D2:D197</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE75427-6500-4E3C-8C33-06492279968D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4276CC-8B96-428D-A216-05C946336FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="75">
   <si>
     <t>Data</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>13,13,13,13</t>
+  </si>
+  <si>
+    <t>13,13,13,13,13,13,13,13,13,13,8,8,8,8</t>
   </si>
 </sst>
 </file>
@@ -622,509 +625,6 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1751,6 +1251,509 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2100,51 +2103,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y197" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y202" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3179,38 +3182,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3219,7 +3222,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3233,7 +3236,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y197"/>
+  <dimension ref="A1:Y202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3257,7 +3260,7 @@
     <col min="22" max="22" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.5703125" customWidth="1"/>
     <col min="24" max="24" width="14.7109375" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="33.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -19132,11 +19135,11 @@
       <c r="A190" s="8">
         <v>46262</v>
       </c>
-      <c r="B190" s="22">
+      <c r="B190" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C190" s="22">
+      <c r="C190" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19216,11 +19219,11 @@
       <c r="A191" s="8">
         <v>46262</v>
       </c>
-      <c r="B191" s="22">
+      <c r="B191" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C191" s="22">
+      <c r="C191" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19300,11 +19303,11 @@
       <c r="A192" s="8">
         <v>46262</v>
       </c>
-      <c r="B192" s="22">
+      <c r="B192" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C192" s="22">
+      <c r="C192" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19384,11 +19387,11 @@
       <c r="A193" s="8">
         <v>46262</v>
       </c>
-      <c r="B193" s="22">
+      <c r="B193" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C193" s="22">
+      <c r="C193" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19468,11 +19471,11 @@
       <c r="A194" s="8">
         <v>46262</v>
       </c>
-      <c r="B194" s="22">
+      <c r="B194" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C194" s="22">
+      <c r="C194" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19552,11 +19555,11 @@
       <c r="A195" s="8">
         <v>46262</v>
       </c>
-      <c r="B195" s="22">
+      <c r="B195" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C195" s="22">
+      <c r="C195" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19636,11 +19639,11 @@
       <c r="A196" s="8">
         <v>46262</v>
       </c>
-      <c r="B196" s="22">
+      <c r="B196" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C196" s="22">
+      <c r="C196" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19720,11 +19723,11 @@
       <c r="A197" s="8">
         <v>46262</v>
       </c>
-      <c r="B197" s="22">
+      <c r="B197" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C197" s="22">
+      <c r="C197" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -19800,40 +19803,460 @@
         <v>0</v>
       </c>
     </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A198" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B198" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C198" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G198" s="10">
+        <v>15749.94</v>
+      </c>
+      <c r="H198" s="10">
+        <v>104499.02</v>
+      </c>
+      <c r="I198" s="4">
+        <v>2536</v>
+      </c>
+      <c r="J198" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.15071854262365331</v>
+      </c>
+      <c r="K198" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L198" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M198" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N198" s="4">
+        <v>118863</v>
+      </c>
+      <c r="O198" s="4">
+        <v>118901</v>
+      </c>
+      <c r="P198" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q198" s="4">
+        <v>500</v>
+      </c>
+      <c r="R198" s="4">
+        <v>11</v>
+      </c>
+      <c r="S198" s="4">
+        <v>11</v>
+      </c>
+      <c r="T198" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U198" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V198" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W198" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X198" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y198" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A199" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B199" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C199" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G199" s="10">
+        <v>3684.39</v>
+      </c>
+      <c r="H199" s="10">
+        <v>69696.740000000005</v>
+      </c>
+      <c r="I199" s="4">
+        <v>879</v>
+      </c>
+      <c r="J199" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2863161175113783E-2</v>
+      </c>
+      <c r="K199" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L199" s="15">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="M199" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4555555555555556</v>
+      </c>
+      <c r="N199" s="4">
+        <v>142266</v>
+      </c>
+      <c r="O199" s="4">
+        <v>142290</v>
+      </c>
+      <c r="P199" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>24</v>
+      </c>
+      <c r="Q199" s="4">
+        <v>174</v>
+      </c>
+      <c r="R199" s="4">
+        <v>14</v>
+      </c>
+      <c r="S199" s="4">
+        <v>0</v>
+      </c>
+      <c r="T199" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>14</v>
+      </c>
+      <c r="U199" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0</v>
+      </c>
+      <c r="V199" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W199" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X199" s="4">
+        <v>14</v>
+      </c>
+      <c r="Y199" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A200" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B200" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C200" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G200" s="10">
+        <v>2779.1</v>
+      </c>
+      <c r="H200" s="10">
+        <v>114743.1</v>
+      </c>
+      <c r="I200" s="4">
+        <v>412</v>
+      </c>
+      <c r="J200" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.4220192761046196E-2</v>
+      </c>
+      <c r="K200" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L200" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M200" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.14583333333333331</v>
+      </c>
+      <c r="N200" s="4">
+        <v>275155</v>
+      </c>
+      <c r="O200" s="4">
+        <v>275192</v>
+      </c>
+      <c r="P200" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q200" s="4">
+        <v>123</v>
+      </c>
+      <c r="R200" s="4">
+        <v>9</v>
+      </c>
+      <c r="S200" s="4">
+        <v>9</v>
+      </c>
+      <c r="T200" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U200" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V200" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W200" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X200" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A201" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B201" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C201" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G201" s="10">
+        <v>1798.27</v>
+      </c>
+      <c r="H201" s="10">
+        <v>21119.42</v>
+      </c>
+      <c r="I201" s="4">
+        <v>588</v>
+      </c>
+      <c r="J201" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.5147698184893345E-2</v>
+      </c>
+      <c r="K201" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L201" s="15">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="M201" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="N201" s="4">
+        <v>154634</v>
+      </c>
+      <c r="O201" s="4">
+        <v>154765</v>
+      </c>
+      <c r="P201" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>131</v>
+      </c>
+      <c r="Q201" s="4">
+        <v>36</v>
+      </c>
+      <c r="R201" s="4">
+        <v>7</v>
+      </c>
+      <c r="S201" s="4">
+        <v>7</v>
+      </c>
+      <c r="T201" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U201" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V201" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W201" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X201" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y201" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A202" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B202" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C202" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G202" s="10">
+        <v>5891.7979999999998</v>
+      </c>
+      <c r="H202" s="10">
+        <v>71421.240000000005</v>
+      </c>
+      <c r="I202" s="4">
+        <v>603</v>
+      </c>
+      <c r="J202" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.2493639147122058E-2</v>
+      </c>
+      <c r="K202" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L202" s="15">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="M202" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.24305555555555552</v>
+      </c>
+      <c r="N202" s="4">
+        <v>118901</v>
+      </c>
+      <c r="O202" s="4">
+        <v>119035</v>
+      </c>
+      <c r="P202" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>134</v>
+      </c>
+      <c r="Q202" s="4">
+        <v>97</v>
+      </c>
+      <c r="R202" s="4">
+        <v>20</v>
+      </c>
+      <c r="S202" s="4">
+        <v>20</v>
+      </c>
+      <c r="T202" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U202" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V202" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W202" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X202" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y202" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J197">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J202">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U197">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U202">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V197">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V202">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -19842,7 +20265,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19858,7 +20281,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D197</xm:sqref>
+          <xm:sqref>D2:D202</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4276CC-8B96-428D-A216-05C946336FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCE3C76-3E67-4B92-8759-B3736667E29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="76">
   <si>
     <t>Data</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>13,13,13,13,13,13,13,13,13,13,8,8,8,8</t>
+  </si>
+  <si>
+    <t>Rota</t>
   </si>
 </sst>
 </file>
@@ -2103,7 +2106,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y202" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y213" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
@@ -2113,7 +2116,7 @@
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Carreta" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
     <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
@@ -3236,7 +3239,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y202"/>
+  <dimension ref="A1:Y213"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3277,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3355,7 +3358,9 @@
       <c r="D2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
       <c r="F2" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -3439,7 +3444,9 @@
       <c r="D3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
       <c r="F3" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -3523,7 +3530,9 @@
       <c r="D4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
       <c r="F4" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -3607,7 +3616,9 @@
       <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
       <c r="F5" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -3691,7 +3702,9 @@
       <c r="D6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
       <c r="F6" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -3775,7 +3788,9 @@
       <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
       <c r="F7" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -3859,7 +3874,9 @@
       <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
       <c r="F8" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -3943,7 +3960,9 @@
       <c r="D9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
       <c r="F9" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -4027,7 +4046,9 @@
       <c r="D10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
       <c r="F10" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Geber</v>
@@ -4111,7 +4132,9 @@
       <c r="D11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
       <c r="F11" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -4195,7 +4218,9 @@
       <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
       <c r="F12" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -4279,7 +4304,9 @@
       <c r="D13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
       <c r="F13" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -4363,7 +4390,9 @@
       <c r="D14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
       <c r="F14" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -4447,7 +4476,9 @@
       <c r="D15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
       <c r="F15" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -4531,7 +4562,9 @@
       <c r="D16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
       <c r="F16" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -4615,7 +4648,9 @@
       <c r="D17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
       <c r="F17" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -4699,7 +4734,9 @@
       <c r="D18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
       <c r="F18" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -4783,7 +4820,9 @@
       <c r="D19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
       <c r="F19" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -4867,7 +4906,9 @@
       <c r="D20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
       <c r="F20" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -4951,7 +4992,9 @@
       <c r="D21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
       <c r="F21" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -5035,7 +5078,9 @@
       <c r="D22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4">
+        <v>0</v>
+      </c>
       <c r="F22" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -5119,7 +5164,9 @@
       <c r="D23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
       <c r="F23" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -5203,7 +5250,9 @@
       <c r="D24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4">
+        <v>0</v>
+      </c>
       <c r="F24" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -5287,7 +5336,9 @@
       <c r="D25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
       <c r="F25" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -5371,7 +5422,9 @@
       <c r="D26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
       <c r="F26" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -5455,7 +5508,9 @@
       <c r="D27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="4">
+        <v>0</v>
+      </c>
       <c r="F27" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -5539,7 +5594,9 @@
       <c r="D28" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
       <c r="F28" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -5623,7 +5680,9 @@
       <c r="D29" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
       <c r="F29" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -5707,7 +5766,9 @@
       <c r="D30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="4"/>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
       <c r="F30" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -5791,7 +5852,9 @@
       <c r="D31" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="4"/>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
       <c r="F31" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -5875,7 +5938,9 @@
       <c r="D32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="4"/>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
       <c r="F32" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -5959,7 +6024,9 @@
       <c r="D33" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="4"/>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
       <c r="F33" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -6043,7 +6110,9 @@
       <c r="D34" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="4"/>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
       <c r="F34" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -6127,7 +6196,9 @@
       <c r="D35" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="4"/>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
       <c r="F35" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -6211,7 +6282,9 @@
       <c r="D36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="4"/>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
       <c r="F36" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -6295,7 +6368,9 @@
       <c r="D37" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E37" s="4"/>
+      <c r="E37" s="4">
+        <v>0</v>
+      </c>
       <c r="F37" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -6379,7 +6454,9 @@
       <c r="D38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E38" s="4"/>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
       <c r="F38" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -6463,7 +6540,9 @@
       <c r="D39" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="4"/>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
       <c r="F39" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -6547,7 +6626,9 @@
       <c r="D40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E40" s="4"/>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
       <c r="F40" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -6631,7 +6712,9 @@
       <c r="D41" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E41" s="4"/>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
       <c r="F41" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -6715,7 +6798,9 @@
       <c r="D42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="4"/>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
       <c r="F42" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -6799,7 +6884,9 @@
       <c r="D43" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="4"/>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
       <c r="F43" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -6883,7 +6970,9 @@
       <c r="D44" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="4"/>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
       <c r="F44" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -6967,7 +7056,9 @@
       <c r="D45" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="4"/>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
       <c r="F45" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -7051,7 +7142,9 @@
       <c r="D46" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E46" s="4"/>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
       <c r="F46" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -7135,7 +7228,9 @@
       <c r="D47" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="4"/>
+      <c r="E47" s="4">
+        <v>0</v>
+      </c>
       <c r="F47" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -7219,7 +7314,9 @@
       <c r="D48" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E48" s="4"/>
+      <c r="E48" s="4">
+        <v>0</v>
+      </c>
       <c r="F48" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -7303,7 +7400,9 @@
       <c r="D49" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="4"/>
+      <c r="E49" s="4">
+        <v>0</v>
+      </c>
       <c r="F49" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -7387,7 +7486,9 @@
       <c r="D50" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E50" s="4"/>
+      <c r="E50" s="4">
+        <v>0</v>
+      </c>
       <c r="F50" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -7471,7 +7572,9 @@
       <c r="D51" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E51" s="4"/>
+      <c r="E51" s="4">
+        <v>0</v>
+      </c>
       <c r="F51" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -7555,7 +7658,9 @@
       <c r="D52" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E52" s="4"/>
+      <c r="E52" s="4">
+        <v>0</v>
+      </c>
       <c r="F52" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -7639,7 +7744,9 @@
       <c r="D53" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E53" s="4"/>
+      <c r="E53" s="4">
+        <v>0</v>
+      </c>
       <c r="F53" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -7723,7 +7830,9 @@
       <c r="D54" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="4"/>
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
       <c r="F54" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -7807,7 +7916,9 @@
       <c r="D55" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E55" s="4"/>
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
       <c r="F55" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Geber</v>
@@ -7891,7 +8002,9 @@
       <c r="D56" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="4"/>
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
       <c r="F56" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -7975,7 +8088,9 @@
       <c r="D57" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E57" s="4"/>
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
       <c r="F57" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -8059,7 +8174,9 @@
       <c r="D58" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E58" s="4"/>
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
       <c r="F58" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -8143,7 +8260,9 @@
       <c r="D59" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E59" s="4"/>
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
       <c r="F59" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -8227,7 +8346,9 @@
       <c r="D60" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E60" s="4"/>
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
       <c r="F60" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -8311,7 +8432,9 @@
       <c r="D61" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E61" s="4"/>
+      <c r="E61" s="4">
+        <v>0</v>
+      </c>
       <c r="F61" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -8395,7 +8518,9 @@
       <c r="D62" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="4"/>
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
       <c r="F62" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -8479,7 +8604,9 @@
       <c r="D63" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E63" s="4"/>
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
       <c r="F63" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -8563,7 +8690,9 @@
       <c r="D64" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E64" s="4"/>
+      <c r="E64" s="4">
+        <v>0</v>
+      </c>
       <c r="F64" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -8647,7 +8776,9 @@
       <c r="D65" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E65" s="4"/>
+      <c r="E65" s="4">
+        <v>0</v>
+      </c>
       <c r="F65" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -8731,7 +8862,9 @@
       <c r="D66" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E66" s="4"/>
+      <c r="E66" s="4">
+        <v>0</v>
+      </c>
       <c r="F66" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -8815,7 +8948,9 @@
       <c r="D67" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E67" s="4"/>
+      <c r="E67" s="4">
+        <v>0</v>
+      </c>
       <c r="F67" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -8899,7 +9034,9 @@
       <c r="D68" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="4"/>
+      <c r="E68" s="4">
+        <v>0</v>
+      </c>
       <c r="F68" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -8983,7 +9120,9 @@
       <c r="D69" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E69" s="4"/>
+      <c r="E69" s="4">
+        <v>0</v>
+      </c>
       <c r="F69" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -9067,7 +9206,9 @@
       <c r="D70" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E70" s="4"/>
+      <c r="E70" s="4">
+        <v>0</v>
+      </c>
       <c r="F70" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -9151,7 +9292,9 @@
       <c r="D71" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E71" s="4"/>
+      <c r="E71" s="4">
+        <v>0</v>
+      </c>
       <c r="F71" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -9235,7 +9378,9 @@
       <c r="D72" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E72" s="4"/>
+      <c r="E72" s="4">
+        <v>0</v>
+      </c>
       <c r="F72" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -9319,7 +9464,9 @@
       <c r="D73" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E73" s="4"/>
+      <c r="E73" s="4">
+        <v>0</v>
+      </c>
       <c r="F73" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -9403,7 +9550,9 @@
       <c r="D74" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E74" s="4"/>
+      <c r="E74" s="4">
+        <v>0</v>
+      </c>
       <c r="F74" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -9487,7 +9636,9 @@
       <c r="D75" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E75" s="4"/>
+      <c r="E75" s="4">
+        <v>0</v>
+      </c>
       <c r="F75" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -9571,7 +9722,9 @@
       <c r="D76" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E76" s="4"/>
+      <c r="E76" s="4">
+        <v>0</v>
+      </c>
       <c r="F76" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -9655,7 +9808,9 @@
       <c r="D77" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E77" s="4"/>
+      <c r="E77" s="4">
+        <v>0</v>
+      </c>
       <c r="F77" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -9739,7 +9894,9 @@
       <c r="D78" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="4"/>
+      <c r="E78" s="4">
+        <v>0</v>
+      </c>
       <c r="F78" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -9823,7 +9980,9 @@
       <c r="D79" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E79" s="4"/>
+      <c r="E79" s="4">
+        <v>0</v>
+      </c>
       <c r="F79" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -9907,7 +10066,9 @@
       <c r="D80" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E80" s="4"/>
+      <c r="E80" s="4">
+        <v>0</v>
+      </c>
       <c r="F80" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -9991,7 +10152,9 @@
       <c r="D81" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E81" s="4"/>
+      <c r="E81" s="4">
+        <v>0</v>
+      </c>
       <c r="F81" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -10075,7 +10238,9 @@
       <c r="D82" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E82" s="4"/>
+      <c r="E82" s="4">
+        <v>0</v>
+      </c>
       <c r="F82" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -10159,7 +10324,9 @@
       <c r="D83" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E83" s="4"/>
+      <c r="E83" s="4">
+        <v>0</v>
+      </c>
       <c r="F83" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -10243,7 +10410,9 @@
       <c r="D84" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E84" s="4"/>
+      <c r="E84" s="4">
+        <v>0</v>
+      </c>
       <c r="F84" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -10327,7 +10496,9 @@
       <c r="D85" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E85" s="4"/>
+      <c r="E85" s="4">
+        <v>0</v>
+      </c>
       <c r="F85" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -10411,7 +10582,9 @@
       <c r="D86" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E86" s="4"/>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
       <c r="F86" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -10495,7 +10668,9 @@
       <c r="D87" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E87" s="4"/>
+      <c r="E87" s="4">
+        <v>0</v>
+      </c>
       <c r="F87" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -10579,7 +10754,9 @@
       <c r="D88" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E88" s="4"/>
+      <c r="E88" s="4">
+        <v>0</v>
+      </c>
       <c r="F88" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -10663,7 +10840,9 @@
       <c r="D89" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E89" s="4"/>
+      <c r="E89" s="4">
+        <v>0</v>
+      </c>
       <c r="F89" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -10747,7 +10926,9 @@
       <c r="D90" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E90" s="4"/>
+      <c r="E90" s="4">
+        <v>0</v>
+      </c>
       <c r="F90" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -10831,7 +11012,9 @@
       <c r="D91" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E91" s="4"/>
+      <c r="E91" s="4">
+        <v>0</v>
+      </c>
       <c r="F91" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -10915,7 +11098,9 @@
       <c r="D92" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E92" s="4"/>
+      <c r="E92" s="4">
+        <v>0</v>
+      </c>
       <c r="F92" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -10999,7 +11184,9 @@
       <c r="D93" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E93" s="4"/>
+      <c r="E93" s="4">
+        <v>0</v>
+      </c>
       <c r="F93" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -11083,7 +11270,9 @@
       <c r="D94" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E94" s="4"/>
+      <c r="E94" s="4">
+        <v>0</v>
+      </c>
       <c r="F94" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -11167,7 +11356,9 @@
       <c r="D95" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E95" s="4"/>
+      <c r="E95" s="4">
+        <v>0</v>
+      </c>
       <c r="F95" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -11251,7 +11442,9 @@
       <c r="D96" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E96" s="4"/>
+      <c r="E96" s="4">
+        <v>0</v>
+      </c>
       <c r="F96" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -11335,7 +11528,9 @@
       <c r="D97" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E97" s="4"/>
+      <c r="E97" s="4">
+        <v>0</v>
+      </c>
       <c r="F97" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -11419,7 +11614,9 @@
       <c r="D98" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E98" s="4"/>
+      <c r="E98" s="4">
+        <v>0</v>
+      </c>
       <c r="F98" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -11503,7 +11700,9 @@
       <c r="D99" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="4"/>
+      <c r="E99" s="4">
+        <v>0</v>
+      </c>
       <c r="F99" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -11587,7 +11786,9 @@
       <c r="D100" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E100" s="4"/>
+      <c r="E100" s="4">
+        <v>0</v>
+      </c>
       <c r="F100" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -11671,7 +11872,9 @@
       <c r="D101" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E101" s="4"/>
+      <c r="E101" s="4">
+        <v>0</v>
+      </c>
       <c r="F101" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -11755,7 +11958,9 @@
       <c r="D102" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E102" s="4"/>
+      <c r="E102" s="4">
+        <v>0</v>
+      </c>
       <c r="F102" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -11839,7 +12044,9 @@
       <c r="D103" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E103" s="4"/>
+      <c r="E103" s="4">
+        <v>0</v>
+      </c>
       <c r="F103" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -11923,7 +12130,9 @@
       <c r="D104" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="4"/>
+      <c r="E104" s="4">
+        <v>0</v>
+      </c>
       <c r="F104" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -12007,7 +12216,9 @@
       <c r="D105" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E105" s="4"/>
+      <c r="E105" s="4">
+        <v>0</v>
+      </c>
       <c r="F105" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -12091,7 +12302,9 @@
       <c r="D106" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E106" s="4"/>
+      <c r="E106" s="4">
+        <v>0</v>
+      </c>
       <c r="F106" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -12175,7 +12388,9 @@
       <c r="D107" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E107" s="4"/>
+      <c r="E107" s="4">
+        <v>0</v>
+      </c>
       <c r="F107" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -12259,7 +12474,9 @@
       <c r="D108" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E108" s="4"/>
+      <c r="E108" s="4">
+        <v>0</v>
+      </c>
       <c r="F108" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -12343,7 +12560,9 @@
       <c r="D109" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E109" s="4"/>
+      <c r="E109" s="4">
+        <v>0</v>
+      </c>
       <c r="F109" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -12427,7 +12646,9 @@
       <c r="D110" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E110" s="4"/>
+      <c r="E110" s="4">
+        <v>0</v>
+      </c>
       <c r="F110" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -12511,7 +12732,9 @@
       <c r="D111" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E111" s="4"/>
+      <c r="E111" s="4">
+        <v>0</v>
+      </c>
       <c r="F111" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -12595,7 +12818,9 @@
       <c r="D112" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E112" s="4"/>
+      <c r="E112" s="4">
+        <v>0</v>
+      </c>
       <c r="F112" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -12679,7 +12904,9 @@
       <c r="D113" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E113" s="4"/>
+      <c r="E113" s="4">
+        <v>0</v>
+      </c>
       <c r="F113" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -12763,7 +12990,9 @@
       <c r="D114" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E114" s="4"/>
+      <c r="E114" s="4">
+        <v>0</v>
+      </c>
       <c r="F114" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -12847,7 +13076,9 @@
       <c r="D115" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E115" s="4"/>
+      <c r="E115" s="4">
+        <v>0</v>
+      </c>
       <c r="F115" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -12931,7 +13162,9 @@
       <c r="D116" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E116" s="4"/>
+      <c r="E116" s="4">
+        <v>0</v>
+      </c>
       <c r="F116" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -13015,7 +13248,9 @@
       <c r="D117" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E117" s="4"/>
+      <c r="E117" s="4">
+        <v>0</v>
+      </c>
       <c r="F117" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -13099,7 +13334,9 @@
       <c r="D118" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E118" s="4"/>
+      <c r="E118" s="4">
+        <v>0</v>
+      </c>
       <c r="F118" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -13183,7 +13420,9 @@
       <c r="D119" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E119" s="4"/>
+      <c r="E119" s="4">
+        <v>0</v>
+      </c>
       <c r="F119" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -13267,7 +13506,9 @@
       <c r="D120" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E120" s="4"/>
+      <c r="E120" s="4">
+        <v>0</v>
+      </c>
       <c r="F120" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -13351,7 +13592,9 @@
       <c r="D121" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E121" s="4"/>
+      <c r="E121" s="4">
+        <v>0</v>
+      </c>
       <c r="F121" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -13435,7 +13678,9 @@
       <c r="D122" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E122" s="4"/>
+      <c r="E122" s="4">
+        <v>0</v>
+      </c>
       <c r="F122" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Manoel</v>
@@ -13519,7 +13764,9 @@
       <c r="D123" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E123" s="4"/>
+      <c r="E123" s="4">
+        <v>0</v>
+      </c>
       <c r="F123" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Geber</v>
@@ -13603,7 +13850,9 @@
       <c r="D124" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E124" s="4"/>
+      <c r="E124" s="4">
+        <v>0</v>
+      </c>
       <c r="F124" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -13687,7 +13936,9 @@
       <c r="D125" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E125" s="4"/>
+      <c r="E125" s="4">
+        <v>0</v>
+      </c>
       <c r="F125" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -13771,7 +14022,9 @@
       <c r="D126" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E126" s="4"/>
+      <c r="E126" s="4">
+        <v>0</v>
+      </c>
       <c r="F126" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -13855,7 +14108,9 @@
       <c r="D127" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E127" s="4"/>
+      <c r="E127" s="4">
+        <v>0</v>
+      </c>
       <c r="F127" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -13939,7 +14194,9 @@
       <c r="D128" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E128" s="4"/>
+      <c r="E128" s="4">
+        <v>0</v>
+      </c>
       <c r="F128" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -14023,7 +14280,9 @@
       <c r="D129" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E129" s="4"/>
+      <c r="E129" s="4">
+        <v>0</v>
+      </c>
       <c r="F129" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -14107,7 +14366,9 @@
       <c r="D130" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E130" s="4"/>
+      <c r="E130" s="4">
+        <v>0</v>
+      </c>
       <c r="F130" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -14191,7 +14452,9 @@
       <c r="D131" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E131" s="4"/>
+      <c r="E131" s="4">
+        <v>0</v>
+      </c>
       <c r="F131" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -14275,7 +14538,9 @@
       <c r="D132" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E132" s="4"/>
+      <c r="E132" s="4">
+        <v>0</v>
+      </c>
       <c r="F132" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -14359,7 +14624,9 @@
       <c r="D133" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E133" s="4"/>
+      <c r="E133" s="4">
+        <v>0</v>
+      </c>
       <c r="F133" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -14443,7 +14710,9 @@
       <c r="D134" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E134" s="4"/>
+      <c r="E134" s="4">
+        <v>0</v>
+      </c>
       <c r="F134" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -14527,7 +14796,9 @@
       <c r="D135" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E135" s="4"/>
+      <c r="E135" s="4">
+        <v>0</v>
+      </c>
       <c r="F135" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -14611,7 +14882,9 @@
       <c r="D136" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E136" s="4"/>
+      <c r="E136" s="4">
+        <v>0</v>
+      </c>
       <c r="F136" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -14695,7 +14968,9 @@
       <c r="D137" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E137" s="4"/>
+      <c r="E137" s="4">
+        <v>0</v>
+      </c>
       <c r="F137" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -14779,7 +15054,9 @@
       <c r="D138" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E138" s="4"/>
+      <c r="E138" s="4">
+        <v>0</v>
+      </c>
       <c r="F138" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -14863,7 +15140,9 @@
       <c r="D139" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="4"/>
+      <c r="E139" s="4">
+        <v>0</v>
+      </c>
       <c r="F139" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -14947,7 +15226,9 @@
       <c r="D140" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E140" s="4"/>
+      <c r="E140" s="4">
+        <v>0</v>
+      </c>
       <c r="F140" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -15031,7 +15312,9 @@
       <c r="D141" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E141" s="4"/>
+      <c r="E141" s="4">
+        <v>0</v>
+      </c>
       <c r="F141" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -15115,7 +15398,9 @@
       <c r="D142" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E142" s="4"/>
+      <c r="E142" s="4">
+        <v>0</v>
+      </c>
       <c r="F142" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -15199,7 +15484,9 @@
       <c r="D143" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E143" s="4"/>
+      <c r="E143" s="4">
+        <v>0</v>
+      </c>
       <c r="F143" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -15283,7 +15570,9 @@
       <c r="D144" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E144" s="4"/>
+      <c r="E144" s="4">
+        <v>0</v>
+      </c>
       <c r="F144" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -15367,7 +15656,9 @@
       <c r="D145" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E145" s="4"/>
+      <c r="E145" s="4">
+        <v>0</v>
+      </c>
       <c r="F145" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -15451,7 +15742,9 @@
       <c r="D146" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E146" s="4"/>
+      <c r="E146" s="4">
+        <v>0</v>
+      </c>
       <c r="F146" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -15535,7 +15828,9 @@
       <c r="D147" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E147" s="4"/>
+      <c r="E147" s="4">
+        <v>0</v>
+      </c>
       <c r="F147" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -15619,7 +15914,9 @@
       <c r="D148" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E148" s="4"/>
+      <c r="E148" s="4">
+        <v>0</v>
+      </c>
       <c r="F148" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -15703,7 +16000,9 @@
       <c r="D149" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E149" s="4"/>
+      <c r="E149" s="4">
+        <v>0</v>
+      </c>
       <c r="F149" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -15787,7 +16086,9 @@
       <c r="D150" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E150" s="4"/>
+      <c r="E150" s="4">
+        <v>0</v>
+      </c>
       <c r="F150" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -15871,7 +16172,9 @@
       <c r="D151" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E151" s="4"/>
+      <c r="E151" s="4">
+        <v>0</v>
+      </c>
       <c r="F151" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -15955,7 +16258,9 @@
       <c r="D152" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E152" s="4"/>
+      <c r="E152" s="4">
+        <v>0</v>
+      </c>
       <c r="F152" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -16039,7 +16344,9 @@
       <c r="D153" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E153" s="4"/>
+      <c r="E153" s="4">
+        <v>0</v>
+      </c>
       <c r="F153" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -16123,7 +16430,9 @@
       <c r="D154" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E154" s="4"/>
+      <c r="E154" s="4">
+        <v>0</v>
+      </c>
       <c r="F154" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -16207,7 +16516,9 @@
       <c r="D155" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E155" s="4"/>
+      <c r="E155" s="4">
+        <v>0</v>
+      </c>
       <c r="F155" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -16291,7 +16602,9 @@
       <c r="D156" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E156" s="4"/>
+      <c r="E156" s="4">
+        <v>0</v>
+      </c>
       <c r="F156" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -16375,7 +16688,9 @@
       <c r="D157" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E157" s="4"/>
+      <c r="E157" s="4">
+        <v>0</v>
+      </c>
       <c r="F157" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -16459,7 +16774,9 @@
       <c r="D158" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E158" s="4"/>
+      <c r="E158" s="4">
+        <v>0</v>
+      </c>
       <c r="F158" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -16543,7 +16860,9 @@
       <c r="D159" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E159" s="4"/>
+      <c r="E159" s="4">
+        <v>0</v>
+      </c>
       <c r="F159" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -16627,7 +16946,9 @@
       <c r="D160" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E160" s="4"/>
+      <c r="E160" s="4">
+        <v>0</v>
+      </c>
       <c r="F160" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -16711,7 +17032,9 @@
       <c r="D161" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E161" s="4"/>
+      <c r="E161" s="4">
+        <v>0</v>
+      </c>
       <c r="F161" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -16795,7 +17118,9 @@
       <c r="D162" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E162" s="4"/>
+      <c r="E162" s="4">
+        <v>0</v>
+      </c>
       <c r="F162" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -16879,7 +17204,9 @@
       <c r="D163" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E163" s="4"/>
+      <c r="E163" s="4">
+        <v>0</v>
+      </c>
       <c r="F163" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -16963,7 +17290,9 @@
       <c r="D164" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E164" s="4"/>
+      <c r="E164" s="4">
+        <v>0</v>
+      </c>
       <c r="F164" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -17047,7 +17376,9 @@
       <c r="D165" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E165" s="4"/>
+      <c r="E165" s="4">
+        <v>0</v>
+      </c>
       <c r="F165" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -17131,7 +17462,9 @@
       <c r="D166" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E166" s="4"/>
+      <c r="E166" s="4">
+        <v>0</v>
+      </c>
       <c r="F166" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -17215,7 +17548,9 @@
       <c r="D167" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E167" s="4"/>
+      <c r="E167" s="4">
+        <v>0</v>
+      </c>
       <c r="F167" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -17299,7 +17634,9 @@
       <c r="D168" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E168" s="4"/>
+      <c r="E168" s="4">
+        <v>0</v>
+      </c>
       <c r="F168" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -17383,7 +17720,9 @@
       <c r="D169" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E169" s="4"/>
+      <c r="E169" s="4">
+        <v>0</v>
+      </c>
       <c r="F169" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -17467,7 +17806,9 @@
       <c r="D170" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E170" s="4"/>
+      <c r="E170" s="4">
+        <v>0</v>
+      </c>
       <c r="F170" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -17551,7 +17892,9 @@
       <c r="D171" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E171" s="4"/>
+      <c r="E171" s="4">
+        <v>0</v>
+      </c>
       <c r="F171" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -17635,7 +17978,9 @@
       <c r="D172" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E172" s="4"/>
+      <c r="E172" s="4">
+        <v>0</v>
+      </c>
       <c r="F172" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -17719,7 +18064,9 @@
       <c r="D173" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E173" s="4"/>
+      <c r="E173" s="4">
+        <v>0</v>
+      </c>
       <c r="F173" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -17803,7 +18150,9 @@
       <c r="D174" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E174" s="4"/>
+      <c r="E174" s="4">
+        <v>0</v>
+      </c>
       <c r="F174" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -17887,7 +18236,9 @@
       <c r="D175" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E175" s="4"/>
+      <c r="E175" s="4">
+        <v>0</v>
+      </c>
       <c r="F175" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -17971,7 +18322,9 @@
       <c r="D176" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E176" s="4"/>
+      <c r="E176" s="4">
+        <v>0</v>
+      </c>
       <c r="F176" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -18055,7 +18408,9 @@
       <c r="D177" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E177" s="4"/>
+      <c r="E177" s="4">
+        <v>0</v>
+      </c>
       <c r="F177" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -18138,7 +18493,9 @@
       <c r="D178" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E178" s="4"/>
+      <c r="E178" s="4">
+        <v>0</v>
+      </c>
       <c r="F178" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -18222,7 +18579,9 @@
       <c r="D179" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E179" s="4"/>
+      <c r="E179" s="4">
+        <v>0</v>
+      </c>
       <c r="F179" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -18306,7 +18665,9 @@
       <c r="D180" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E180" s="4"/>
+      <c r="E180" s="4">
+        <v>0</v>
+      </c>
       <c r="F180" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -18390,7 +18751,9 @@
       <c r="D181" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E181" s="4"/>
+      <c r="E181" s="4">
+        <v>0</v>
+      </c>
       <c r="F181" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -18474,7 +18837,9 @@
       <c r="D182" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E182" s="4"/>
+      <c r="E182" s="4">
+        <v>0</v>
+      </c>
       <c r="F182" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -18558,7 +18923,9 @@
       <c r="D183" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E183" s="4"/>
+      <c r="E183" s="4">
+        <v>0</v>
+      </c>
       <c r="F183" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -18642,7 +19009,9 @@
       <c r="D184" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E184" s="4"/>
+      <c r="E184" s="4">
+        <v>0</v>
+      </c>
       <c r="F184" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -18726,7 +19095,9 @@
       <c r="D185" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E185" s="4"/>
+      <c r="E185" s="4">
+        <v>0</v>
+      </c>
       <c r="F185" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -18810,7 +19181,9 @@
       <c r="D186" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E186" s="4"/>
+      <c r="E186" s="4">
+        <v>0</v>
+      </c>
       <c r="F186" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -18894,7 +19267,9 @@
       <c r="D187" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E187" s="4"/>
+      <c r="E187" s="4">
+        <v>0</v>
+      </c>
       <c r="F187" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -18978,7 +19353,9 @@
       <c r="D188" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E188" s="4"/>
+      <c r="E188" s="4">
+        <v>0</v>
+      </c>
       <c r="F188" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -19062,7 +19439,9 @@
       <c r="D189" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E189" s="4"/>
+      <c r="E189" s="4">
+        <v>0</v>
+      </c>
       <c r="F189" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -19146,7 +19525,9 @@
       <c r="D190" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E190" s="4"/>
+      <c r="E190" s="4">
+        <v>0</v>
+      </c>
       <c r="F190" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
@@ -19230,7 +19611,9 @@
       <c r="D191" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E191" s="4"/>
+      <c r="E191" s="4">
+        <v>0</v>
+      </c>
       <c r="F191" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
@@ -19314,7 +19697,9 @@
       <c r="D192" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E192" s="4"/>
+      <c r="E192" s="4">
+        <v>0</v>
+      </c>
       <c r="F192" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -19398,7 +19783,9 @@
       <c r="D193" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E193" s="4"/>
+      <c r="E193" s="4">
+        <v>0</v>
+      </c>
       <c r="F193" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -19482,7 +19869,9 @@
       <c r="D194" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E194" s="4"/>
+      <c r="E194" s="4">
+        <v>0</v>
+      </c>
       <c r="F194" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
@@ -19566,7 +19955,9 @@
       <c r="D195" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E195" s="4"/>
+      <c r="E195" s="4">
+        <v>0</v>
+      </c>
       <c r="F195" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Wesley</v>
@@ -19650,7 +20041,9 @@
       <c r="D196" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E196" s="4"/>
+      <c r="E196" s="4">
+        <v>0</v>
+      </c>
       <c r="F196" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Jerson</v>
@@ -19734,7 +20127,9 @@
       <c r="D197" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E197" s="4"/>
+      <c r="E197" s="4">
+        <v>0</v>
+      </c>
       <c r="F197" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
@@ -19807,18 +20202,20 @@
       <c r="A198" s="8">
         <v>46262</v>
       </c>
-      <c r="B198" s="22">
+      <c r="B198" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C198" s="22">
+      <c r="C198" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E198" s="4"/>
+      <c r="E198" s="4">
+        <v>0</v>
+      </c>
       <c r="F198" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -19891,18 +20288,20 @@
       <c r="A199" s="8">
         <v>46262</v>
       </c>
-      <c r="B199" s="22">
+      <c r="B199" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C199" s="22">
+      <c r="C199" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E199" s="4"/>
+      <c r="E199" s="4">
+        <v>0</v>
+      </c>
       <c r="F199" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
@@ -19975,18 +20374,20 @@
       <c r="A200" s="8">
         <v>46263</v>
       </c>
-      <c r="B200" s="22">
+      <c r="B200" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C200" s="22">
+      <c r="C200" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E200" s="4"/>
+      <c r="E200" s="4">
+        <v>0</v>
+      </c>
       <c r="F200" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Sandro</v>
@@ -20059,18 +20460,20 @@
       <c r="A201" s="8">
         <v>46263</v>
       </c>
-      <c r="B201" s="22">
+      <c r="B201" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C201" s="22">
+      <c r="C201" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E201" s="4"/>
+      <c r="E201" s="4">
+        <v>0</v>
+      </c>
       <c r="F201" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
@@ -20143,18 +20546,20 @@
       <c r="A202" s="8">
         <v>46263</v>
       </c>
-      <c r="B202" s="22">
+      <c r="B202" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C202" s="22">
+      <c r="C202" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E202" s="4"/>
+      <c r="E202" s="4">
+        <v>0</v>
+      </c>
       <c r="F202" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
@@ -20223,8 +20628,954 @@
         <v>0</v>
       </c>
     </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A203" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B203" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C203" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E203" s="4">
+        <v>4</v>
+      </c>
+      <c r="F203" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G203" s="10">
+        <v>6554.17</v>
+      </c>
+      <c r="H203" s="10">
+        <v>152572.85</v>
+      </c>
+      <c r="I203" s="4">
+        <v>2600</v>
+      </c>
+      <c r="J203" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2957642857166266E-2</v>
+      </c>
+      <c r="K203" s="11">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="L203" s="15">
+        <v>0.70277777777777772</v>
+      </c>
+      <c r="M203" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41805555555555551</v>
+      </c>
+      <c r="N203" s="4">
+        <v>119035</v>
+      </c>
+      <c r="O203" s="4">
+        <v>119102</v>
+      </c>
+      <c r="P203" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q203" s="4">
+        <v>99</v>
+      </c>
+      <c r="R203" s="4">
+        <v>12</v>
+      </c>
+      <c r="S203" s="4">
+        <v>12</v>
+      </c>
+      <c r="T203" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U203" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V203" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W203" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X203" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y203" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A204" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B204" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C204" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E204" s="4">
+        <v>5</v>
+      </c>
+      <c r="F204" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G204" s="10">
+        <v>6755.44</v>
+      </c>
+      <c r="H204" s="10">
+        <v>89700.37</v>
+      </c>
+      <c r="I204" s="4">
+        <v>647</v>
+      </c>
+      <c r="J204" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5311172072088442E-2</v>
+      </c>
+      <c r="K204" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L204" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M204" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N204" s="4">
+        <v>142290</v>
+      </c>
+      <c r="O204" s="4">
+        <v>142370</v>
+      </c>
+      <c r="P204" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>80</v>
+      </c>
+      <c r="Q204" s="4">
+        <v>107</v>
+      </c>
+      <c r="R204" s="4">
+        <v>11</v>
+      </c>
+      <c r="S204" s="4">
+        <v>11</v>
+      </c>
+      <c r="T204" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U204" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V204" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W204" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X204" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y204" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A205" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B205" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C205" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E205" s="4">
+        <v>11</v>
+      </c>
+      <c r="F205" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G205" s="10">
+        <v>9866.33</v>
+      </c>
+      <c r="H205" s="10">
+        <v>147461.76000000001</v>
+      </c>
+      <c r="I205" s="4">
+        <v>1447</v>
+      </c>
+      <c r="J205" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.6907718991011625E-2</v>
+      </c>
+      <c r="K205" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L205" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M205" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222227</v>
+      </c>
+      <c r="N205" s="4">
+        <v>104557</v>
+      </c>
+      <c r="O205" s="4">
+        <v>104697</v>
+      </c>
+      <c r="P205" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>140</v>
+      </c>
+      <c r="Q205" s="4">
+        <v>196</v>
+      </c>
+      <c r="R205" s="4">
+        <v>23</v>
+      </c>
+      <c r="S205" s="4">
+        <v>23</v>
+      </c>
+      <c r="T205" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U205" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V205" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W205" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X205" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A206" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B206" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C206" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E206" s="4">
+        <v>1</v>
+      </c>
+      <c r="F206" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G206" s="10">
+        <v>10576.51</v>
+      </c>
+      <c r="H206" s="10">
+        <v>137277.46</v>
+      </c>
+      <c r="I206" s="4">
+        <v>1875</v>
+      </c>
+      <c r="J206" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.7044767582383891E-2</v>
+      </c>
+      <c r="K206" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L206" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M206" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N206" s="4">
+        <v>303720</v>
+      </c>
+      <c r="O206" s="4">
+        <v>303777</v>
+      </c>
+      <c r="P206" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>57</v>
+      </c>
+      <c r="Q206" s="4">
+        <v>248</v>
+      </c>
+      <c r="R206" s="4">
+        <v>22</v>
+      </c>
+      <c r="S206" s="4">
+        <v>22</v>
+      </c>
+      <c r="T206" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U206" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V206" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W206" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X206" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A207" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B207" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C207" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E207" s="4">
+        <v>5</v>
+      </c>
+      <c r="F207" s="10" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G207" s="10">
+        <v>1963.5</v>
+      </c>
+      <c r="H207" s="10">
+        <v>46524.72</v>
+      </c>
+      <c r="I207" s="4">
+        <v>109</v>
+      </c>
+      <c r="J207" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.220337059524485E-2</v>
+      </c>
+      <c r="K207" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L207" s="15">
+        <v>0.53125</v>
+      </c>
+      <c r="M207" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.23958333333333331</v>
+      </c>
+      <c r="N207" s="4">
+        <v>275192</v>
+      </c>
+      <c r="O207" s="4">
+        <v>275225</v>
+      </c>
+      <c r="P207" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>33</v>
+      </c>
+      <c r="Q207" s="4">
+        <v>12</v>
+      </c>
+      <c r="R207" s="4">
+        <v>3</v>
+      </c>
+      <c r="S207" s="4">
+        <v>3</v>
+      </c>
+      <c r="T207" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U207" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V207" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W207" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X207" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A208" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B208" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C208" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E208" s="4">
+        <v>5</v>
+      </c>
+      <c r="F208" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G208" s="10">
+        <v>1657.74</v>
+      </c>
+      <c r="H208" s="10">
+        <v>62424</v>
+      </c>
+      <c r="I208" s="4">
+        <v>565</v>
+      </c>
+      <c r="J208" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.6556132256824298E-2</v>
+      </c>
+      <c r="K208" s="11">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="L208" s="15">
+        <v>0.68541666666666667</v>
+      </c>
+      <c r="M208" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>7.0833333333333304E-2</v>
+      </c>
+      <c r="N208" s="4">
+        <v>275225</v>
+      </c>
+      <c r="O208" s="4">
+        <v>275261</v>
+      </c>
+      <c r="P208" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q208" s="4">
+        <v>92</v>
+      </c>
+      <c r="R208" s="4">
+        <v>5</v>
+      </c>
+      <c r="S208" s="4">
+        <v>5</v>
+      </c>
+      <c r="T208" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U208" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V208" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W208" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X208" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y208" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A209" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B209" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C209" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E209" s="4">
+        <v>3</v>
+      </c>
+      <c r="F209" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G209" s="10">
+        <v>6318.8</v>
+      </c>
+      <c r="H209" s="10">
+        <v>107463.47</v>
+      </c>
+      <c r="I209" s="4">
+        <v>1069</v>
+      </c>
+      <c r="J209" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8799515779641216E-2</v>
+      </c>
+      <c r="K209" s="11">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="L209" s="15">
+        <v>0.79305555555555551</v>
+      </c>
+      <c r="M209" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47013888888888883</v>
+      </c>
+      <c r="N209" s="4">
+        <v>279886</v>
+      </c>
+      <c r="O209" s="4">
+        <v>279962</v>
+      </c>
+      <c r="P209" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>76</v>
+      </c>
+      <c r="Q209" s="4">
+        <v>151</v>
+      </c>
+      <c r="R209" s="4">
+        <v>18</v>
+      </c>
+      <c r="S209" s="4">
+        <v>18</v>
+      </c>
+      <c r="T209" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U209" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V209" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W209" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X209" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y209" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A210" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B210" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C210" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E210" s="4">
+        <v>1</v>
+      </c>
+      <c r="F210" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G210" s="10">
+        <v>10769.09</v>
+      </c>
+      <c r="H210" s="10">
+        <v>179421.4</v>
+      </c>
+      <c r="I210" s="4">
+        <v>1091</v>
+      </c>
+      <c r="J210" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.002121263126918E-2</v>
+      </c>
+      <c r="K210" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L210" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M210" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40624999999999994</v>
+      </c>
+      <c r="N210" s="4">
+        <v>290873</v>
+      </c>
+      <c r="O210" s="4">
+        <v>290905</v>
+      </c>
+      <c r="P210" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>32</v>
+      </c>
+      <c r="Q210" s="4">
+        <v>253</v>
+      </c>
+      <c r="R210" s="4">
+        <v>8</v>
+      </c>
+      <c r="S210" s="4">
+        <v>8</v>
+      </c>
+      <c r="T210" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U210" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V210" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W210" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X210" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y210" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A211" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B211" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C211" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E211" s="4">
+        <v>1</v>
+      </c>
+      <c r="F211" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G211" s="10">
+        <v>4864.74</v>
+      </c>
+      <c r="H211" s="10">
+        <v>38078</v>
+      </c>
+      <c r="I211" s="4">
+        <v>518</v>
+      </c>
+      <c r="J211" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.12775723514890489</v>
+      </c>
+      <c r="K211" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L211" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M211" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="N211" s="4">
+        <v>124600</v>
+      </c>
+      <c r="O211" s="4">
+        <v>124648</v>
+      </c>
+      <c r="P211" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q211" s="4">
+        <v>122</v>
+      </c>
+      <c r="R211" s="4">
+        <v>7</v>
+      </c>
+      <c r="S211" s="4">
+        <v>7</v>
+      </c>
+      <c r="T211" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U211" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V211" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W211" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X211" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A212" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B212" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C212" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E212" s="4">
+        <v>1</v>
+      </c>
+      <c r="F212" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G212" s="10">
+        <v>1692.59</v>
+      </c>
+      <c r="H212" s="10">
+        <v>42377.94</v>
+      </c>
+      <c r="I212" s="4">
+        <v>48</v>
+      </c>
+      <c r="J212" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.9940355760567876E-2</v>
+      </c>
+      <c r="K212" s="11">
+        <v>0.29305555555555557</v>
+      </c>
+      <c r="L212" s="15">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="M212" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="N212" s="4">
+        <v>154765</v>
+      </c>
+      <c r="O212" s="4">
+        <v>154807</v>
+      </c>
+      <c r="P212" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q212" s="4">
+        <v>27</v>
+      </c>
+      <c r="R212" s="4">
+        <v>3</v>
+      </c>
+      <c r="S212" s="4">
+        <v>3</v>
+      </c>
+      <c r="T212" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U212" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V212" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W212" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X212" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y212" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A213" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B213" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C213" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>8</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E213" s="4">
+        <v>1</v>
+      </c>
+      <c r="F213" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G213" s="10">
+        <v>10862.98</v>
+      </c>
+      <c r="H213" s="10">
+        <v>120436.68</v>
+      </c>
+      <c r="I213" s="4">
+        <v>4594</v>
+      </c>
+      <c r="J213" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.0196607877267951E-2</v>
+      </c>
+      <c r="K213" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L213" s="15">
+        <v>0.71875</v>
+      </c>
+      <c r="M213" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N213" s="4">
+        <v>12828</v>
+      </c>
+      <c r="O213" s="4">
+        <v>12862</v>
+      </c>
+      <c r="P213" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>34</v>
+      </c>
+      <c r="Q213" s="4">
+        <v>9</v>
+      </c>
+      <c r="R213" s="4">
+        <v>1</v>
+      </c>
+      <c r="S213" s="4">
+        <v>1</v>
+      </c>
+      <c r="T213" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U213" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V213" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W213" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X213" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y213" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J202">
+  <conditionalFormatting sqref="J2:J213">
     <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -20232,7 +21583,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U202">
+  <conditionalFormatting sqref="U2:U213">
     <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -20255,7 +21606,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V202">
+  <conditionalFormatting sqref="V2:V213">
     <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -20281,7 +21632,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D202</xm:sqref>
+          <xm:sqref>D2:D213</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCE3C76-3E67-4B92-8759-B3736667E29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4D7DF9-6FE1-42DA-A6AD-8958D4059BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="76">
   <si>
     <t>Data</t>
   </si>
@@ -628,6 +628,509 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1254,509 +1757,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2106,51 +2106,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y213" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y223" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3185,38 +3185,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3225,7 +3225,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3239,7 +3239,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y213"/>
+  <dimension ref="A1:Y223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3359,7 +3359,7 @@
         <v>24</v>
       </c>
       <c r="E2" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3445,7 +3445,7 @@
         <v>34</v>
       </c>
       <c r="E3" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3531,7 +3531,7 @@
         <v>55</v>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3617,7 +3617,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3703,7 +3703,7 @@
         <v>36</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3789,7 +3789,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3875,7 +3875,7 @@
         <v>30</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -3961,7 +3961,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4047,7 +4047,7 @@
         <v>37</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4133,7 +4133,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4219,7 +4219,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F12" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4305,7 +4305,7 @@
         <v>26</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4391,7 +4391,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F14" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4477,7 +4477,7 @@
         <v>55</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4563,7 +4563,7 @@
         <v>36</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F16" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4649,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4735,7 +4735,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4821,7 +4821,7 @@
         <v>34</v>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4907,7 +4907,7 @@
         <v>34</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -4993,7 +4993,7 @@
         <v>32</v>
       </c>
       <c r="E21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5079,7 +5079,7 @@
         <v>26</v>
       </c>
       <c r="E22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5165,7 +5165,7 @@
         <v>30</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5251,7 +5251,7 @@
         <v>28</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F24" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5337,7 +5337,7 @@
         <v>29</v>
       </c>
       <c r="E25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5423,7 +5423,7 @@
         <v>26</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5509,7 +5509,7 @@
         <v>30</v>
       </c>
       <c r="E27" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5595,7 +5595,7 @@
         <v>22</v>
       </c>
       <c r="E28" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F28" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5681,7 +5681,7 @@
         <v>24</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F29" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5767,7 +5767,7 @@
         <v>55</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5853,7 +5853,7 @@
         <v>29</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -5939,7 +5939,7 @@
         <v>28</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F32" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6025,7 +6025,7 @@
         <v>32</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6111,7 +6111,7 @@
         <v>34</v>
       </c>
       <c r="E34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6197,7 +6197,7 @@
         <v>34</v>
       </c>
       <c r="E35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6283,7 +6283,7 @@
         <v>29</v>
       </c>
       <c r="E36" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F36" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6369,7 +6369,7 @@
         <v>24</v>
       </c>
       <c r="E37" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6455,7 +6455,7 @@
         <v>28</v>
       </c>
       <c r="E38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6541,7 +6541,7 @@
         <v>36</v>
       </c>
       <c r="E39" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6627,7 +6627,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6713,7 +6713,7 @@
         <v>22</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F41" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6799,7 +6799,7 @@
         <v>55</v>
       </c>
       <c r="E42" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F42" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6885,7 +6885,7 @@
         <v>26</v>
       </c>
       <c r="E43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -6971,7 +6971,7 @@
         <v>26</v>
       </c>
       <c r="E44" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7057,7 +7057,7 @@
         <v>34</v>
       </c>
       <c r="E45" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7143,7 +7143,7 @@
         <v>29</v>
       </c>
       <c r="E46" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7229,7 +7229,7 @@
         <v>34</v>
       </c>
       <c r="E47" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F47" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7315,7 +7315,7 @@
         <v>22</v>
       </c>
       <c r="E48" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F48" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7401,7 +7401,7 @@
         <v>55</v>
       </c>
       <c r="E49" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F49" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7487,7 +7487,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F50" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7573,7 +7573,7 @@
         <v>26</v>
       </c>
       <c r="E51" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F51" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7659,7 +7659,7 @@
         <v>36</v>
       </c>
       <c r="E52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7745,7 +7745,7 @@
         <v>28</v>
       </c>
       <c r="E53" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7831,7 +7831,7 @@
         <v>24</v>
       </c>
       <c r="E54" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -7917,7 +7917,7 @@
         <v>37</v>
       </c>
       <c r="E55" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8003,7 +8003,7 @@
         <v>55</v>
       </c>
       <c r="E56" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8089,7 +8089,7 @@
         <v>28</v>
       </c>
       <c r="E57" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8175,7 +8175,7 @@
         <v>22</v>
       </c>
       <c r="E58" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8261,7 +8261,7 @@
         <v>36</v>
       </c>
       <c r="E59" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8347,7 +8347,7 @@
         <v>34</v>
       </c>
       <c r="E60" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8433,7 +8433,7 @@
         <v>32</v>
       </c>
       <c r="E61" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F61" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8519,7 +8519,7 @@
         <v>24</v>
       </c>
       <c r="E62" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F62" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8605,7 +8605,7 @@
         <v>26</v>
       </c>
       <c r="E63" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F63" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8691,7 +8691,7 @@
         <v>29</v>
       </c>
       <c r="E64" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F64" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8777,7 +8777,7 @@
         <v>28</v>
       </c>
       <c r="E65" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F65" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8863,7 +8863,7 @@
         <v>22</v>
       </c>
       <c r="E66" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -8949,7 +8949,7 @@
         <v>29</v>
       </c>
       <c r="E67" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F67" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9035,7 +9035,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9121,7 +9121,7 @@
         <v>36</v>
       </c>
       <c r="E69" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9207,7 +9207,7 @@
         <v>34</v>
       </c>
       <c r="E70" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9293,7 +9293,7 @@
         <v>26</v>
       </c>
       <c r="E71" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F71" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9379,7 +9379,7 @@
         <v>55</v>
       </c>
       <c r="E72" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F72" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9465,7 +9465,7 @@
         <v>32</v>
       </c>
       <c r="E73" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F73" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9551,7 +9551,7 @@
         <v>36</v>
       </c>
       <c r="E74" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9637,7 +9637,7 @@
         <v>34</v>
       </c>
       <c r="E75" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F75" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9723,7 +9723,7 @@
         <v>22</v>
       </c>
       <c r="E76" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9809,7 +9809,7 @@
         <v>24</v>
       </c>
       <c r="E77" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9895,7 +9895,7 @@
         <v>26</v>
       </c>
       <c r="E78" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F78" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -9981,7 +9981,7 @@
         <v>28</v>
       </c>
       <c r="E79" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10067,7 +10067,7 @@
         <v>34</v>
       </c>
       <c r="E80" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10153,7 +10153,7 @@
         <v>29</v>
       </c>
       <c r="E81" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10239,7 +10239,7 @@
         <v>32</v>
       </c>
       <c r="E82" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F82" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10325,7 +10325,7 @@
         <v>55</v>
       </c>
       <c r="E83" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F83" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10411,7 +10411,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F84" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10497,7 +10497,7 @@
         <v>36</v>
       </c>
       <c r="E85" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10583,7 +10583,7 @@
         <v>26</v>
       </c>
       <c r="E86" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F86" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10669,7 +10669,7 @@
         <v>32</v>
       </c>
       <c r="E87" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F87" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10755,7 +10755,7 @@
         <v>22</v>
       </c>
       <c r="E88" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F88" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10841,7 +10841,7 @@
         <v>55</v>
       </c>
       <c r="E89" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F89" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -10927,7 +10927,7 @@
         <v>29</v>
       </c>
       <c r="E90" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11013,7 +11013,7 @@
         <v>28</v>
       </c>
       <c r="E91" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11099,7 +11099,7 @@
         <v>26</v>
       </c>
       <c r="E92" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11185,7 +11185,7 @@
         <v>30</v>
       </c>
       <c r="E93" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11271,7 +11271,7 @@
         <v>34</v>
       </c>
       <c r="E94" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11357,7 +11357,7 @@
         <v>55</v>
       </c>
       <c r="E95" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F95" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11443,7 +11443,7 @@
         <v>34</v>
       </c>
       <c r="E96" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11529,7 +11529,7 @@
         <v>28</v>
       </c>
       <c r="E97" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11615,7 +11615,7 @@
         <v>30</v>
       </c>
       <c r="E98" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F98" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11701,7 +11701,7 @@
         <v>29</v>
       </c>
       <c r="E99" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11787,7 +11787,7 @@
         <v>36</v>
       </c>
       <c r="E100" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11873,7 +11873,7 @@
         <v>22</v>
       </c>
       <c r="E101" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F101" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -11959,7 +11959,7 @@
         <v>26</v>
       </c>
       <c r="E102" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F102" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12045,7 +12045,7 @@
         <v>24</v>
       </c>
       <c r="E103" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F103" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12131,7 +12131,7 @@
         <v>32</v>
       </c>
       <c r="E104" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12217,7 +12217,7 @@
         <v>34</v>
       </c>
       <c r="E105" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12303,7 +12303,7 @@
         <v>30</v>
       </c>
       <c r="E106" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F106" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12389,7 +12389,7 @@
         <v>36</v>
       </c>
       <c r="E107" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12475,7 +12475,7 @@
         <v>24</v>
       </c>
       <c r="E108" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F108" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12561,7 +12561,7 @@
         <v>28</v>
       </c>
       <c r="E109" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12647,7 +12647,7 @@
         <v>22</v>
       </c>
       <c r="E110" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F110" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12733,7 +12733,7 @@
         <v>55</v>
       </c>
       <c r="E111" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12819,7 +12819,7 @@
         <v>29</v>
       </c>
       <c r="E112" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F112" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12905,7 +12905,7 @@
         <v>26</v>
       </c>
       <c r="E113" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F113" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -12991,7 +12991,7 @@
         <v>34</v>
       </c>
       <c r="E114" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13077,7 +13077,7 @@
         <v>22</v>
       </c>
       <c r="E115" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F115" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13163,7 +13163,7 @@
         <v>34</v>
       </c>
       <c r="E116" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13249,7 +13249,7 @@
         <v>36</v>
       </c>
       <c r="E117" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13335,7 +13335,7 @@
         <v>24</v>
       </c>
       <c r="E118" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F118" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13421,7 +13421,7 @@
         <v>26</v>
       </c>
       <c r="E119" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F119" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13507,7 +13507,7 @@
         <v>30</v>
       </c>
       <c r="E120" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F120" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13593,7 +13593,7 @@
         <v>29</v>
       </c>
       <c r="E121" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13602,7 +13602,7 @@
       <c r="G121" s="10">
         <v>34859.64</v>
       </c>
-      <c r="H121" s="4">
+      <c r="H121" s="10">
         <v>798551.77</v>
       </c>
       <c r="I121" s="4">
@@ -13679,7 +13679,7 @@
         <v>38</v>
       </c>
       <c r="E122" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13765,7 +13765,7 @@
         <v>37</v>
       </c>
       <c r="E123" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13851,7 +13851,7 @@
         <v>28</v>
       </c>
       <c r="E124" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -13937,7 +13937,7 @@
         <v>36</v>
       </c>
       <c r="E125" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F125" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14023,7 +14023,7 @@
         <v>55</v>
       </c>
       <c r="E126" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F126" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14109,7 +14109,7 @@
         <v>34</v>
       </c>
       <c r="E127" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14195,7 +14195,7 @@
         <v>30</v>
       </c>
       <c r="E128" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14281,7 +14281,7 @@
         <v>24</v>
       </c>
       <c r="E129" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14367,7 +14367,7 @@
         <v>22</v>
       </c>
       <c r="E130" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F130" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14453,7 +14453,7 @@
         <v>29</v>
       </c>
       <c r="E131" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F131" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14539,7 +14539,7 @@
         <v>36</v>
       </c>
       <c r="E132" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F132" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14625,7 +14625,7 @@
         <v>34</v>
       </c>
       <c r="E133" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14711,7 +14711,7 @@
         <v>28</v>
       </c>
       <c r="E134" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14797,7 +14797,7 @@
         <v>26</v>
       </c>
       <c r="E135" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F135" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14883,7 +14883,7 @@
         <v>55</v>
       </c>
       <c r="E136" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F136" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -14969,7 +14969,7 @@
         <v>30</v>
       </c>
       <c r="E137" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F137" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15055,7 +15055,7 @@
         <v>29</v>
       </c>
       <c r="E138" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15141,7 +15141,7 @@
         <v>55</v>
       </c>
       <c r="E139" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F139" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15227,7 +15227,7 @@
         <v>30</v>
       </c>
       <c r="E140" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15313,7 +15313,7 @@
         <v>26</v>
       </c>
       <c r="E141" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F141" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15399,7 +15399,7 @@
         <v>36</v>
       </c>
       <c r="E142" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15485,7 +15485,7 @@
         <v>32</v>
       </c>
       <c r="E143" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15571,7 +15571,7 @@
         <v>22</v>
       </c>
       <c r="E144" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F144" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15657,7 +15657,7 @@
         <v>34</v>
       </c>
       <c r="E145" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15743,7 +15743,7 @@
         <v>24</v>
       </c>
       <c r="E146" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15829,7 +15829,7 @@
         <v>30</v>
       </c>
       <c r="E147" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F147" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -15915,7 +15915,7 @@
         <v>30</v>
       </c>
       <c r="E148" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16001,7 +16001,7 @@
         <v>30</v>
       </c>
       <c r="E149" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16087,7 +16087,7 @@
         <v>32</v>
       </c>
       <c r="E150" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16173,7 +16173,7 @@
         <v>26</v>
       </c>
       <c r="E151" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F151" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16259,7 +16259,7 @@
         <v>36</v>
       </c>
       <c r="E152" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16345,7 +16345,7 @@
         <v>34</v>
       </c>
       <c r="E153" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16431,7 +16431,7 @@
         <v>29</v>
       </c>
       <c r="E154" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16517,7 +16517,7 @@
         <v>55</v>
       </c>
       <c r="E155" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F155" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16603,7 +16603,7 @@
         <v>22</v>
       </c>
       <c r="E156" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F156" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16689,7 +16689,7 @@
         <v>28</v>
       </c>
       <c r="E157" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F157" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16775,7 +16775,7 @@
         <v>24</v>
       </c>
       <c r="E158" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16861,7 +16861,7 @@
         <v>26</v>
       </c>
       <c r="E159" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F159" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -16947,7 +16947,7 @@
         <v>22</v>
       </c>
       <c r="E160" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F160" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17033,7 +17033,7 @@
         <v>55</v>
       </c>
       <c r="E161" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F161" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17119,7 +17119,7 @@
         <v>32</v>
       </c>
       <c r="E162" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F162" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17205,7 +17205,7 @@
         <v>24</v>
       </c>
       <c r="E163" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F163" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17291,7 +17291,7 @@
         <v>34</v>
       </c>
       <c r="E164" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17377,7 +17377,7 @@
         <v>36</v>
       </c>
       <c r="E165" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17463,7 +17463,7 @@
         <v>29</v>
       </c>
       <c r="E166" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F166" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17549,7 +17549,7 @@
         <v>28</v>
       </c>
       <c r="E167" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17635,7 +17635,7 @@
         <v>30</v>
       </c>
       <c r="E168" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17721,7 +17721,7 @@
         <v>30</v>
       </c>
       <c r="E169" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17807,7 +17807,7 @@
         <v>55</v>
       </c>
       <c r="E170" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F170" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17893,7 +17893,7 @@
         <v>28</v>
       </c>
       <c r="E171" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F171" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -17979,7 +17979,7 @@
         <v>26</v>
       </c>
       <c r="E172" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F172" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18065,7 +18065,7 @@
         <v>24</v>
       </c>
       <c r="E173" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F173" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18151,7 +18151,7 @@
         <v>22</v>
       </c>
       <c r="E174" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F174" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18237,7 +18237,7 @@
         <v>29</v>
       </c>
       <c r="E175" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18323,7 +18323,7 @@
         <v>32</v>
       </c>
       <c r="E176" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F176" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18409,7 +18409,7 @@
         <v>36</v>
       </c>
       <c r="E177" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18494,7 +18494,7 @@
         <v>34</v>
       </c>
       <c r="E178" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18580,7 +18580,7 @@
         <v>55</v>
       </c>
       <c r="E179" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F179" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18666,7 +18666,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F180" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18752,7 +18752,7 @@
         <v>34</v>
       </c>
       <c r="E181" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18838,7 +18838,7 @@
         <v>36</v>
       </c>
       <c r="E182" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -18924,7 +18924,7 @@
         <v>28</v>
       </c>
       <c r="E183" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19010,7 +19010,7 @@
         <v>22</v>
       </c>
       <c r="E184" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F184" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19182,7 +19182,7 @@
         <v>30</v>
       </c>
       <c r="E186" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19268,7 +19268,7 @@
         <v>32</v>
       </c>
       <c r="E187" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F187" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19354,7 +19354,7 @@
         <v>32</v>
       </c>
       <c r="E188" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F188" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19440,7 +19440,7 @@
         <v>26</v>
       </c>
       <c r="E189" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F189" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19526,7 +19526,7 @@
         <v>22</v>
       </c>
       <c r="E190" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F190" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19612,7 +19612,7 @@
         <v>29</v>
       </c>
       <c r="E191" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F191" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19698,7 +19698,7 @@
         <v>30</v>
       </c>
       <c r="E192" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19784,7 +19784,7 @@
         <v>34</v>
       </c>
       <c r="E193" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19870,7 +19870,7 @@
         <v>28</v>
       </c>
       <c r="E194" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -19956,7 +19956,7 @@
         <v>24</v>
       </c>
       <c r="E195" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F195" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20042,7 +20042,7 @@
         <v>32</v>
       </c>
       <c r="E196" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F196" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20128,7 +20128,7 @@
         <v>55</v>
       </c>
       <c r="E197" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F197" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20214,7 +20214,7 @@
         <v>26</v>
       </c>
       <c r="E198" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F198" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20300,7 +20300,7 @@
         <v>36</v>
       </c>
       <c r="E199" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20386,7 +20386,7 @@
         <v>30</v>
       </c>
       <c r="E200" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F200" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20472,7 +20472,7 @@
         <v>34</v>
       </c>
       <c r="E201" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20558,7 +20558,7 @@
         <v>26</v>
       </c>
       <c r="E202" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
@@ -20632,11 +20632,11 @@
       <c r="A203" s="8">
         <v>46265</v>
       </c>
-      <c r="B203" s="22">
+      <c r="B203" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C203" s="22">
+      <c r="C203" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -20718,11 +20718,11 @@
       <c r="A204" s="8">
         <v>46265</v>
       </c>
-      <c r="B204" s="22">
+      <c r="B204" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C204" s="22">
+      <c r="C204" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -20804,11 +20804,11 @@
       <c r="A205" s="8">
         <v>46265</v>
       </c>
-      <c r="B205" s="22">
+      <c r="B205" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C205" s="22">
+      <c r="C205" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -20890,11 +20890,11 @@
       <c r="A206" s="8">
         <v>46265</v>
       </c>
-      <c r="B206" s="22">
+      <c r="B206" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C206" s="22">
+      <c r="C206" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -20976,11 +20976,11 @@
       <c r="A207" s="8">
         <v>46265</v>
       </c>
-      <c r="B207" s="22">
+      <c r="B207" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C207" s="22">
+      <c r="C207" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21062,11 +21062,11 @@
       <c r="A208" s="8">
         <v>46265</v>
       </c>
-      <c r="B208" s="22">
+      <c r="B208" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C208" s="22">
+      <c r="C208" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21148,11 +21148,11 @@
       <c r="A209" s="8">
         <v>46265</v>
       </c>
-      <c r="B209" s="22">
+      <c r="B209" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C209" s="22">
+      <c r="C209" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21234,11 +21234,11 @@
       <c r="A210" s="8">
         <v>46265</v>
       </c>
-      <c r="B210" s="22">
+      <c r="B210" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C210" s="22">
+      <c r="C210" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21320,11 +21320,11 @@
       <c r="A211" s="8">
         <v>46265</v>
       </c>
-      <c r="B211" s="22">
+      <c r="B211" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C211" s="22">
+      <c r="C211" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21406,11 +21406,11 @@
       <c r="A212" s="8">
         <v>46265</v>
       </c>
-      <c r="B212" s="22">
+      <c r="B212" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C212" s="22">
+      <c r="C212" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21492,11 +21492,11 @@
       <c r="A213" s="8">
         <v>46265</v>
       </c>
-      <c r="B213" s="22">
+      <c r="B213" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C213" s="22">
+      <c r="C213" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>8</v>
       </c>
@@ -21574,40 +21574,900 @@
         <v>0</v>
       </c>
     </row>
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A214" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B214" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C214" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E214" s="4">
+        <v>11</v>
+      </c>
+      <c r="F214" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G214" s="10">
+        <v>6588.3</v>
+      </c>
+      <c r="H214" s="10">
+        <v>166308.68</v>
+      </c>
+      <c r="I214" s="4">
+        <v>1123</v>
+      </c>
+      <c r="J214" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.9614889613699057E-2</v>
+      </c>
+      <c r="K214" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L214" s="15">
+        <v>0.73472222222222228</v>
+      </c>
+      <c r="M214" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46388888888888896</v>
+      </c>
+      <c r="N214" s="4">
+        <v>142371</v>
+      </c>
+      <c r="O214" s="4">
+        <v>142526</v>
+      </c>
+      <c r="P214" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>155</v>
+      </c>
+      <c r="Q214" s="4">
+        <v>146</v>
+      </c>
+      <c r="R214" s="4">
+        <v>16</v>
+      </c>
+      <c r="S214" s="4">
+        <v>16</v>
+      </c>
+      <c r="T214" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U214" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V214" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W214" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X214" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y214" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A215" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B215" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C215" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E215" s="4">
+        <v>1</v>
+      </c>
+      <c r="F215" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G215" s="10">
+        <v>542.14</v>
+      </c>
+      <c r="H215" s="10">
+        <v>6099.54</v>
+      </c>
+      <c r="I215" s="4">
+        <v>57</v>
+      </c>
+      <c r="J215" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.8882112421592441E-2</v>
+      </c>
+      <c r="K215" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L215" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M215" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N215" s="4">
+        <v>154807</v>
+      </c>
+      <c r="O215" s="4">
+        <v>154845</v>
+      </c>
+      <c r="P215" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q215" s="4">
+        <v>10</v>
+      </c>
+      <c r="R215" s="4">
+        <v>1</v>
+      </c>
+      <c r="S215" s="4">
+        <v>1</v>
+      </c>
+      <c r="T215" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U215" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V215" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W215" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X215" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y215" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A216" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B216" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C216" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E216" s="4">
+        <v>5</v>
+      </c>
+      <c r="F216" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G216" s="10">
+        <v>6668.43</v>
+      </c>
+      <c r="H216" s="10">
+        <v>110103.48</v>
+      </c>
+      <c r="I216" s="4">
+        <v>205</v>
+      </c>
+      <c r="J216" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0565115653020238E-2</v>
+      </c>
+      <c r="K216" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L216" s="15">
+        <v>0.81944444444444442</v>
+      </c>
+      <c r="M216" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N216" s="4">
+        <v>12862</v>
+      </c>
+      <c r="O216" s="4">
+        <v>12964</v>
+      </c>
+      <c r="P216" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>102</v>
+      </c>
+      <c r="Q216" s="4">
+        <v>205</v>
+      </c>
+      <c r="R216" s="4">
+        <v>21</v>
+      </c>
+      <c r="S216" s="4">
+        <v>21</v>
+      </c>
+      <c r="T216" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U216" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V216" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W216" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X216" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y216" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A217" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B217" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C217" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E217" s="4">
+        <v>1</v>
+      </c>
+      <c r="F217" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G217" s="10">
+        <v>23158.1</v>
+      </c>
+      <c r="H217" s="10">
+        <v>477368.73</v>
+      </c>
+      <c r="I217" s="4">
+        <v>2798</v>
+      </c>
+      <c r="J217" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8511975218820891E-2</v>
+      </c>
+      <c r="K217" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L217" s="15">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="M217" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="N217" s="4">
+        <v>104697</v>
+      </c>
+      <c r="O217" s="4">
+        <v>104737</v>
+      </c>
+      <c r="P217" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q217" s="4">
+        <v>528</v>
+      </c>
+      <c r="R217" s="4">
+        <v>23</v>
+      </c>
+      <c r="S217" s="4">
+        <v>23</v>
+      </c>
+      <c r="T217" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U217" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V217" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W217" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X217" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y217" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A218" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B218" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C218" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E218" s="4">
+        <v>1</v>
+      </c>
+      <c r="F218" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G218" s="10">
+        <v>709.78</v>
+      </c>
+      <c r="H218" s="10">
+        <v>16994.12</v>
+      </c>
+      <c r="I218" s="4">
+        <v>226</v>
+      </c>
+      <c r="J218" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1766210901182294E-2</v>
+      </c>
+      <c r="K218" s="11">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L218" s="15">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="M218" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>5.8333333333333348E-2</v>
+      </c>
+      <c r="N218" s="4">
+        <v>11749</v>
+      </c>
+      <c r="O218" s="4">
+        <v>11758</v>
+      </c>
+      <c r="P218" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>9</v>
+      </c>
+      <c r="Q218" s="4">
+        <v>20</v>
+      </c>
+      <c r="R218" s="4">
+        <v>1</v>
+      </c>
+      <c r="S218" s="4">
+        <v>1</v>
+      </c>
+      <c r="T218" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U218" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V218" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W218" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X218" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y218" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A219" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B219" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C219" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E219" s="4">
+        <v>1</v>
+      </c>
+      <c r="F219" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G219" s="10">
+        <v>10475.75</v>
+      </c>
+      <c r="H219" s="10">
+        <v>260971.29</v>
+      </c>
+      <c r="I219" s="4">
+        <v>1550</v>
+      </c>
+      <c r="J219" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0141388732837242E-2</v>
+      </c>
+      <c r="K219" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L219" s="15">
+        <v>0.83819444444444446</v>
+      </c>
+      <c r="M219" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5361111111111112</v>
+      </c>
+      <c r="N219" s="4">
+        <v>303777</v>
+      </c>
+      <c r="O219" s="4">
+        <v>303898</v>
+      </c>
+      <c r="P219" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>121</v>
+      </c>
+      <c r="Q219" s="4">
+        <v>253</v>
+      </c>
+      <c r="R219" s="4">
+        <v>25</v>
+      </c>
+      <c r="S219" s="4">
+        <v>25</v>
+      </c>
+      <c r="T219" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U219" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V219" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W219" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X219" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y219" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A220" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B220" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C220" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E220" s="4">
+        <v>1</v>
+      </c>
+      <c r="F220" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G220" s="10">
+        <v>8407.9599999999991</v>
+      </c>
+      <c r="H220" s="10">
+        <v>267389.46000000002</v>
+      </c>
+      <c r="I220" s="4">
+        <v>1071</v>
+      </c>
+      <c r="J220" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.1444620143217306E-2</v>
+      </c>
+      <c r="K220" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L220" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M220" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="N220" s="4">
+        <v>290905</v>
+      </c>
+      <c r="O220" s="4">
+        <v>290948</v>
+      </c>
+      <c r="P220" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q220" s="4">
+        <v>21</v>
+      </c>
+      <c r="R220" s="4">
+        <v>10</v>
+      </c>
+      <c r="S220" s="4">
+        <v>10</v>
+      </c>
+      <c r="T220" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U220" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V220" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W220" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X220" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y220" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A221" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B221" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C221" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E221" s="4">
+        <v>3</v>
+      </c>
+      <c r="F221" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G221" s="10">
+        <v>5715.23</v>
+      </c>
+      <c r="H221" s="10">
+        <v>88671.92</v>
+      </c>
+      <c r="I221" s="4">
+        <v>544</v>
+      </c>
+      <c r="J221" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4453662444661164E-2</v>
+      </c>
+      <c r="K221" s="11">
+        <v>0.31597222222222221</v>
+      </c>
+      <c r="L221" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M221" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38541666666666663</v>
+      </c>
+      <c r="N221" s="4">
+        <v>279962</v>
+      </c>
+      <c r="O221" s="4">
+        <v>280018</v>
+      </c>
+      <c r="P221" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q221" s="4">
+        <v>114</v>
+      </c>
+      <c r="R221" s="4">
+        <v>17</v>
+      </c>
+      <c r="S221" s="4">
+        <v>17</v>
+      </c>
+      <c r="T221" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U221" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V221" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W221" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X221" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y221" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A222" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B222" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C222" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E222" s="4">
+        <v>1</v>
+      </c>
+      <c r="F222" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G222" s="10">
+        <v>5172.97</v>
+      </c>
+      <c r="H222" s="10">
+        <v>73651.199999999997</v>
+      </c>
+      <c r="I222" s="4">
+        <v>2364</v>
+      </c>
+      <c r="J222" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.0236058611400767E-2</v>
+      </c>
+      <c r="K222" s="11">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="L222" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M222" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="N222" s="4">
+        <v>275261</v>
+      </c>
+      <c r="O222" s="4">
+        <v>275291</v>
+      </c>
+      <c r="P222" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q222" s="4">
+        <v>548</v>
+      </c>
+      <c r="R222" s="4">
+        <v>3</v>
+      </c>
+      <c r="S222" s="4">
+        <v>3</v>
+      </c>
+      <c r="T222" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U222" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V222" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W222" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X222" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y222" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A223" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B223" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C223" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E223" s="4">
+        <v>4</v>
+      </c>
+      <c r="F223" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G223" s="10">
+        <v>14619.28</v>
+      </c>
+      <c r="H223" s="10">
+        <v>184569.31</v>
+      </c>
+      <c r="I223" s="4">
+        <v>3034</v>
+      </c>
+      <c r="J223" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.9207534557072357E-2</v>
+      </c>
+      <c r="K223" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L223" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M223" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222215</v>
+      </c>
+      <c r="N223" s="4">
+        <v>119102</v>
+      </c>
+      <c r="O223" s="4">
+        <v>119159</v>
+      </c>
+      <c r="P223" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>57</v>
+      </c>
+      <c r="Q223" s="4">
+        <v>280</v>
+      </c>
+      <c r="R223" s="4">
+        <v>29</v>
+      </c>
+      <c r="S223" s="4">
+        <v>29</v>
+      </c>
+      <c r="T223" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U223" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V223" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W223" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X223" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y223" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J213">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J223">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U213">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U223">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V213">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V223">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -21616,7 +22476,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21632,7 +22492,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D213</xm:sqref>
+          <xm:sqref>D2:D223</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4D7DF9-6FE1-42DA-A6AD-8958D4059BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01163C64-4135-4095-9CB1-CCFE4BA08316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="76">
   <si>
     <t>Data</t>
   </si>
@@ -551,7 +551,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="145">
     <dxf>
       <font>
         <b/>
@@ -1595,6 +1595,83 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2063,50 +2140,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V9" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y223" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y233" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
@@ -3185,38 +3262,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3225,7 +3302,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3239,7 +3316,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y223"/>
+  <dimension ref="A1:Y233"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -21578,11 +21655,11 @@
       <c r="A214" s="8">
         <v>46266</v>
       </c>
-      <c r="B214" s="22">
+      <c r="B214" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C214" s="22">
+      <c r="C214" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -21664,11 +21741,11 @@
       <c r="A215" s="8">
         <v>46266</v>
       </c>
-      <c r="B215" s="22">
+      <c r="B215" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C215" s="22">
+      <c r="C215" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -21750,11 +21827,11 @@
       <c r="A216" s="8">
         <v>46266</v>
       </c>
-      <c r="B216" s="22">
+      <c r="B216" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C216" s="22">
+      <c r="C216" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -21836,11 +21913,11 @@
       <c r="A217" s="8">
         <v>46266</v>
       </c>
-      <c r="B217" s="22">
+      <c r="B217" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C217" s="22">
+      <c r="C217" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -21922,11 +21999,11 @@
       <c r="A218" s="8">
         <v>46266</v>
       </c>
-      <c r="B218" s="22">
+      <c r="B218" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C218" s="22">
+      <c r="C218" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22008,11 +22085,11 @@
       <c r="A219" s="8">
         <v>46266</v>
       </c>
-      <c r="B219" s="22">
+      <c r="B219" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C219" s="22">
+      <c r="C219" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22094,11 +22171,11 @@
       <c r="A220" s="8">
         <v>46266</v>
       </c>
-      <c r="B220" s="22">
+      <c r="B220" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C220" s="22">
+      <c r="C220" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22180,11 +22257,11 @@
       <c r="A221" s="8">
         <v>46266</v>
       </c>
-      <c r="B221" s="22">
+      <c r="B221" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C221" s="22">
+      <c r="C221" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22266,11 +22343,11 @@
       <c r="A222" s="8">
         <v>46266</v>
       </c>
-      <c r="B222" s="22">
+      <c r="B222" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C222" s="22">
+      <c r="C222" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22352,11 +22429,11 @@
       <c r="A223" s="8">
         <v>46266</v>
       </c>
-      <c r="B223" s="22">
+      <c r="B223" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C223" s="22">
+      <c r="C223" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22434,8 +22511,868 @@
         <v>0</v>
       </c>
     </row>
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A224" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B224" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C224" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E224" s="4">
+        <v>2</v>
+      </c>
+      <c r="F224" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G224" s="10">
+        <v>11956.81</v>
+      </c>
+      <c r="H224" s="10">
+        <v>188606.24</v>
+      </c>
+      <c r="I224" s="4">
+        <v>1857</v>
+      </c>
+      <c r="J224" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3395622541438712E-2</v>
+      </c>
+      <c r="K224" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L224" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M224" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N224" s="4">
+        <v>119159</v>
+      </c>
+      <c r="O224" s="4">
+        <v>119218</v>
+      </c>
+      <c r="P224" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q224" s="4">
+        <v>293</v>
+      </c>
+      <c r="R224" s="4">
+        <v>45</v>
+      </c>
+      <c r="S224" s="4">
+        <v>45</v>
+      </c>
+      <c r="T224" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U224" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V224" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W224" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X224" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y224" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A225" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B225" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C225" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E225" s="4">
+        <v>11</v>
+      </c>
+      <c r="F225" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G225" s="10">
+        <v>12929.96</v>
+      </c>
+      <c r="H225" s="10">
+        <v>196157.74</v>
+      </c>
+      <c r="I225" s="4">
+        <v>2212</v>
+      </c>
+      <c r="J225" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5916134637358681E-2</v>
+      </c>
+      <c r="K225" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L225" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M225" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="N225" s="4">
+        <v>142526</v>
+      </c>
+      <c r="O225" s="4">
+        <v>142664</v>
+      </c>
+      <c r="P225" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>138</v>
+      </c>
+      <c r="Q225" s="4">
+        <v>371</v>
+      </c>
+      <c r="R225" s="4">
+        <v>29</v>
+      </c>
+      <c r="S225" s="4">
+        <v>29</v>
+      </c>
+      <c r="T225" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U225" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V225" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W225" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X225" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y225" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A226" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B226" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C226" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E226" s="4">
+        <v>5</v>
+      </c>
+      <c r="F226" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G226" s="10">
+        <v>6644.17</v>
+      </c>
+      <c r="H226" s="10">
+        <v>127234.81</v>
+      </c>
+      <c r="I226" s="4">
+        <v>1206</v>
+      </c>
+      <c r="J226" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2219750239733922E-2</v>
+      </c>
+      <c r="K226" s="11">
+        <v>0.27638888888888891</v>
+      </c>
+      <c r="L226" s="15">
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="M226" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43541666666666667</v>
+      </c>
+      <c r="N226" s="4">
+        <v>104737</v>
+      </c>
+      <c r="O226" s="4">
+        <v>104767</v>
+      </c>
+      <c r="P226" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q226" s="4">
+        <v>258</v>
+      </c>
+      <c r="R226" s="4">
+        <v>7</v>
+      </c>
+      <c r="S226" s="4">
+        <v>7</v>
+      </c>
+      <c r="T226" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U226" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V226" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W226" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X226" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y226" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A227" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B227" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C227" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E227" s="4">
+        <v>1</v>
+      </c>
+      <c r="F227" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G227" s="10">
+        <v>842.93</v>
+      </c>
+      <c r="H227" s="10">
+        <v>29652.35</v>
+      </c>
+      <c r="I227" s="4">
+        <v>62</v>
+      </c>
+      <c r="J227" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.8427089252622474E-2</v>
+      </c>
+      <c r="K227" s="11">
+        <v>0.29305555555555557</v>
+      </c>
+      <c r="L227" s="15">
+        <v>0.78611111111111109</v>
+      </c>
+      <c r="M227" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49305555555555552</v>
+      </c>
+      <c r="N227" s="4">
+        <v>154854</v>
+      </c>
+      <c r="O227" s="4">
+        <v>154891</v>
+      </c>
+      <c r="P227" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q227" s="4">
+        <v>19</v>
+      </c>
+      <c r="R227" s="4">
+        <v>1</v>
+      </c>
+      <c r="S227" s="4">
+        <v>1</v>
+      </c>
+      <c r="T227" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U227" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V227" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W227" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X227" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y227" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A228" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B228" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C228" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E228" s="4">
+        <v>1</v>
+      </c>
+      <c r="F228" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G228" s="10">
+        <v>15120.59</v>
+      </c>
+      <c r="H228" s="10">
+        <v>107062.53</v>
+      </c>
+      <c r="I228" s="4">
+        <v>1351</v>
+      </c>
+      <c r="J228" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.14123139066487594</v>
+      </c>
+      <c r="K228" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L228" s="15">
+        <v>0.78402777777777777</v>
+      </c>
+      <c r="M228" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49236111111111108</v>
+      </c>
+      <c r="N228" s="4">
+        <v>275291</v>
+      </c>
+      <c r="O228" s="4">
+        <v>275378</v>
+      </c>
+      <c r="P228" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>87</v>
+      </c>
+      <c r="Q228" s="4">
+        <v>573</v>
+      </c>
+      <c r="R228" s="4">
+        <v>2</v>
+      </c>
+      <c r="S228" s="4">
+        <v>2</v>
+      </c>
+      <c r="T228" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U228" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V228" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W228" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="X228" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y228" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A229" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B229" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C229" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E229" s="4">
+        <v>5</v>
+      </c>
+      <c r="F229" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G229" s="10">
+        <v>13060.73</v>
+      </c>
+      <c r="H229" s="10">
+        <v>274114.09000000003</v>
+      </c>
+      <c r="I229" s="4">
+        <v>2366</v>
+      </c>
+      <c r="J229" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.7647058201203733E-2</v>
+      </c>
+      <c r="K229" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L229" s="15">
+        <v>0.8208333333333333</v>
+      </c>
+      <c r="M229" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52916666666666656</v>
+      </c>
+      <c r="N229" s="4">
+        <v>124660</v>
+      </c>
+      <c r="O229" s="4">
+        <v>124753</v>
+      </c>
+      <c r="P229" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>93</v>
+      </c>
+      <c r="Q229" s="4">
+        <v>527</v>
+      </c>
+      <c r="R229" s="4">
+        <v>33</v>
+      </c>
+      <c r="S229" s="4">
+        <v>32</v>
+      </c>
+      <c r="T229" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U229" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="V229" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W229" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X229" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y229" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A230" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B230" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C230" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E230" s="4">
+        <v>1</v>
+      </c>
+      <c r="F230" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G230" s="10">
+        <v>9382.2999999999993</v>
+      </c>
+      <c r="H230" s="10">
+        <v>127468.07</v>
+      </c>
+      <c r="I230" s="4">
+        <v>1627</v>
+      </c>
+      <c r="J230" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3605099692809331E-2</v>
+      </c>
+      <c r="K230" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L230" s="15">
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="M230" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.22222222222222227</v>
+      </c>
+      <c r="N230" s="4">
+        <v>280018</v>
+      </c>
+      <c r="O230" s="4">
+        <v>280060</v>
+      </c>
+      <c r="P230" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q230" s="4">
+        <v>166</v>
+      </c>
+      <c r="R230" s="4">
+        <v>13</v>
+      </c>
+      <c r="S230" s="4">
+        <v>13</v>
+      </c>
+      <c r="T230" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U230" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V230" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W230" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X230" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y230" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A231" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B231" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C231" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E231" s="4">
+        <v>1</v>
+      </c>
+      <c r="F231" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G231" s="10">
+        <v>6934.2</v>
+      </c>
+      <c r="H231" s="10">
+        <v>152491.51999999999</v>
+      </c>
+      <c r="I231" s="4">
+        <v>1956</v>
+      </c>
+      <c r="J231" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5472692514311616E-2</v>
+      </c>
+      <c r="K231" s="11">
+        <v>0.59027777777777779</v>
+      </c>
+      <c r="L231" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M231" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.24305555555555558</v>
+      </c>
+      <c r="N231" s="4">
+        <v>280060</v>
+      </c>
+      <c r="O231" s="4">
+        <v>280095</v>
+      </c>
+      <c r="P231" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q231" s="4">
+        <v>211</v>
+      </c>
+      <c r="R231" s="4">
+        <v>7</v>
+      </c>
+      <c r="S231" s="4">
+        <v>7</v>
+      </c>
+      <c r="T231" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U231" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V231" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W231" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X231" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y231" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A232" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B232" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C232" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E232" s="4">
+        <v>2</v>
+      </c>
+      <c r="F232" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G232" s="10">
+        <v>12262.11</v>
+      </c>
+      <c r="H232" s="10">
+        <v>213653.1</v>
+      </c>
+      <c r="I232" s="4">
+        <v>2491</v>
+      </c>
+      <c r="J232" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.7392614476457396E-2</v>
+      </c>
+      <c r="K232" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L232" s="15">
+        <v>0.76458333333333328</v>
+      </c>
+      <c r="M232" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4729166666666666</v>
+      </c>
+      <c r="N232" s="4">
+        <v>290948</v>
+      </c>
+      <c r="O232" s="4">
+        <v>291032</v>
+      </c>
+      <c r="P232" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>84</v>
+      </c>
+      <c r="Q232" s="4">
+        <v>258</v>
+      </c>
+      <c r="R232" s="4">
+        <v>12</v>
+      </c>
+      <c r="S232" s="4">
+        <v>12</v>
+      </c>
+      <c r="T232" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U232" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V232" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W232" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X232" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y232" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A233" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B233" s="22">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C233" s="22">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E233" s="4">
+        <v>1</v>
+      </c>
+      <c r="F233" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G233" s="10">
+        <v>10367.19</v>
+      </c>
+      <c r="H233" s="10">
+        <v>161135.26999999999</v>
+      </c>
+      <c r="I233" s="4">
+        <v>1532</v>
+      </c>
+      <c r="J233" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4338428203831483E-2</v>
+      </c>
+      <c r="K233" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L233" s="15">
+        <v>0.80694444444444446</v>
+      </c>
+      <c r="M233" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="N233" s="4">
+        <v>303898</v>
+      </c>
+      <c r="O233" s="4">
+        <v>304009</v>
+      </c>
+      <c r="P233" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>111</v>
+      </c>
+      <c r="Q233" s="4">
+        <v>222</v>
+      </c>
+      <c r="R233" s="4">
+        <v>26</v>
+      </c>
+      <c r="S233" s="4">
+        <v>26</v>
+      </c>
+      <c r="T233" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U233" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V233" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W233" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X233" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y233" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J223">
+  <conditionalFormatting sqref="J2:J233">
     <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -22443,7 +23380,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U223">
+  <conditionalFormatting sqref="U2:U233">
     <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -22466,7 +23403,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V223">
+  <conditionalFormatting sqref="V2:V233">
     <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -22492,7 +23429,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D223</xm:sqref>
+          <xm:sqref>D2:D233</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01163C64-4135-4095-9CB1-CCFE4BA08316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA032B3-D8F7-486D-8C75-424AB235EC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="77">
   <si>
     <t>Data</t>
   </si>
@@ -272,6 +272,9 @@
   <si>
     <t>Rota</t>
   </si>
+  <si>
+    <t>13,13,13,13,13,13,13,13</t>
+  </si>
 </sst>
 </file>
 
@@ -474,7 +477,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -533,15 +536,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -551,7 +563,59 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="134">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -933,7 +997,7 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -950,7 +1014,7 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1131,83 +1195,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1989,40 +1976,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -2036,21 +1989,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2140,94 +2078,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V9" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="2"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="126"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="0" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="1" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="125"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="124" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="123"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="122"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="121">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="120" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="119" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="118"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="117"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="116"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="115">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="114" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="113" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="112"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="111"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y233" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y242" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" headerRowBorderDxfId="40" tableBorderDxfId="41" totalsRowBorderDxfId="39">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="38"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="37">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="36">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="33">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="32" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="31" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="29" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="26">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="23">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="19">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="18" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="17">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="15"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2659,17 +2597,17 @@
   <dimension ref="A1:V9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13" style="27" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="27" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" style="21" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" customWidth="1"/>
     <col min="15" max="15" width="15.5703125" customWidth="1"/>
@@ -2683,7 +2621,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2695,10 +2633,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -2716,7 +2654,7 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="22" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -2761,10 +2699,10 @@
       <c r="D2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="26">
         <v>4275.3</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="26">
         <v>77009.210000000006</v>
       </c>
       <c r="G2" s="4">
@@ -2833,10 +2771,10 @@
       <c r="D3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="26">
         <v>7461.93</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="26">
         <v>46748.29</v>
       </c>
       <c r="G3" s="4">
@@ -2887,10 +2825,10 @@
       <c r="D4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="26">
         <v>4770.58</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="26">
         <v>89040.79</v>
       </c>
       <c r="G4" s="4">
@@ -2955,10 +2893,10 @@
       <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="26">
         <v>7701.21</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="26">
         <v>160981.76000000001</v>
       </c>
       <c r="G5" s="4">
@@ -3019,10 +2957,10 @@
       <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="26">
         <v>5668.48</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="26">
         <v>94110.1</v>
       </c>
       <c r="G6" s="4">
@@ -3087,10 +3025,10 @@
       <c r="D7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="26">
         <v>8639.84</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="26">
         <v>131603.82</v>
       </c>
       <c r="G7" s="4">
@@ -3145,7 +3083,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
+      <c r="A8" s="8">
         <v>46253</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -3155,10 +3093,10 @@
       <c r="D8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="26">
         <v>8971</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="26">
         <v>79084.990000000005</v>
       </c>
       <c r="G8" s="4">
@@ -3208,27 +3146,27 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
-        <v>46259</v>
+        <v>46268</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="10">
-        <v>12786.37</v>
-      </c>
-      <c r="F9" s="10">
-        <v>104458.62</v>
+        <v>47</v>
+      </c>
+      <c r="E9" s="26">
+        <v>5954.82</v>
+      </c>
+      <c r="F9" s="26">
+        <v>69924.039999999994</v>
       </c>
       <c r="G9" s="4">
-        <v>633</v>
+        <v>1514</v>
       </c>
       <c r="H9" s="9">
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
-        <v>0.12240607811973776</v>
+        <v>8.5161269285927987E-2</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -3236,10 +3174,12 @@
         <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
         <v>0</v>
       </c>
-      <c r="L9" s="10"/>
+      <c r="L9" s="10">
+        <v>500</v>
+      </c>
       <c r="M9" s="9">
         <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
-        <v>0</v>
+        <v>8.3965594258096812E-2</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -3262,38 +3202,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="109" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="108" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="107" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="106" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="104" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="103" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="102" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="100" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3302,7 +3242,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3316,15 +3256,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y233"/>
+  <dimension ref="A1:Y242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="21" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" customWidth="1"/>
     <col min="11" max="11" width="10.28515625" customWidth="1"/>
     <col min="12" max="12" width="13.140625" customWidth="1"/>
@@ -3362,10 +3302,10 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="22" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -12644,10 +12584,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Rosinaldo</v>
       </c>
-      <c r="G109" s="20">
+      <c r="G109" s="10">
         <v>6107.34</v>
       </c>
-      <c r="H109" s="20">
+      <c r="H109" s="10">
         <v>220201.19</v>
       </c>
       <c r="I109" s="4">
@@ -12730,10 +12670,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
-      <c r="G110" s="20">
+      <c r="G110" s="10">
         <v>8968.25</v>
       </c>
-      <c r="H110" s="20">
+      <c r="H110" s="10">
         <v>121071.14</v>
       </c>
       <c r="I110" s="4">
@@ -12816,10 +12756,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Arnaldo</v>
       </c>
-      <c r="G111" s="20">
+      <c r="G111" s="10">
         <v>13448.98</v>
       </c>
-      <c r="H111" s="20">
+      <c r="H111" s="10">
         <v>203621.83</v>
       </c>
       <c r="I111" s="4">
@@ -12902,10 +12842,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Edilson</v>
       </c>
-      <c r="G112" s="20">
+      <c r="G112" s="10">
         <v>16015.07</v>
       </c>
-      <c r="H112" s="20">
+      <c r="H112" s="10">
         <v>218177.17</v>
       </c>
       <c r="I112" s="4">
@@ -12988,10 +12928,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Gilberto</v>
       </c>
-      <c r="G113" s="20">
+      <c r="G113" s="10">
         <v>6269.27</v>
       </c>
-      <c r="H113" s="20">
+      <c r="H113" s="10">
         <v>193795.68</v>
       </c>
       <c r="I113" s="4">
@@ -13074,10 +13014,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
-      <c r="G114" s="20">
+      <c r="G114" s="10">
         <v>1959.35</v>
       </c>
-      <c r="H114" s="20">
+      <c r="H114" s="10">
         <v>24688.86</v>
       </c>
       <c r="I114" s="4">
@@ -13160,10 +13100,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Juscelino</v>
       </c>
-      <c r="G115" s="20">
+      <c r="G115" s="10">
         <v>6952.52</v>
       </c>
-      <c r="H115" s="20">
+      <c r="H115" s="10">
         <v>192915.32</v>
       </c>
       <c r="I115" s="4">
@@ -13246,10 +13186,10 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Paulo</v>
       </c>
-      <c r="G116" s="20">
+      <c r="G116" s="10">
         <v>677.17</v>
       </c>
-      <c r="H116" s="20">
+      <c r="H116" s="10">
         <v>22770.12</v>
       </c>
       <c r="I116" s="4">
@@ -13332,7 +13272,7 @@
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
         <v>Osvaldo</v>
       </c>
-      <c r="G117" s="20">
+      <c r="G117" s="10">
         <v>2289.52</v>
       </c>
       <c r="H117" s="10">
@@ -22515,11 +22455,11 @@
       <c r="A224" s="8">
         <v>46267</v>
       </c>
-      <c r="B224" s="22">
+      <c r="B224" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C224" s="22">
+      <c r="C224" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22601,11 +22541,11 @@
       <c r="A225" s="8">
         <v>46267</v>
       </c>
-      <c r="B225" s="22">
+      <c r="B225" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C225" s="22">
+      <c r="C225" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22687,11 +22627,11 @@
       <c r="A226" s="8">
         <v>46267</v>
       </c>
-      <c r="B226" s="22">
+      <c r="B226" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C226" s="22">
+      <c r="C226" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22773,11 +22713,11 @@
       <c r="A227" s="8">
         <v>46267</v>
       </c>
-      <c r="B227" s="22">
+      <c r="B227" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C227" s="22">
+      <c r="C227" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22859,11 +22799,11 @@
       <c r="A228" s="8">
         <v>46267</v>
       </c>
-      <c r="B228" s="22">
+      <c r="B228" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C228" s="22">
+      <c r="C228" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -22945,11 +22885,11 @@
       <c r="A229" s="8">
         <v>46267</v>
       </c>
-      <c r="B229" s="22">
+      <c r="B229" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C229" s="22">
+      <c r="C229" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23031,11 +22971,11 @@
       <c r="A230" s="8">
         <v>46267</v>
       </c>
-      <c r="B230" s="22">
+      <c r="B230" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C230" s="22">
+      <c r="C230" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23117,11 +23057,11 @@
       <c r="A231" s="8">
         <v>46267</v>
       </c>
-      <c r="B231" s="22">
+      <c r="B231" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C231" s="22">
+      <c r="C231" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23203,11 +23143,11 @@
       <c r="A232" s="8">
         <v>46267</v>
       </c>
-      <c r="B232" s="22">
+      <c r="B232" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C232" s="22">
+      <c r="C232" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23289,11 +23229,11 @@
       <c r="A233" s="8">
         <v>46267</v>
       </c>
-      <c r="B233" s="22">
+      <c r="B233" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C233" s="22">
+      <c r="C233" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23371,40 +23311,814 @@
         <v>0</v>
       </c>
     </row>
+    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A234" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B234" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C234" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E234" s="4">
+        <v>1</v>
+      </c>
+      <c r="F234" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G234" s="10">
+        <v>4151.6400000000003</v>
+      </c>
+      <c r="H234" s="10">
+        <v>44278.43</v>
+      </c>
+      <c r="I234" s="4">
+        <v>553</v>
+      </c>
+      <c r="J234" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.376213203584681E-2</v>
+      </c>
+      <c r="K234" s="11">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="L234" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M234" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39861111111111108</v>
+      </c>
+      <c r="N234" s="4">
+        <v>154891</v>
+      </c>
+      <c r="O234" s="4">
+        <v>154949</v>
+      </c>
+      <c r="P234" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>58</v>
+      </c>
+      <c r="Q234" s="4">
+        <v>121</v>
+      </c>
+      <c r="R234" s="4">
+        <v>15</v>
+      </c>
+      <c r="S234" s="4">
+        <v>15</v>
+      </c>
+      <c r="T234" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U234" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V234" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W234" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X234" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y234" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A235" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B235" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C235" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E235" s="4">
+        <v>11</v>
+      </c>
+      <c r="F235" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G235" s="10">
+        <v>18210.439999999999</v>
+      </c>
+      <c r="H235" s="10">
+        <v>232635.02</v>
+      </c>
+      <c r="I235" s="4">
+        <v>4506</v>
+      </c>
+      <c r="J235" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.8279014053859994E-2</v>
+      </c>
+      <c r="K235" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L235" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M235" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777785</v>
+      </c>
+      <c r="N235" s="4">
+        <v>104767</v>
+      </c>
+      <c r="O235" s="4">
+        <v>104895</v>
+      </c>
+      <c r="P235" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>128</v>
+      </c>
+      <c r="Q235" s="4">
+        <v>771</v>
+      </c>
+      <c r="R235" s="4">
+        <v>21</v>
+      </c>
+      <c r="S235" s="4">
+        <v>13</v>
+      </c>
+      <c r="T235" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>8</v>
+      </c>
+      <c r="U235" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="V235" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W235" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X235" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y235" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A236" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B236" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C236" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E236" s="4">
+        <v>1</v>
+      </c>
+      <c r="F236" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G236" s="10">
+        <v>8185.35</v>
+      </c>
+      <c r="H236" s="10">
+        <v>133587.75</v>
+      </c>
+      <c r="I236" s="4">
+        <v>1616</v>
+      </c>
+      <c r="J236" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1273208059870764E-2</v>
+      </c>
+      <c r="K236" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L236" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M236" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N236" s="4">
+        <v>304009</v>
+      </c>
+      <c r="O236" s="4">
+        <v>304114</v>
+      </c>
+      <c r="P236" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>105</v>
+      </c>
+      <c r="Q236" s="4">
+        <v>235</v>
+      </c>
+      <c r="R236" s="4">
+        <v>21</v>
+      </c>
+      <c r="S236" s="4">
+        <v>21</v>
+      </c>
+      <c r="T236" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U236" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V236" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W236" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X236" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y236" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A237" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B237" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C237" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E237" s="4">
+        <v>5</v>
+      </c>
+      <c r="F237" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G237" s="10">
+        <v>7540.74</v>
+      </c>
+      <c r="H237" s="10">
+        <v>186752.55</v>
+      </c>
+      <c r="I237" s="4">
+        <v>2506</v>
+      </c>
+      <c r="J237" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0378243831208735E-2</v>
+      </c>
+      <c r="K237" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L237" s="15">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="M237" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41319444444444448</v>
+      </c>
+      <c r="N237" s="4">
+        <v>124753</v>
+      </c>
+      <c r="O237" s="4">
+        <v>124827</v>
+      </c>
+      <c r="P237" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>74</v>
+      </c>
+      <c r="Q237" s="4">
+        <v>425</v>
+      </c>
+      <c r="R237" s="4">
+        <v>20</v>
+      </c>
+      <c r="S237" s="4">
+        <v>20</v>
+      </c>
+      <c r="T237" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U237" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V237" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W237" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X237" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y237" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A238" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B238" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C238" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E238" s="4">
+        <v>1</v>
+      </c>
+      <c r="F238" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G238" s="10">
+        <v>2273.54</v>
+      </c>
+      <c r="H238" s="10">
+        <v>101478.36</v>
+      </c>
+      <c r="I238" s="4">
+        <v>224</v>
+      </c>
+      <c r="J238" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.2404185483486331E-2</v>
+      </c>
+      <c r="K238" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L238" s="15">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="M238" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46249999999999997</v>
+      </c>
+      <c r="N238" s="4">
+        <v>275378</v>
+      </c>
+      <c r="O238" s="4">
+        <v>275420</v>
+      </c>
+      <c r="P238" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q238" s="4">
+        <v>91</v>
+      </c>
+      <c r="R238" s="4">
+        <v>3</v>
+      </c>
+      <c r="S238" s="4">
+        <v>3</v>
+      </c>
+      <c r="T238" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U238" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V238" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W238" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X238" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y238" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A239" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B239" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C239" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E239" s="4">
+        <v>4</v>
+      </c>
+      <c r="F239" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G239" s="10">
+        <v>6173.28</v>
+      </c>
+      <c r="H239" s="10">
+        <v>138635.42000000001</v>
+      </c>
+      <c r="I239" s="4">
+        <v>1804</v>
+      </c>
+      <c r="J239" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.4528880137557916E-2</v>
+      </c>
+      <c r="K239" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L239" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M239" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.36805555555555552</v>
+      </c>
+      <c r="N239" s="4">
+        <v>142664</v>
+      </c>
+      <c r="O239" s="4">
+        <v>142732</v>
+      </c>
+      <c r="P239" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>68</v>
+      </c>
+      <c r="Q239" s="4">
+        <v>324</v>
+      </c>
+      <c r="R239" s="4">
+        <v>23</v>
+      </c>
+      <c r="S239" s="4">
+        <v>23</v>
+      </c>
+      <c r="T239" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U239" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V239" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W239" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X239" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y239" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A240" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B240" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C240" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E240" s="4">
+        <v>2</v>
+      </c>
+      <c r="F240" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G240" s="10">
+        <v>7243.93</v>
+      </c>
+      <c r="H240" s="10">
+        <v>161351.76</v>
+      </c>
+      <c r="I240" s="4">
+        <v>1097</v>
+      </c>
+      <c r="J240" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.48952648548736E-2</v>
+      </c>
+      <c r="K240" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L240" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M240" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N240" s="4">
+        <v>119218</v>
+      </c>
+      <c r="O240" s="4">
+        <v>119272</v>
+      </c>
+      <c r="P240" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q240" s="4">
+        <v>263</v>
+      </c>
+      <c r="R240" s="4">
+        <v>29</v>
+      </c>
+      <c r="S240" s="4">
+        <v>29</v>
+      </c>
+      <c r="T240" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U240" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V240" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W240" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X240" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y240" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A241" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B241" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C241" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E241" s="4">
+        <v>3</v>
+      </c>
+      <c r="F241" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G241" s="10">
+        <v>7983.97</v>
+      </c>
+      <c r="H241" s="10">
+        <v>84635.8</v>
+      </c>
+      <c r="I241" s="4">
+        <v>1622</v>
+      </c>
+      <c r="J241" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.433324905063814E-2</v>
+      </c>
+      <c r="K241" s="11">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="L241" s="15">
+        <v>0.75624999999999998</v>
+      </c>
+      <c r="M241" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43680555555555556</v>
+      </c>
+      <c r="N241" s="4">
+        <v>280095</v>
+      </c>
+      <c r="O241" s="4">
+        <v>280154</v>
+      </c>
+      <c r="P241" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q241" s="4">
+        <v>131</v>
+      </c>
+      <c r="R241" s="4">
+        <v>14</v>
+      </c>
+      <c r="S241" s="4">
+        <v>14</v>
+      </c>
+      <c r="T241" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U241" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V241" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W241" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X241" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y241" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A242" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B242" s="20">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C242" s="20">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E242" s="4">
+        <v>1</v>
+      </c>
+      <c r="F242" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G242" s="10">
+        <v>3588.06</v>
+      </c>
+      <c r="H242" s="10">
+        <v>39576.42</v>
+      </c>
+      <c r="I242" s="4">
+        <v>326</v>
+      </c>
+      <c r="J242" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.0661560595930613E-2</v>
+      </c>
+      <c r="K242" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L242" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M242" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49999999999999994</v>
+      </c>
+      <c r="N242" s="4">
+        <v>291032</v>
+      </c>
+      <c r="O242" s="4">
+        <v>291074</v>
+      </c>
+      <c r="P242" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q242" s="4">
+        <v>45</v>
+      </c>
+      <c r="R242" s="4">
+        <v>3</v>
+      </c>
+      <c r="S242" s="4">
+        <v>3</v>
+      </c>
+      <c r="T242" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U242" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V242" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W242" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X242" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y242" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J233">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J242">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U233">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U242">
+    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V233">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V242">
+    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -23413,7 +24127,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23429,7 +24143,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D233</xm:sqref>
+          <xm:sqref>D2:D242</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
